--- a/data/Mina_modelo_costo_fijo_BS/elmo_data.xlsx
+++ b/data/Mina_modelo_costo_fijo_BS/elmo_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Agustin\Desktop\Elmo_infrastructure_NP\data\Mina_modelo_costo_fijo_BS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22FFBB25-F49C-4042-9134-F86050E4F40D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92B57914-0EF2-4D6A-A2C8-4756B8E24314}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2248,8 +2248,7 @@
         <v>8.3000000000000004E-2</v>
       </c>
       <c r="AE3">
-        <f>($Z$3-$Z$3*$AA$3)/chargers!$D$3</f>
-        <v>0.79999999999999993</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:31" ht="23.7" customHeight="1" x14ac:dyDescent="0.3">
@@ -2344,8 +2343,7 @@
         <v>8.3000000000000004E-2</v>
       </c>
       <c r="AE4">
-        <f>($Z$3-$Z$3*$AA$3)/chargers!$D$3</f>
-        <v>0.79999999999999993</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:31" ht="23.7" customHeight="1" x14ac:dyDescent="0.3">
@@ -2440,8 +2438,7 @@
         <v>8.3000000000000004E-2</v>
       </c>
       <c r="AE5">
-        <f>($Z$3-$Z$3*$AA$3)/chargers!$D$3</f>
-        <v>0.79999999999999993</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:31" ht="23.7" customHeight="1" x14ac:dyDescent="0.3">
@@ -2536,8 +2533,8 @@
         <v>8.3000000000000004E-2</v>
       </c>
       <c r="AE6">
-        <f>($Z$3-$Z$3*$AA$3)/chargers!$D$3</f>
-        <v>0.79999999999999993</v>
+        <f>AE3</f>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:31" ht="23.7" customHeight="1" x14ac:dyDescent="0.3">

--- a/data/Mina_modelo_costo_fijo_BS/elmo_data.xlsx
+++ b/data/Mina_modelo_costo_fijo_BS/elmo_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Agustin\Desktop\Elmo_infrastructure_NP\data\Mina_modelo_costo_fijo_BS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TECNO-MASTER\Desktop\Elmo_infrastructure_sizing_NP-\data\Mina_modelo_costo_fijo_BS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92B57914-0EF2-4D6A-A2C8-4756B8E24314}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB3E1622-4007-402D-8548-A19348BBF505}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Batteries" sheetId="1" r:id="rId1"/>
@@ -1297,24 +1297,24 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:AC34"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.6640625" style="32" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.33203125" style="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.6640625" style="18" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" style="17" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5546875" style="17" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.33203125" style="17" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" style="33" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.6640625" style="17" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.7109375" style="32" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" style="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.7109375" style="18" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" style="17" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="17" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="17" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" style="33" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" style="17" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15" style="17" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.6640625" style="33" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.44140625" style="33" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.7109375" style="33" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.42578125" style="33" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:29" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1365,7 +1365,7 @@
       <c r="AB1" s="36"/>
       <c r="AC1" s="36"/>
     </row>
-    <row r="2" spans="1:29" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:29" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="40" t="s">
         <v>3</v>
       </c>
@@ -1416,7 +1416,7 @@
       <c r="AB2" s="36"/>
       <c r="AC2" s="36"/>
     </row>
-    <row r="3" spans="1:29" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:29" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="41">
         <v>1</v>
       </c>
@@ -1467,7 +1467,7 @@
       <c r="AB3" s="46"/>
       <c r="AC3" s="46"/>
     </row>
-    <row r="4" spans="1:29" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:29" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="41">
         <v>2</v>
       </c>
@@ -1518,7 +1518,7 @@
       <c r="AB4" s="46"/>
       <c r="AC4" s="46"/>
     </row>
-    <row r="5" spans="1:29" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:29" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="41">
         <v>3</v>
       </c>
@@ -1569,7 +1569,7 @@
       <c r="AB5" s="46"/>
       <c r="AC5" s="46"/>
     </row>
-    <row r="6" spans="1:29" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:29" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="41">
         <v>4</v>
       </c>
@@ -1620,7 +1620,7 @@
       <c r="AB6" s="46"/>
       <c r="AC6" s="46"/>
     </row>
-    <row r="7" spans="1:29" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:29" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="41"/>
       <c r="B7" s="43"/>
       <c r="C7" s="45"/>
@@ -1635,7 +1635,7 @@
       <c r="L7" s="52"/>
       <c r="M7" s="52"/>
     </row>
-    <row r="8" spans="1:29" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:29" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="41"/>
       <c r="B8" s="43"/>
       <c r="C8" s="45"/>
@@ -1650,7 +1650,7 @@
       <c r="L8" s="52"/>
       <c r="M8" s="52"/>
     </row>
-    <row r="9" spans="1:29" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:29" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="41"/>
       <c r="B9" s="43"/>
       <c r="C9" s="45"/>
@@ -1665,7 +1665,7 @@
       <c r="L9" s="52"/>
       <c r="M9" s="52"/>
     </row>
-    <row r="10" spans="1:29" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:29" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="41"/>
       <c r="B10" s="43"/>
       <c r="C10" s="45"/>
@@ -1680,7 +1680,7 @@
       <c r="L10" s="52"/>
       <c r="M10" s="52"/>
     </row>
-    <row r="11" spans="1:29" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:29" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="41"/>
       <c r="B11" s="43"/>
       <c r="C11" s="45"/>
@@ -1695,7 +1695,7 @@
       <c r="L11" s="52"/>
       <c r="M11" s="52"/>
     </row>
-    <row r="12" spans="1:29" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:29" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="41"/>
       <c r="B12" s="43"/>
       <c r="C12" s="45"/>
@@ -1710,7 +1710,7 @@
       <c r="L12" s="52"/>
       <c r="M12" s="52"/>
     </row>
-    <row r="13" spans="1:29" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:29" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="41"/>
       <c r="B13" s="43"/>
       <c r="C13" s="45"/>
@@ -1725,7 +1725,7 @@
       <c r="L13" s="52"/>
       <c r="M13" s="52"/>
     </row>
-    <row r="14" spans="1:29" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:29" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="41"/>
       <c r="B14" s="43"/>
       <c r="C14" s="45"/>
@@ -1740,7 +1740,7 @@
       <c r="L14" s="52"/>
       <c r="M14" s="52"/>
     </row>
-    <row r="15" spans="1:29" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:29" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="41"/>
       <c r="B15" s="43"/>
       <c r="C15" s="45"/>
@@ -1755,7 +1755,7 @@
       <c r="L15" s="52"/>
       <c r="M15" s="52"/>
     </row>
-    <row r="16" spans="1:29" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:29" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="41"/>
       <c r="B16" s="43"/>
       <c r="C16" s="45"/>
@@ -1770,7 +1770,7 @@
       <c r="L16" s="52"/>
       <c r="M16" s="52"/>
     </row>
-    <row r="17" spans="1:13" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="41"/>
       <c r="B17" s="43"/>
       <c r="C17" s="45"/>
@@ -1785,7 +1785,7 @@
       <c r="L17" s="52"/>
       <c r="M17" s="52"/>
     </row>
-    <row r="18" spans="1:13" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="41"/>
       <c r="B18" s="43"/>
       <c r="C18" s="45"/>
@@ -1800,7 +1800,7 @@
       <c r="L18" s="52"/>
       <c r="M18" s="52"/>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="41"/>
       <c r="B19" s="43"/>
       <c r="C19" s="45"/>
@@ -1815,7 +1815,7 @@
       <c r="L19" s="52"/>
       <c r="M19" s="52"/>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="41"/>
       <c r="B20" s="43"/>
       <c r="C20" s="45"/>
@@ -1830,7 +1830,7 @@
       <c r="L20" s="52"/>
       <c r="M20" s="52"/>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="41"/>
       <c r="B21" s="43"/>
       <c r="C21" s="45"/>
@@ -1845,7 +1845,7 @@
       <c r="L21" s="52"/>
       <c r="M21" s="52"/>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="41"/>
       <c r="B22" s="43"/>
       <c r="C22" s="45"/>
@@ -1860,7 +1860,7 @@
       <c r="L22" s="52"/>
       <c r="M22" s="52"/>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="41"/>
       <c r="B23" s="43"/>
       <c r="C23" s="45"/>
@@ -1875,7 +1875,7 @@
       <c r="L23" s="52"/>
       <c r="M23" s="52"/>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="41"/>
       <c r="B24" s="43"/>
       <c r="C24" s="45"/>
@@ -1890,7 +1890,7 @@
       <c r="L24" s="52"/>
       <c r="M24" s="52"/>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="41"/>
       <c r="B25" s="43"/>
       <c r="C25" s="45"/>
@@ -1905,7 +1905,7 @@
       <c r="L25" s="52"/>
       <c r="M25" s="52"/>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="41"/>
       <c r="B26" s="43"/>
       <c r="C26" s="45"/>
@@ -1920,7 +1920,7 @@
       <c r="L26" s="52"/>
       <c r="M26" s="52"/>
     </row>
-    <row r="34" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H34" s="33"/>
     </row>
   </sheetData>
@@ -1935,38 +1935,38 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:AE17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" style="30" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" style="30" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.33203125" style="30" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5546875" style="30" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.44140625" style="30" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" style="30" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" style="30" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" style="30" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" style="30" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.42578125" style="30" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="7" style="30" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5546875" style="30" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.6640625" style="31" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.33203125" style="30" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5703125" style="30" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" style="31" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.28515625" style="30" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="15" style="30" customWidth="1"/>
-    <col min="16" max="16" width="17.33203125" style="30" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.5546875" style="31" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.28515625" style="30" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.5703125" style="31" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="18" style="31" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="20.6640625" style="31" bestFit="1" customWidth="1"/>
-    <col min="20" max="23" width="20.6640625" style="31" customWidth="1"/>
-    <col min="24" max="24" width="18.44140625" style="31" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="20.33203125" style="31" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15.5546875" style="31" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.33203125" style="31" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="20.7109375" style="31" bestFit="1" customWidth="1"/>
+    <col min="20" max="23" width="20.7109375" style="31" customWidth="1"/>
+    <col min="24" max="24" width="18.42578125" style="31" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="20.28515625" style="31" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15.5703125" style="31" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.28515625" style="31" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -2061,7 +2061,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="2" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="40" t="s">
         <v>3</v>
       </c>
@@ -2156,7 +2156,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="3" spans="1:31" ht="23.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:31" ht="23.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="41">
         <v>1</v>
       </c>
@@ -2251,7 +2251,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:31" ht="23.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:31" ht="23.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="41">
         <v>2</v>
       </c>
@@ -2346,7 +2346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:31" ht="23.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:31" ht="23.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="41">
         <v>3</v>
       </c>
@@ -2441,7 +2441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:31" ht="23.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:31" ht="23.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="41">
         <v>4</v>
       </c>
@@ -2537,7 +2537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" ht="23.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:31" ht="23.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="41"/>
       <c r="B7" s="70"/>
       <c r="C7" s="71"/>
@@ -2562,7 +2562,7 @@
       <c r="V7" s="46"/>
       <c r="W7" s="46"/>
     </row>
-    <row r="8" spans="1:31" ht="23.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:31" ht="23.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="41"/>
       <c r="B8" s="43"/>
       <c r="C8" s="45"/>
@@ -2587,7 +2587,7 @@
       <c r="V8" s="46"/>
       <c r="W8" s="46"/>
     </row>
-    <row r="9" spans="1:31" ht="23.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:31" ht="23.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="41"/>
       <c r="B9" s="43"/>
       <c r="C9" s="45"/>
@@ -2612,7 +2612,7 @@
       <c r="V9" s="46"/>
       <c r="W9" s="46"/>
     </row>
-    <row r="10" spans="1:31" ht="23.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:31" ht="23.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="58"/>
       <c r="B10" s="59"/>
       <c r="C10" s="60"/>
@@ -2637,7 +2637,7 @@
       <c r="V10" s="68"/>
       <c r="W10" s="68"/>
     </row>
-    <row r="11" spans="1:31" s="46" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:31" s="46" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="41"/>
       <c r="B11" s="43"/>
       <c r="C11" s="45"/>
@@ -2664,7 +2664,7 @@
       <c r="Z11" s="69"/>
       <c r="AA11" s="69"/>
     </row>
-    <row r="12" spans="1:31" s="46" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:31" s="46" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="41"/>
       <c r="B12" s="43"/>
       <c r="C12" s="45"/>
@@ -2691,7 +2691,7 @@
       <c r="Z12" s="69"/>
       <c r="AA12" s="69"/>
     </row>
-    <row r="13" spans="1:31" s="46" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:31" s="46" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="41"/>
       <c r="B13" s="43"/>
       <c r="C13" s="45"/>
@@ -2718,7 +2718,7 @@
       <c r="Z13" s="69"/>
       <c r="AA13" s="69"/>
     </row>
-    <row r="14" spans="1:31" s="46" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:31" s="46" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="41"/>
       <c r="B14" s="43"/>
       <c r="C14" s="45"/>
@@ -2745,9 +2745,9 @@
       <c r="Z14" s="69"/>
       <c r="AA14" s="69"/>
     </row>
-    <row r="15" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="17" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2757,13 +2757,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D86F6B0-26ED-4B02-B890-EDAFE42B3137}">
   <dimension ref="A1:G5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2786,7 +2786,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2809,7 +2809,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2823,16 +2823,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F3">
         <v>0</v>
       </c>
       <c r="G3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2846,16 +2846,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
       <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>3</v>
       </c>
@@ -2869,13 +2869,13 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -2886,15 +2886,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0351544-AA63-4F3E-855C-5CF465DCF681}">
   <dimension ref="A1:I3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2923,7 +2923,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2952,7 +2952,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2992,16 +2992,16 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:H346"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="13.5546875" style="18" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.44140625" style="18" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="29.33203125" style="17" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5546875" style="17" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" style="17" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="13.5703125" style="18" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="29.28515625" style="17" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" style="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -3027,7 +3027,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>3</v>
       </c>
@@ -3053,7 +3053,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14">
         <v>0</v>
       </c>
@@ -3079,7 +3079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="16">
         <v>1</v>
       </c>
@@ -3105,7 +3105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="16">
         <v>2</v>
       </c>
@@ -3131,7 +3131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="16">
         <v>3</v>
       </c>
@@ -3157,7 +3157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="16">
         <v>4</v>
       </c>
@@ -3183,7 +3183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16">
         <v>5</v>
       </c>
@@ -3209,7 +3209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16">
         <v>6</v>
       </c>
@@ -3235,7 +3235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16">
         <v>7</v>
       </c>
@@ -3261,7 +3261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="16">
         <v>8</v>
       </c>
@@ -3287,7 +3287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16">
         <v>9</v>
       </c>
@@ -3313,7 +3313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="16">
         <v>10</v>
       </c>
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="16">
         <v>11</v>
       </c>
@@ -3365,7 +3365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="16">
         <v>12</v>
       </c>
@@ -3391,7 +3391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="16">
         <v>13</v>
       </c>
@@ -3417,7 +3417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="16">
         <v>14</v>
       </c>
@@ -3443,7 +3443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="16">
         <v>15</v>
       </c>
@@ -3469,7 +3469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="16">
         <v>16</v>
       </c>
@@ -3495,7 +3495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16">
         <v>17</v>
       </c>
@@ -3521,7 +3521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="16">
         <v>18</v>
       </c>
@@ -3547,7 +3547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="16">
         <v>19</v>
       </c>
@@ -3573,7 +3573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="16">
         <v>20</v>
       </c>
@@ -3599,7 +3599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16">
         <v>21</v>
       </c>
@@ -3625,7 +3625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="16">
         <v>22</v>
       </c>
@@ -3651,7 +3651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="16">
         <v>23</v>
       </c>
@@ -3677,7 +3677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="16">
         <v>24</v>
       </c>
@@ -3703,7 +3703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="16">
         <v>25</v>
       </c>
@@ -3729,7 +3729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="16">
         <v>26</v>
       </c>
@@ -3755,7 +3755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="16">
         <v>27</v>
       </c>
@@ -3781,7 +3781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="16">
         <v>28</v>
       </c>
@@ -3807,7 +3807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="16">
         <v>29</v>
       </c>
@@ -3833,7 +3833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="16">
         <v>30</v>
       </c>
@@ -3859,7 +3859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="16">
         <v>31</v>
       </c>
@@ -3885,7 +3885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="16">
         <v>32</v>
       </c>
@@ -3911,7 +3911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="16">
         <v>33</v>
       </c>
@@ -3937,7 +3937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="16">
         <v>34</v>
       </c>
@@ -3963,7 +3963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="16">
         <v>35</v>
       </c>
@@ -3989,7 +3989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="16">
         <v>36</v>
       </c>
@@ -4015,7 +4015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="16">
         <v>37</v>
       </c>
@@ -4041,7 +4041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="16">
         <v>38</v>
       </c>
@@ -4067,7 +4067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="16">
         <v>39</v>
       </c>
@@ -4093,7 +4093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="16"/>
       <c r="B43" s="15"/>
       <c r="C43" s="15"/>
@@ -4103,7 +4103,7 @@
       <c r="G43" s="16"/>
       <c r="H43" s="14"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="16"/>
       <c r="B44" s="15"/>
       <c r="C44" s="15"/>
@@ -4113,7 +4113,7 @@
       <c r="G44" s="16"/>
       <c r="H44" s="14"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="16"/>
       <c r="B45" s="15"/>
       <c r="C45" s="15"/>
@@ -4123,7 +4123,7 @@
       <c r="G45" s="16"/>
       <c r="H45" s="14"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="16"/>
       <c r="B46" s="15"/>
       <c r="C46" s="15"/>
@@ -4133,7 +4133,7 @@
       <c r="G46" s="16"/>
       <c r="H46" s="14"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="16"/>
       <c r="B47" s="15"/>
       <c r="C47" s="15"/>
@@ -4143,7 +4143,7 @@
       <c r="G47" s="16"/>
       <c r="H47" s="14"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="16"/>
       <c r="B48" s="15"/>
       <c r="C48" s="15"/>
@@ -4153,7 +4153,7 @@
       <c r="G48" s="16"/>
       <c r="H48" s="14"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="16"/>
       <c r="B49" s="15"/>
       <c r="C49" s="15"/>
@@ -4163,7 +4163,7 @@
       <c r="G49" s="16"/>
       <c r="H49" s="14"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="16"/>
       <c r="B50" s="15"/>
       <c r="C50" s="15"/>
@@ -4173,7 +4173,7 @@
       <c r="G50" s="16"/>
       <c r="H50" s="14"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="16"/>
       <c r="B51" s="15"/>
       <c r="C51" s="15"/>
@@ -4183,7 +4183,7 @@
       <c r="G51" s="16"/>
       <c r="H51" s="14"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="16"/>
       <c r="B52" s="15"/>
       <c r="C52" s="15"/>
@@ -4193,7 +4193,7 @@
       <c r="G52" s="16"/>
       <c r="H52" s="14"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="16"/>
       <c r="B53" s="15"/>
       <c r="C53" s="15"/>
@@ -4203,7 +4203,7 @@
       <c r="G53" s="16"/>
       <c r="H53" s="14"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="16"/>
       <c r="B54" s="15"/>
       <c r="C54" s="15"/>
@@ -4213,7 +4213,7 @@
       <c r="G54" s="16"/>
       <c r="H54" s="14"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="16"/>
       <c r="B55" s="15"/>
       <c r="C55" s="15"/>
@@ -4223,7 +4223,7 @@
       <c r="G55" s="16"/>
       <c r="H55" s="14"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="16"/>
       <c r="B56" s="15"/>
       <c r="C56" s="15"/>
@@ -4233,7 +4233,7 @@
       <c r="G56" s="16"/>
       <c r="H56" s="14"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="16"/>
       <c r="B57" s="15"/>
       <c r="C57" s="15"/>
@@ -4243,7 +4243,7 @@
       <c r="G57" s="16"/>
       <c r="H57" s="14"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="16"/>
       <c r="B58" s="15"/>
       <c r="C58" s="15"/>
@@ -4253,7 +4253,7 @@
       <c r="G58" s="16"/>
       <c r="H58" s="14"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="16"/>
       <c r="B59" s="15"/>
       <c r="C59" s="15"/>
@@ -4263,7 +4263,7 @@
       <c r="G59" s="16"/>
       <c r="H59" s="14"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="16"/>
       <c r="B60" s="15"/>
       <c r="C60" s="15"/>
@@ -4273,7 +4273,7 @@
       <c r="G60" s="16"/>
       <c r="H60" s="14"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="16"/>
       <c r="B61" s="15"/>
       <c r="C61" s="15"/>
@@ -4283,7 +4283,7 @@
       <c r="G61" s="16"/>
       <c r="H61" s="14"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="16"/>
       <c r="B62" s="15"/>
       <c r="C62" s="15"/>
@@ -4293,7 +4293,7 @@
       <c r="G62" s="16"/>
       <c r="H62" s="14"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="16"/>
       <c r="B63" s="15"/>
       <c r="C63" s="15"/>
@@ -4303,7 +4303,7 @@
       <c r="G63" s="16"/>
       <c r="H63" s="14"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="16"/>
       <c r="B64" s="15"/>
       <c r="C64" s="15"/>
@@ -4313,7 +4313,7 @@
       <c r="G64" s="16"/>
       <c r="H64" s="14"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="16"/>
       <c r="B65" s="15"/>
       <c r="C65" s="15"/>
@@ -4323,7 +4323,7 @@
       <c r="G65" s="16"/>
       <c r="H65" s="14"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="16"/>
       <c r="B66" s="15"/>
       <c r="C66" s="15"/>
@@ -4333,7 +4333,7 @@
       <c r="G66" s="16"/>
       <c r="H66" s="14"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="16"/>
       <c r="B67" s="15"/>
       <c r="C67" s="15"/>
@@ -4343,7 +4343,7 @@
       <c r="G67" s="16"/>
       <c r="H67" s="14"/>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="16"/>
       <c r="B68" s="15"/>
       <c r="C68" s="15"/>
@@ -4353,7 +4353,7 @@
       <c r="G68" s="16"/>
       <c r="H68" s="14"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="16"/>
       <c r="B69" s="15"/>
       <c r="C69" s="15"/>
@@ -4363,7 +4363,7 @@
       <c r="G69" s="16"/>
       <c r="H69" s="14"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="16"/>
       <c r="B70" s="15"/>
       <c r="C70" s="15"/>
@@ -4373,7 +4373,7 @@
       <c r="G70" s="16"/>
       <c r="H70" s="14"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="16"/>
       <c r="B71" s="15"/>
       <c r="C71" s="15"/>
@@ -4383,7 +4383,7 @@
       <c r="G71" s="16"/>
       <c r="H71" s="14"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="16"/>
       <c r="B72" s="15"/>
       <c r="C72" s="15"/>
@@ -4393,7 +4393,7 @@
       <c r="G72" s="16"/>
       <c r="H72" s="14"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="16"/>
       <c r="B73" s="15"/>
       <c r="C73" s="15"/>
@@ -4403,7 +4403,7 @@
       <c r="G73" s="16"/>
       <c r="H73" s="14"/>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="16"/>
       <c r="B74" s="15"/>
       <c r="C74" s="15"/>
@@ -4413,7 +4413,7 @@
       <c r="G74" s="16"/>
       <c r="H74" s="14"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="16"/>
       <c r="B75" s="15"/>
       <c r="C75" s="15"/>
@@ -4423,7 +4423,7 @@
       <c r="G75" s="16"/>
       <c r="H75" s="14"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="16"/>
       <c r="B76" s="15"/>
       <c r="C76" s="15"/>
@@ -4433,7 +4433,7 @@
       <c r="G76" s="16"/>
       <c r="H76" s="14"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="16"/>
       <c r="B77" s="15"/>
       <c r="C77" s="15"/>
@@ -4443,7 +4443,7 @@
       <c r="G77" s="16"/>
       <c r="H77" s="14"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="16"/>
       <c r="B78" s="15"/>
       <c r="C78" s="15"/>
@@ -4453,7 +4453,7 @@
       <c r="G78" s="16"/>
       <c r="H78" s="14"/>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="16"/>
       <c r="B79" s="15"/>
       <c r="C79" s="15"/>
@@ -4463,7 +4463,7 @@
       <c r="G79" s="16"/>
       <c r="H79" s="14"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="16"/>
       <c r="B80" s="15"/>
       <c r="C80" s="15"/>
@@ -4473,7 +4473,7 @@
       <c r="G80" s="16"/>
       <c r="H80" s="14"/>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="16"/>
       <c r="B81" s="15"/>
       <c r="C81" s="15"/>
@@ -4483,7 +4483,7 @@
       <c r="G81" s="16"/>
       <c r="H81" s="14"/>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="16"/>
       <c r="B82" s="15"/>
       <c r="C82" s="15"/>
@@ -4493,7 +4493,7 @@
       <c r="G82" s="16"/>
       <c r="H82" s="14"/>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="16"/>
       <c r="B83" s="15"/>
       <c r="C83" s="15"/>
@@ -4503,7 +4503,7 @@
       <c r="G83" s="16"/>
       <c r="H83" s="14"/>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="16"/>
       <c r="B84" s="15"/>
       <c r="C84" s="15"/>
@@ -4513,7 +4513,7 @@
       <c r="G84" s="16"/>
       <c r="H84" s="14"/>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="16"/>
       <c r="B85" s="15"/>
       <c r="C85" s="15"/>
@@ -4523,7 +4523,7 @@
       <c r="G85" s="16"/>
       <c r="H85" s="14"/>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="16"/>
       <c r="B86" s="15"/>
       <c r="C86" s="15"/>
@@ -4533,7 +4533,7 @@
       <c r="G86" s="16"/>
       <c r="H86" s="14"/>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="16"/>
       <c r="B87" s="15"/>
       <c r="C87" s="15"/>
@@ -4543,7 +4543,7 @@
       <c r="G87" s="16"/>
       <c r="H87" s="14"/>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="16"/>
       <c r="B88" s="15"/>
       <c r="C88" s="15"/>
@@ -4553,7 +4553,7 @@
       <c r="G88" s="16"/>
       <c r="H88" s="14"/>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="16"/>
       <c r="B89" s="15"/>
       <c r="C89" s="15"/>
@@ -4563,7 +4563,7 @@
       <c r="G89" s="16"/>
       <c r="H89" s="14"/>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="16"/>
       <c r="B90" s="15"/>
       <c r="C90" s="15"/>
@@ -4573,7 +4573,7 @@
       <c r="G90" s="16"/>
       <c r="H90" s="14"/>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="16"/>
       <c r="B91" s="15"/>
       <c r="C91" s="15"/>
@@ -4583,7 +4583,7 @@
       <c r="G91" s="16"/>
       <c r="H91" s="14"/>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="16"/>
       <c r="B92" s="15"/>
       <c r="C92" s="15"/>
@@ -4593,7 +4593,7 @@
       <c r="G92" s="16"/>
       <c r="H92" s="14"/>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="16"/>
       <c r="B93" s="15"/>
       <c r="C93" s="15"/>
@@ -4603,7 +4603,7 @@
       <c r="G93" s="16"/>
       <c r="H93" s="14"/>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="16"/>
       <c r="B94" s="15"/>
       <c r="C94" s="15"/>
@@ -4613,7 +4613,7 @@
       <c r="G94" s="16"/>
       <c r="H94" s="14"/>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="16"/>
       <c r="B95" s="15"/>
       <c r="C95" s="15"/>
@@ -4623,7 +4623,7 @@
       <c r="G95" s="16"/>
       <c r="H95" s="14"/>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="16"/>
       <c r="B96" s="15"/>
       <c r="C96" s="15"/>
@@ -4633,7 +4633,7 @@
       <c r="G96" s="16"/>
       <c r="H96" s="14"/>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="16"/>
       <c r="B97" s="15"/>
       <c r="C97" s="15"/>
@@ -4643,7 +4643,7 @@
       <c r="G97" s="16"/>
       <c r="H97" s="14"/>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="16"/>
       <c r="B98" s="15"/>
       <c r="C98" s="15"/>
@@ -4653,7 +4653,7 @@
       <c r="G98" s="16"/>
       <c r="H98" s="14"/>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" s="16"/>
       <c r="B99" s="15"/>
       <c r="C99" s="15"/>
@@ -4663,7 +4663,7 @@
       <c r="G99" s="16"/>
       <c r="H99" s="14"/>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="16"/>
       <c r="B100" s="15"/>
       <c r="C100" s="15"/>
@@ -4673,7 +4673,7 @@
       <c r="G100" s="16"/>
       <c r="H100" s="14"/>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="16"/>
       <c r="B101" s="15"/>
       <c r="C101" s="15"/>
@@ -4683,7 +4683,7 @@
       <c r="G101" s="16"/>
       <c r="H101" s="14"/>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" s="16"/>
       <c r="B102" s="15"/>
       <c r="C102" s="15"/>
@@ -4693,7 +4693,7 @@
       <c r="G102" s="16"/>
       <c r="H102" s="14"/>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" s="16"/>
       <c r="B103" s="15"/>
       <c r="C103" s="15"/>
@@ -4703,7 +4703,7 @@
       <c r="G103" s="16"/>
       <c r="H103" s="14"/>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" s="16"/>
       <c r="B104" s="15"/>
       <c r="C104" s="15"/>
@@ -4713,7 +4713,7 @@
       <c r="G104" s="16"/>
       <c r="H104" s="14"/>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" s="16"/>
       <c r="B105" s="15"/>
       <c r="C105" s="15"/>
@@ -4723,7 +4723,7 @@
       <c r="G105" s="16"/>
       <c r="H105" s="14"/>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" s="16"/>
       <c r="B106" s="15"/>
       <c r="C106" s="15"/>
@@ -4733,7 +4733,7 @@
       <c r="G106" s="16"/>
       <c r="H106" s="14"/>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" s="16"/>
       <c r="B107" s="15"/>
       <c r="C107" s="15"/>
@@ -4743,7 +4743,7 @@
       <c r="G107" s="16"/>
       <c r="H107" s="14"/>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" s="16"/>
       <c r="B108" s="15"/>
       <c r="C108" s="15"/>
@@ -4753,7 +4753,7 @@
       <c r="G108" s="16"/>
       <c r="H108" s="14"/>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" s="16"/>
       <c r="B109" s="15"/>
       <c r="C109" s="15"/>
@@ -4763,7 +4763,7 @@
       <c r="G109" s="16"/>
       <c r="H109" s="14"/>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" s="16"/>
       <c r="B110" s="15"/>
       <c r="C110" s="15"/>
@@ -4773,7 +4773,7 @@
       <c r="G110" s="16"/>
       <c r="H110" s="14"/>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" s="16"/>
       <c r="B111" s="15"/>
       <c r="C111" s="15"/>
@@ -4783,7 +4783,7 @@
       <c r="G111" s="16"/>
       <c r="H111" s="14"/>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" s="38"/>
       <c r="B112" s="15"/>
       <c r="C112" s="15"/>
@@ -4793,7 +4793,7 @@
       <c r="G112" s="16"/>
       <c r="H112" s="14"/>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" s="50"/>
       <c r="B113" s="15"/>
       <c r="C113" s="15"/>
@@ -4803,7 +4803,7 @@
       <c r="G113" s="16"/>
       <c r="H113" s="14"/>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" s="16"/>
       <c r="B114" s="15"/>
       <c r="C114" s="15"/>
@@ -4813,7 +4813,7 @@
       <c r="G114" s="56"/>
       <c r="H114" s="14"/>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" s="16"/>
       <c r="B115" s="15"/>
       <c r="C115" s="15"/>
@@ -4823,7 +4823,7 @@
       <c r="G115" s="56"/>
       <c r="H115" s="14"/>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" s="38"/>
       <c r="B116" s="15"/>
       <c r="C116" s="15"/>
@@ -4833,7 +4833,7 @@
       <c r="G116" s="56"/>
       <c r="H116" s="14"/>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" s="50"/>
       <c r="B117" s="15"/>
       <c r="C117" s="15"/>
@@ -4843,7 +4843,7 @@
       <c r="G117" s="56"/>
       <c r="H117" s="14"/>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" s="16"/>
       <c r="B118" s="15"/>
       <c r="C118" s="15"/>
@@ -4853,7 +4853,7 @@
       <c r="G118" s="56"/>
       <c r="H118" s="14"/>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" s="16"/>
       <c r="B119" s="15"/>
       <c r="C119" s="15"/>
@@ -4863,7 +4863,7 @@
       <c r="G119" s="56"/>
       <c r="H119" s="14"/>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" s="38"/>
       <c r="B120" s="15"/>
       <c r="C120" s="15"/>
@@ -4873,7 +4873,7 @@
       <c r="G120" s="56"/>
       <c r="H120" s="14"/>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" s="50"/>
       <c r="B121" s="15"/>
       <c r="C121" s="15"/>
@@ -4883,7 +4883,7 @@
       <c r="G121" s="56"/>
       <c r="H121" s="14"/>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" s="16"/>
       <c r="B122" s="15"/>
       <c r="C122" s="15"/>
@@ -4893,7 +4893,7 @@
       <c r="G122" s="56"/>
       <c r="H122" s="14"/>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" s="16"/>
       <c r="B123" s="15"/>
       <c r="C123" s="15"/>
@@ -4903,7 +4903,7 @@
       <c r="G123" s="56"/>
       <c r="H123" s="14"/>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" s="38"/>
       <c r="B124" s="15"/>
       <c r="C124" s="15"/>
@@ -4913,7 +4913,7 @@
       <c r="G124" s="56"/>
       <c r="H124" s="14"/>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" s="50"/>
       <c r="B125" s="15"/>
       <c r="C125" s="15"/>
@@ -4923,7 +4923,7 @@
       <c r="G125" s="56"/>
       <c r="H125" s="14"/>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" s="16"/>
       <c r="B126" s="15"/>
       <c r="C126" s="15"/>
@@ -4933,7 +4933,7 @@
       <c r="G126" s="56"/>
       <c r="H126" s="14"/>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" s="16"/>
       <c r="B127" s="15"/>
       <c r="C127" s="15"/>
@@ -4943,7 +4943,7 @@
       <c r="G127" s="56"/>
       <c r="H127" s="14"/>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" s="38"/>
       <c r="B128" s="15"/>
       <c r="C128" s="15"/>
@@ -4953,7 +4953,7 @@
       <c r="G128" s="56"/>
       <c r="H128" s="14"/>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" s="50"/>
       <c r="B129" s="15"/>
       <c r="C129" s="15"/>
@@ -4963,7 +4963,7 @@
       <c r="G129" s="56"/>
       <c r="H129" s="14"/>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" s="16"/>
       <c r="B130" s="15"/>
       <c r="C130" s="15"/>
@@ -4973,7 +4973,7 @@
       <c r="G130" s="56"/>
       <c r="H130" s="14"/>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" s="16"/>
       <c r="B131" s="15"/>
       <c r="C131" s="15"/>
@@ -4983,7 +4983,7 @@
       <c r="G131" s="56"/>
       <c r="H131" s="14"/>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" s="38"/>
       <c r="B132" s="15"/>
       <c r="C132" s="15"/>
@@ -4993,7 +4993,7 @@
       <c r="G132" s="56"/>
       <c r="H132" s="14"/>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" s="50"/>
       <c r="B133" s="15"/>
       <c r="C133" s="15"/>
@@ -5003,7 +5003,7 @@
       <c r="G133" s="56"/>
       <c r="H133" s="14"/>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" s="16"/>
       <c r="B134" s="15"/>
       <c r="C134" s="15"/>
@@ -5013,7 +5013,7 @@
       <c r="G134" s="56"/>
       <c r="H134" s="14"/>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" s="16"/>
       <c r="B135" s="15"/>
       <c r="C135" s="15"/>
@@ -5023,7 +5023,7 @@
       <c r="G135" s="56"/>
       <c r="H135" s="14"/>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" s="38"/>
       <c r="B136" s="15"/>
       <c r="C136" s="15"/>
@@ -5033,7 +5033,7 @@
       <c r="G136" s="56"/>
       <c r="H136" s="14"/>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" s="50"/>
       <c r="B137" s="15"/>
       <c r="C137" s="15"/>
@@ -5043,7 +5043,7 @@
       <c r="G137" s="56"/>
       <c r="H137" s="14"/>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" s="16"/>
       <c r="B138" s="15"/>
       <c r="C138" s="15"/>
@@ -5053,7 +5053,7 @@
       <c r="G138" s="56"/>
       <c r="H138" s="14"/>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" s="16"/>
       <c r="B139" s="15"/>
       <c r="C139" s="15"/>
@@ -5063,7 +5063,7 @@
       <c r="G139" s="56"/>
       <c r="H139" s="14"/>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" s="38"/>
       <c r="B140" s="15"/>
       <c r="C140" s="15"/>
@@ -5073,7 +5073,7 @@
       <c r="G140" s="56"/>
       <c r="H140" s="14"/>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" s="50"/>
       <c r="B141" s="15"/>
       <c r="C141" s="15"/>
@@ -5083,7 +5083,7 @@
       <c r="G141" s="56"/>
       <c r="H141" s="14"/>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" s="16"/>
       <c r="B142" s="15"/>
       <c r="C142" s="15"/>
@@ -5093,7 +5093,7 @@
       <c r="G142" s="56"/>
       <c r="H142" s="14"/>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" s="16"/>
       <c r="B143" s="15"/>
       <c r="C143" s="15"/>
@@ -5103,7 +5103,7 @@
       <c r="G143" s="56"/>
       <c r="H143" s="14"/>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" s="38"/>
       <c r="B144" s="15"/>
       <c r="C144" s="15"/>
@@ -5113,7 +5113,7 @@
       <c r="G144" s="56"/>
       <c r="H144" s="14"/>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" s="50"/>
       <c r="B145" s="15"/>
       <c r="C145" s="15"/>
@@ -5123,7 +5123,7 @@
       <c r="G145" s="56"/>
       <c r="H145" s="14"/>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" s="16"/>
       <c r="B146" s="15"/>
       <c r="C146" s="15"/>
@@ -5133,7 +5133,7 @@
       <c r="G146" s="56"/>
       <c r="H146" s="14"/>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" s="16"/>
       <c r="B147" s="15"/>
       <c r="C147" s="15"/>
@@ -5143,7 +5143,7 @@
       <c r="G147" s="56"/>
       <c r="H147" s="14"/>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" s="38"/>
       <c r="B148" s="15"/>
       <c r="C148" s="15"/>
@@ -5153,7 +5153,7 @@
       <c r="G148" s="56"/>
       <c r="H148" s="14"/>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" s="50"/>
       <c r="B149" s="15"/>
       <c r="C149" s="15"/>
@@ -5163,7 +5163,7 @@
       <c r="G149" s="56"/>
       <c r="H149" s="14"/>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" s="16"/>
       <c r="B150" s="15"/>
       <c r="C150" s="15"/>
@@ -5173,7 +5173,7 @@
       <c r="G150" s="56"/>
       <c r="H150" s="14"/>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" s="16"/>
       <c r="B151" s="15"/>
       <c r="C151" s="15"/>
@@ -5183,7 +5183,7 @@
       <c r="G151" s="56"/>
       <c r="H151" s="14"/>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" s="38"/>
       <c r="B152" s="15"/>
       <c r="C152" s="15"/>
@@ -5193,7 +5193,7 @@
       <c r="G152" s="56"/>
       <c r="H152" s="14"/>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" s="50"/>
       <c r="B153" s="15"/>
       <c r="C153" s="15"/>
@@ -5203,7 +5203,7 @@
       <c r="G153" s="56"/>
       <c r="H153" s="14"/>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" s="16"/>
       <c r="B154" s="15"/>
       <c r="C154" s="15"/>
@@ -5213,7 +5213,7 @@
       <c r="G154" s="56"/>
       <c r="H154" s="14"/>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155" s="16"/>
       <c r="B155" s="15"/>
       <c r="C155" s="15"/>
@@ -5223,7 +5223,7 @@
       <c r="G155" s="56"/>
       <c r="H155" s="14"/>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" s="38"/>
       <c r="B156" s="15"/>
       <c r="C156" s="15"/>
@@ -5233,7 +5233,7 @@
       <c r="G156" s="56"/>
       <c r="H156" s="14"/>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" s="50"/>
       <c r="B157" s="15"/>
       <c r="C157" s="15"/>
@@ -5243,7 +5243,7 @@
       <c r="G157" s="56"/>
       <c r="H157" s="14"/>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" s="16"/>
       <c r="B158" s="15"/>
       <c r="C158" s="15"/>
@@ -5253,7 +5253,7 @@
       <c r="G158" s="56"/>
       <c r="H158" s="14"/>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" s="16"/>
       <c r="B159" s="15"/>
       <c r="C159" s="15"/>
@@ -5263,7 +5263,7 @@
       <c r="G159" s="56"/>
       <c r="H159" s="14"/>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160" s="38"/>
       <c r="B160" s="15"/>
       <c r="C160" s="15"/>
@@ -5273,7 +5273,7 @@
       <c r="G160" s="56"/>
       <c r="H160" s="14"/>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" s="50"/>
       <c r="B161" s="15"/>
       <c r="C161" s="15"/>
@@ -5283,7 +5283,7 @@
       <c r="G161" s="56"/>
       <c r="H161" s="14"/>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" s="16"/>
       <c r="B162" s="15"/>
       <c r="C162" s="15"/>
@@ -5293,7 +5293,7 @@
       <c r="G162" s="56"/>
       <c r="H162" s="14"/>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" s="16"/>
       <c r="B163" s="15"/>
       <c r="C163" s="15"/>
@@ -5303,7 +5303,7 @@
       <c r="G163" s="56"/>
       <c r="H163" s="14"/>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" s="38"/>
       <c r="B164" s="15"/>
       <c r="C164" s="15"/>
@@ -5313,7 +5313,7 @@
       <c r="G164" s="56"/>
       <c r="H164" s="14"/>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165" s="50"/>
       <c r="B165" s="15"/>
       <c r="C165" s="15"/>
@@ -5323,7 +5323,7 @@
       <c r="G165" s="56"/>
       <c r="H165" s="14"/>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166" s="16"/>
       <c r="B166" s="15"/>
       <c r="C166" s="15"/>
@@ -5333,7 +5333,7 @@
       <c r="G166" s="56"/>
       <c r="H166" s="14"/>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167" s="16"/>
       <c r="B167" s="15"/>
       <c r="C167" s="15"/>
@@ -5343,7 +5343,7 @@
       <c r="G167" s="56"/>
       <c r="H167" s="14"/>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168" s="38"/>
       <c r="B168" s="15"/>
       <c r="C168" s="15"/>
@@ -5353,7 +5353,7 @@
       <c r="G168" s="56"/>
       <c r="H168" s="14"/>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169" s="50"/>
       <c r="B169" s="15"/>
       <c r="C169" s="15"/>
@@ -5363,7 +5363,7 @@
       <c r="G169" s="56"/>
       <c r="H169" s="14"/>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170" s="16"/>
       <c r="B170" s="15"/>
       <c r="C170" s="15"/>
@@ -5373,7 +5373,7 @@
       <c r="G170" s="56"/>
       <c r="H170" s="14"/>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171" s="16"/>
       <c r="B171" s="15"/>
       <c r="C171" s="15"/>
@@ -5383,7 +5383,7 @@
       <c r="G171" s="56"/>
       <c r="H171" s="14"/>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172" s="38"/>
       <c r="B172" s="15"/>
       <c r="C172" s="15"/>
@@ -5393,7 +5393,7 @@
       <c r="G172" s="56"/>
       <c r="H172" s="14"/>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" s="50"/>
       <c r="B173" s="15"/>
       <c r="C173" s="15"/>
@@ -5403,7 +5403,7 @@
       <c r="G173" s="56"/>
       <c r="H173" s="14"/>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174" s="16"/>
       <c r="B174" s="15"/>
       <c r="C174" s="15"/>
@@ -5413,7 +5413,7 @@
       <c r="G174" s="56"/>
       <c r="H174" s="14"/>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175" s="16"/>
       <c r="B175" s="15"/>
       <c r="C175" s="15"/>
@@ -5423,7 +5423,7 @@
       <c r="G175" s="56"/>
       <c r="H175" s="14"/>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176" s="38"/>
       <c r="B176" s="15"/>
       <c r="C176" s="15"/>
@@ -5433,7 +5433,7 @@
       <c r="G176" s="56"/>
       <c r="H176" s="14"/>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177" s="50"/>
       <c r="B177" s="15"/>
       <c r="C177" s="15"/>
@@ -5443,7 +5443,7 @@
       <c r="G177" s="56"/>
       <c r="H177" s="14"/>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178" s="16"/>
       <c r="B178" s="15"/>
       <c r="C178" s="15"/>
@@ -5453,7 +5453,7 @@
       <c r="G178" s="56"/>
       <c r="H178" s="14"/>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179" s="16"/>
       <c r="B179" s="15"/>
       <c r="C179" s="15"/>
@@ -5463,7 +5463,7 @@
       <c r="G179" s="56"/>
       <c r="H179" s="14"/>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180" s="38"/>
       <c r="B180" s="15"/>
       <c r="C180" s="15"/>
@@ -5473,7 +5473,7 @@
       <c r="G180" s="56"/>
       <c r="H180" s="14"/>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181" s="50"/>
       <c r="B181" s="15"/>
       <c r="C181" s="15"/>
@@ -5483,7 +5483,7 @@
       <c r="G181" s="56"/>
       <c r="H181" s="14"/>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182" s="16"/>
       <c r="B182" s="15"/>
       <c r="C182" s="15"/>
@@ -5493,7 +5493,7 @@
       <c r="G182" s="56"/>
       <c r="H182" s="14"/>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183" s="16"/>
       <c r="B183" s="15"/>
       <c r="C183" s="15"/>
@@ -5503,7 +5503,7 @@
       <c r="G183" s="56"/>
       <c r="H183" s="14"/>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184" s="38"/>
       <c r="B184" s="15"/>
       <c r="C184" s="15"/>
@@ -5513,7 +5513,7 @@
       <c r="G184" s="56"/>
       <c r="H184" s="14"/>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185" s="50"/>
       <c r="B185" s="15"/>
       <c r="C185" s="15"/>
@@ -5523,7 +5523,7 @@
       <c r="G185" s="56"/>
       <c r="H185" s="14"/>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186" s="16"/>
       <c r="B186" s="15"/>
       <c r="C186" s="15"/>
@@ -5533,7 +5533,7 @@
       <c r="G186" s="56"/>
       <c r="H186" s="14"/>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A187" s="16"/>
       <c r="B187" s="15"/>
       <c r="C187" s="15"/>
@@ -5543,7 +5543,7 @@
       <c r="G187" s="56"/>
       <c r="H187" s="14"/>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188" s="38"/>
       <c r="B188" s="15"/>
       <c r="C188" s="15"/>
@@ -5553,7 +5553,7 @@
       <c r="G188" s="56"/>
       <c r="H188" s="14"/>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189" s="50"/>
       <c r="B189" s="15"/>
       <c r="C189" s="15"/>
@@ -5563,7 +5563,7 @@
       <c r="G189" s="56"/>
       <c r="H189" s="14"/>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A190" s="16"/>
       <c r="B190" s="15"/>
       <c r="C190" s="15"/>
@@ -5573,7 +5573,7 @@
       <c r="G190" s="56"/>
       <c r="H190" s="14"/>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191" s="16"/>
       <c r="B191" s="15"/>
       <c r="C191" s="15"/>
@@ -5583,7 +5583,7 @@
       <c r="G191" s="56"/>
       <c r="H191" s="14"/>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A192" s="38"/>
       <c r="B192" s="15"/>
       <c r="C192" s="15"/>
@@ -5593,7 +5593,7 @@
       <c r="G192" s="56"/>
       <c r="H192" s="14"/>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193" s="50"/>
       <c r="B193" s="15"/>
       <c r="C193" s="15"/>
@@ -5603,7 +5603,7 @@
       <c r="G193" s="56"/>
       <c r="H193" s="14"/>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194" s="16"/>
       <c r="B194" s="15"/>
       <c r="C194" s="15"/>
@@ -5613,7 +5613,7 @@
       <c r="G194" s="56"/>
       <c r="H194" s="14"/>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195" s="16"/>
       <c r="B195" s="15"/>
       <c r="C195" s="15"/>
@@ -5623,7 +5623,7 @@
       <c r="G195" s="56"/>
       <c r="H195" s="14"/>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196" s="38"/>
       <c r="B196" s="15"/>
       <c r="C196" s="15"/>
@@ -5633,7 +5633,7 @@
       <c r="G196" s="56"/>
       <c r="H196" s="14"/>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197" s="50"/>
       <c r="B197" s="15"/>
       <c r="C197" s="15"/>
@@ -5643,7 +5643,7 @@
       <c r="G197" s="56"/>
       <c r="H197" s="14"/>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198" s="16"/>
       <c r="B198" s="15"/>
       <c r="C198" s="15"/>
@@ -5653,7 +5653,7 @@
       <c r="G198" s="56"/>
       <c r="H198" s="14"/>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A199" s="16"/>
       <c r="B199" s="15"/>
       <c r="C199" s="15"/>
@@ -5663,7 +5663,7 @@
       <c r="G199" s="56"/>
       <c r="H199" s="14"/>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200" s="38"/>
       <c r="B200" s="15"/>
       <c r="C200" s="15"/>
@@ -5673,7 +5673,7 @@
       <c r="G200" s="56"/>
       <c r="H200" s="14"/>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201" s="50"/>
       <c r="B201" s="15"/>
       <c r="C201" s="15"/>
@@ -5683,7 +5683,7 @@
       <c r="G201" s="56"/>
       <c r="H201" s="14"/>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A202" s="16"/>
       <c r="B202" s="15"/>
       <c r="C202" s="15"/>
@@ -5693,7 +5693,7 @@
       <c r="G202" s="56"/>
       <c r="H202" s="14"/>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A203" s="16"/>
       <c r="B203" s="15"/>
       <c r="C203" s="15"/>
@@ -5703,7 +5703,7 @@
       <c r="G203" s="56"/>
       <c r="H203" s="14"/>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A204" s="38"/>
       <c r="B204" s="15"/>
       <c r="C204" s="15"/>
@@ -5713,7 +5713,7 @@
       <c r="G204" s="56"/>
       <c r="H204" s="14"/>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A205" s="50"/>
       <c r="B205" s="15"/>
       <c r="C205" s="15"/>
@@ -5723,7 +5723,7 @@
       <c r="G205" s="56"/>
       <c r="H205" s="14"/>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A206" s="16"/>
       <c r="B206" s="15"/>
       <c r="C206" s="15"/>
@@ -5733,7 +5733,7 @@
       <c r="G206" s="56"/>
       <c r="H206" s="14"/>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A207" s="16"/>
       <c r="B207" s="15"/>
       <c r="C207" s="15"/>
@@ -5743,7 +5743,7 @@
       <c r="G207" s="56"/>
       <c r="H207" s="14"/>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A208" s="38"/>
       <c r="B208" s="15"/>
       <c r="C208" s="15"/>
@@ -5753,7 +5753,7 @@
       <c r="G208" s="56"/>
       <c r="H208" s="14"/>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A209" s="50"/>
       <c r="B209" s="15"/>
       <c r="C209" s="15"/>
@@ -5763,7 +5763,7 @@
       <c r="G209" s="56"/>
       <c r="H209" s="14"/>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A210" s="16"/>
       <c r="B210" s="15"/>
       <c r="C210" s="15"/>
@@ -5773,7 +5773,7 @@
       <c r="G210" s="56"/>
       <c r="H210" s="14"/>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A211" s="16"/>
       <c r="B211" s="15"/>
       <c r="C211" s="15"/>
@@ -5783,7 +5783,7 @@
       <c r="G211" s="56"/>
       <c r="H211" s="14"/>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A212" s="38"/>
       <c r="B212" s="15"/>
       <c r="C212" s="15"/>
@@ -5793,7 +5793,7 @@
       <c r="G212" s="56"/>
       <c r="H212" s="14"/>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A213" s="50"/>
       <c r="B213" s="15"/>
       <c r="C213" s="15"/>
@@ -5803,7 +5803,7 @@
       <c r="G213" s="56"/>
       <c r="H213" s="14"/>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A214" s="16"/>
       <c r="B214" s="15"/>
       <c r="C214" s="15"/>
@@ -5813,7 +5813,7 @@
       <c r="G214" s="56"/>
       <c r="H214" s="14"/>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A215" s="16"/>
       <c r="B215" s="15"/>
       <c r="C215" s="15"/>
@@ -5823,7 +5823,7 @@
       <c r="G215" s="56"/>
       <c r="H215" s="14"/>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A216" s="38"/>
       <c r="B216" s="15"/>
       <c r="C216" s="15"/>
@@ -5833,7 +5833,7 @@
       <c r="G216" s="56"/>
       <c r="H216" s="14"/>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A217" s="50"/>
       <c r="B217" s="15"/>
       <c r="C217" s="15"/>
@@ -5843,7 +5843,7 @@
       <c r="G217" s="56"/>
       <c r="H217" s="14"/>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A218" s="16"/>
       <c r="B218" s="15"/>
       <c r="C218" s="15"/>
@@ -5853,7 +5853,7 @@
       <c r="G218" s="56"/>
       <c r="H218" s="14"/>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A219" s="16"/>
       <c r="B219" s="15"/>
       <c r="C219" s="15"/>
@@ -5863,7 +5863,7 @@
       <c r="G219" s="56"/>
       <c r="H219" s="14"/>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A220" s="38"/>
       <c r="B220" s="15"/>
       <c r="C220" s="15"/>
@@ -5873,7 +5873,7 @@
       <c r="G220" s="56"/>
       <c r="H220" s="14"/>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A221" s="50"/>
       <c r="B221" s="15"/>
       <c r="C221" s="15"/>
@@ -5883,7 +5883,7 @@
       <c r="G221" s="56"/>
       <c r="H221" s="14"/>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A222" s="16"/>
       <c r="B222" s="15"/>
       <c r="C222" s="15"/>
@@ -5893,7 +5893,7 @@
       <c r="G222" s="56"/>
       <c r="H222" s="14"/>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A223" s="16"/>
       <c r="B223" s="15"/>
       <c r="C223" s="15"/>
@@ -5903,7 +5903,7 @@
       <c r="G223" s="56"/>
       <c r="H223" s="14"/>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A224" s="38"/>
       <c r="B224" s="15"/>
       <c r="C224" s="15"/>
@@ -5913,7 +5913,7 @@
       <c r="G224" s="56"/>
       <c r="H224" s="14"/>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A225" s="50"/>
       <c r="B225" s="15"/>
       <c r="C225" s="15"/>
@@ -5923,7 +5923,7 @@
       <c r="G225" s="56"/>
       <c r="H225" s="14"/>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A226" s="16"/>
       <c r="B226" s="15"/>
       <c r="C226" s="15"/>
@@ -5933,7 +5933,7 @@
       <c r="G226" s="56"/>
       <c r="H226" s="14"/>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A227" s="16"/>
       <c r="B227" s="15"/>
       <c r="C227" s="15"/>
@@ -5943,7 +5943,7 @@
       <c r="G227" s="56"/>
       <c r="H227" s="14"/>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A228" s="38"/>
       <c r="B228" s="15"/>
       <c r="C228" s="15"/>
@@ -5953,7 +5953,7 @@
       <c r="G228" s="56"/>
       <c r="H228" s="14"/>
     </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A229" s="50"/>
       <c r="B229" s="15"/>
       <c r="C229" s="15"/>
@@ -5963,7 +5963,7 @@
       <c r="G229" s="56"/>
       <c r="H229" s="14"/>
     </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A230" s="16"/>
       <c r="B230" s="15"/>
       <c r="C230" s="15"/>
@@ -5973,7 +5973,7 @@
       <c r="G230" s="56"/>
       <c r="H230" s="14"/>
     </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A231" s="16"/>
       <c r="B231" s="15"/>
       <c r="C231" s="15"/>
@@ -5981,7 +5981,7 @@
       <c r="G231" s="56"/>
       <c r="H231" s="14"/>
     </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A232" s="16"/>
       <c r="B232" s="15"/>
       <c r="C232" s="15"/>
@@ -5989,7 +5989,7 @@
       <c r="G232" s="56"/>
       <c r="H232" s="14"/>
     </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A233" s="38"/>
       <c r="B233" s="15"/>
       <c r="C233" s="15"/>
@@ -5997,7 +5997,7 @@
       <c r="G233" s="56"/>
       <c r="H233" s="14"/>
     </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A234" s="50"/>
       <c r="B234" s="15"/>
       <c r="C234" s="15"/>
@@ -6005,7 +6005,7 @@
       <c r="G234" s="56"/>
       <c r="H234" s="14"/>
     </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A235" s="16"/>
       <c r="B235" s="15"/>
       <c r="C235" s="15"/>
@@ -6013,7 +6013,7 @@
       <c r="G235" s="56"/>
       <c r="H235" s="14"/>
     </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A236" s="16"/>
       <c r="B236" s="15"/>
       <c r="C236" s="15"/>
@@ -6021,7 +6021,7 @@
       <c r="G236" s="56"/>
       <c r="H236" s="14"/>
     </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A237" s="16"/>
       <c r="B237" s="15"/>
       <c r="C237" s="15"/>
@@ -6029,7 +6029,7 @@
       <c r="G237" s="56"/>
       <c r="H237" s="14"/>
     </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A238" s="38"/>
       <c r="B238" s="15"/>
       <c r="C238" s="15"/>
@@ -6037,7 +6037,7 @@
       <c r="G238" s="56"/>
       <c r="H238" s="14"/>
     </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A239" s="50"/>
       <c r="B239" s="15"/>
       <c r="C239" s="15"/>
@@ -6045,7 +6045,7 @@
       <c r="G239" s="56"/>
       <c r="H239" s="14"/>
     </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A240" s="16"/>
       <c r="B240" s="15"/>
       <c r="C240" s="15"/>
@@ -6053,7 +6053,7 @@
       <c r="G240" s="56"/>
       <c r="H240" s="14"/>
     </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A241" s="16"/>
       <c r="B241" s="15"/>
       <c r="C241" s="15"/>
@@ -6061,7 +6061,7 @@
       <c r="G241" s="56"/>
       <c r="H241" s="14"/>
     </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A242" s="16"/>
       <c r="B242" s="15"/>
       <c r="C242" s="15"/>
@@ -6069,7 +6069,7 @@
       <c r="G242" s="56"/>
       <c r="H242" s="14"/>
     </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A243" s="38"/>
       <c r="B243" s="15"/>
       <c r="C243" s="15"/>
@@ -6077,7 +6077,7 @@
       <c r="G243" s="56"/>
       <c r="H243" s="14"/>
     </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A244" s="50"/>
       <c r="B244" s="15"/>
       <c r="C244" s="15"/>
@@ -6085,7 +6085,7 @@
       <c r="G244" s="56"/>
       <c r="H244" s="14"/>
     </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A245" s="16"/>
       <c r="B245" s="15"/>
       <c r="C245" s="15"/>
@@ -6093,7 +6093,7 @@
       <c r="G245" s="56"/>
       <c r="H245" s="14"/>
     </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A246" s="16"/>
       <c r="B246" s="15"/>
       <c r="C246" s="15"/>
@@ -6101,7 +6101,7 @@
       <c r="G246" s="56"/>
       <c r="H246" s="14"/>
     </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A247" s="16"/>
       <c r="B247" s="15"/>
       <c r="C247" s="15"/>
@@ -6109,7 +6109,7 @@
       <c r="G247" s="56"/>
       <c r="H247" s="14"/>
     </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A248" s="38"/>
       <c r="B248" s="15"/>
       <c r="C248" s="15"/>
@@ -6117,7 +6117,7 @@
       <c r="G248" s="56"/>
       <c r="H248" s="14"/>
     </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A249" s="50"/>
       <c r="B249" s="15"/>
       <c r="C249" s="15"/>
@@ -6125,7 +6125,7 @@
       <c r="G249" s="56"/>
       <c r="H249" s="14"/>
     </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A250" s="16"/>
       <c r="B250" s="15"/>
       <c r="C250" s="15"/>
@@ -6133,7 +6133,7 @@
       <c r="G250" s="56"/>
       <c r="H250" s="14"/>
     </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A251" s="16"/>
       <c r="B251" s="15"/>
       <c r="C251" s="15"/>
@@ -6141,7 +6141,7 @@
       <c r="G251" s="56"/>
       <c r="H251" s="14"/>
     </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A252" s="16"/>
       <c r="B252" s="15"/>
       <c r="C252" s="15"/>
@@ -6149,7 +6149,7 @@
       <c r="G252" s="56"/>
       <c r="H252" s="14"/>
     </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A253" s="38"/>
       <c r="B253" s="15"/>
       <c r="C253" s="15"/>
@@ -6157,7 +6157,7 @@
       <c r="G253" s="56"/>
       <c r="H253" s="14"/>
     </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A254" s="50"/>
       <c r="B254" s="15"/>
       <c r="C254" s="15"/>
@@ -6165,7 +6165,7 @@
       <c r="G254" s="56"/>
       <c r="H254" s="14"/>
     </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A255" s="16"/>
       <c r="B255" s="15"/>
       <c r="C255" s="15"/>
@@ -6173,7 +6173,7 @@
       <c r="G255" s="56"/>
       <c r="H255" s="14"/>
     </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A256" s="16"/>
       <c r="B256" s="15"/>
       <c r="C256" s="15"/>
@@ -6181,7 +6181,7 @@
       <c r="G256" s="56"/>
       <c r="H256" s="14"/>
     </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A257" s="16"/>
       <c r="B257" s="15"/>
       <c r="C257" s="15"/>
@@ -6189,7 +6189,7 @@
       <c r="G257" s="56"/>
       <c r="H257" s="14"/>
     </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A258" s="38"/>
       <c r="B258" s="15"/>
       <c r="C258" s="15"/>
@@ -6197,7 +6197,7 @@
       <c r="G258" s="56"/>
       <c r="H258" s="14"/>
     </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A259" s="50"/>
       <c r="B259" s="15"/>
       <c r="C259" s="15"/>
@@ -6205,7 +6205,7 @@
       <c r="G259" s="56"/>
       <c r="H259" s="14"/>
     </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A260" s="16"/>
       <c r="B260" s="15"/>
       <c r="C260" s="15"/>
@@ -6213,7 +6213,7 @@
       <c r="G260" s="56"/>
       <c r="H260" s="14"/>
     </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A261" s="16"/>
       <c r="B261" s="15"/>
       <c r="C261" s="15"/>
@@ -6221,7 +6221,7 @@
       <c r="G261" s="56"/>
       <c r="H261" s="14"/>
     </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A262" s="16"/>
       <c r="B262" s="15"/>
       <c r="C262" s="15"/>
@@ -6229,7 +6229,7 @@
       <c r="G262" s="56"/>
       <c r="H262" s="14"/>
     </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A263" s="38"/>
       <c r="B263" s="15"/>
       <c r="C263" s="15"/>
@@ -6237,7 +6237,7 @@
       <c r="G263" s="56"/>
       <c r="H263" s="14"/>
     </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A264" s="50"/>
       <c r="B264" s="15"/>
       <c r="C264" s="15"/>
@@ -6245,7 +6245,7 @@
       <c r="G264" s="56"/>
       <c r="H264" s="14"/>
     </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A265" s="16"/>
       <c r="B265" s="15"/>
       <c r="C265" s="15"/>
@@ -6253,7 +6253,7 @@
       <c r="G265" s="56"/>
       <c r="H265" s="14"/>
     </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A266" s="16"/>
       <c r="B266" s="15"/>
       <c r="C266" s="15"/>
@@ -6261,7 +6261,7 @@
       <c r="G266" s="56"/>
       <c r="H266" s="14"/>
     </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A267" s="16"/>
       <c r="B267" s="15"/>
       <c r="C267" s="15"/>
@@ -6269,7 +6269,7 @@
       <c r="G267" s="56"/>
       <c r="H267" s="14"/>
     </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A268" s="38"/>
       <c r="B268" s="15"/>
       <c r="C268" s="15"/>
@@ -6277,7 +6277,7 @@
       <c r="G268" s="56"/>
       <c r="H268" s="14"/>
     </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A269" s="50"/>
       <c r="B269" s="15"/>
       <c r="C269" s="15"/>
@@ -6285,7 +6285,7 @@
       <c r="G269" s="56"/>
       <c r="H269" s="14"/>
     </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A270" s="16"/>
       <c r="B270" s="15"/>
       <c r="C270" s="15"/>
@@ -6293,7 +6293,7 @@
       <c r="G270" s="56"/>
       <c r="H270" s="14"/>
     </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A271" s="16"/>
       <c r="B271" s="15"/>
       <c r="C271" s="15"/>
@@ -6301,7 +6301,7 @@
       <c r="G271" s="56"/>
       <c r="H271" s="14"/>
     </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A272" s="16"/>
       <c r="B272" s="15"/>
       <c r="C272" s="15"/>
@@ -6309,7 +6309,7 @@
       <c r="G272" s="56"/>
       <c r="H272" s="14"/>
     </row>
-    <row r="273" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A273" s="38"/>
       <c r="B273" s="15"/>
       <c r="C273" s="15"/>
@@ -6317,7 +6317,7 @@
       <c r="G273" s="56"/>
       <c r="H273" s="14"/>
     </row>
-    <row r="274" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A274" s="50"/>
       <c r="B274" s="15"/>
       <c r="C274" s="15"/>
@@ -6325,7 +6325,7 @@
       <c r="G274" s="56"/>
       <c r="H274" s="14"/>
     </row>
-    <row r="275" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A275" s="16"/>
       <c r="B275" s="15"/>
       <c r="C275" s="15"/>
@@ -6333,7 +6333,7 @@
       <c r="G275" s="56"/>
       <c r="H275" s="14"/>
     </row>
-    <row r="276" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A276" s="16"/>
       <c r="B276" s="15"/>
       <c r="C276" s="15"/>
@@ -6341,7 +6341,7 @@
       <c r="G276" s="56"/>
       <c r="H276" s="14"/>
     </row>
-    <row r="277" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A277" s="16"/>
       <c r="B277" s="15"/>
       <c r="C277" s="15"/>
@@ -6349,7 +6349,7 @@
       <c r="G277" s="56"/>
       <c r="H277" s="14"/>
     </row>
-    <row r="278" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A278" s="38"/>
       <c r="B278" s="15"/>
       <c r="C278" s="15"/>
@@ -6357,7 +6357,7 @@
       <c r="G278" s="56"/>
       <c r="H278" s="14"/>
     </row>
-    <row r="279" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A279" s="50"/>
       <c r="B279" s="15"/>
       <c r="C279" s="15"/>
@@ -6365,7 +6365,7 @@
       <c r="G279" s="56"/>
       <c r="H279" s="14"/>
     </row>
-    <row r="280" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A280" s="16"/>
       <c r="B280" s="15"/>
       <c r="C280" s="15"/>
@@ -6373,7 +6373,7 @@
       <c r="G280" s="56"/>
       <c r="H280" s="14"/>
     </row>
-    <row r="281" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A281" s="16"/>
       <c r="B281" s="15"/>
       <c r="C281" s="15"/>
@@ -6381,7 +6381,7 @@
       <c r="G281" s="56"/>
       <c r="H281" s="14"/>
     </row>
-    <row r="282" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A282" s="16"/>
       <c r="B282" s="15"/>
       <c r="C282" s="15"/>
@@ -6389,7 +6389,7 @@
       <c r="G282" s="56"/>
       <c r="H282" s="14"/>
     </row>
-    <row r="283" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A283" s="38"/>
       <c r="B283" s="15"/>
       <c r="C283" s="15"/>
@@ -6397,7 +6397,7 @@
       <c r="G283" s="56"/>
       <c r="H283" s="14"/>
     </row>
-    <row r="284" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A284" s="50"/>
       <c r="B284" s="15"/>
       <c r="C284" s="15"/>
@@ -6405,7 +6405,7 @@
       <c r="G284" s="56"/>
       <c r="H284" s="14"/>
     </row>
-    <row r="285" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A285" s="16"/>
       <c r="B285" s="15"/>
       <c r="C285" s="15"/>
@@ -6413,7 +6413,7 @@
       <c r="G285" s="56"/>
       <c r="H285" s="14"/>
     </row>
-    <row r="286" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A286" s="16"/>
       <c r="B286" s="15"/>
       <c r="C286" s="15"/>
@@ -6421,7 +6421,7 @@
       <c r="G286" s="56"/>
       <c r="H286" s="14"/>
     </row>
-    <row r="287" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A287" s="16"/>
       <c r="B287" s="15"/>
       <c r="C287" s="15"/>
@@ -6429,7 +6429,7 @@
       <c r="G287" s="56"/>
       <c r="H287" s="14"/>
     </row>
-    <row r="288" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A288" s="38"/>
       <c r="B288" s="15"/>
       <c r="C288" s="15"/>
@@ -6437,7 +6437,7 @@
       <c r="G288" s="56"/>
       <c r="H288" s="14"/>
     </row>
-    <row r="289" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A289" s="50"/>
       <c r="B289" s="15"/>
       <c r="C289" s="15"/>
@@ -6445,7 +6445,7 @@
       <c r="G289" s="56"/>
       <c r="H289" s="14"/>
     </row>
-    <row r="290" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A290" s="16"/>
       <c r="B290" s="15"/>
       <c r="C290" s="15"/>
@@ -6453,7 +6453,7 @@
       <c r="G290" s="56"/>
       <c r="H290" s="14"/>
     </row>
-    <row r="291" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A291" s="16"/>
       <c r="B291" s="15"/>
       <c r="C291" s="15"/>
@@ -6461,7 +6461,7 @@
       <c r="G291" s="56"/>
       <c r="H291" s="14"/>
     </row>
-    <row r="292" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A292" s="16"/>
       <c r="B292" s="15"/>
       <c r="C292" s="15"/>
@@ -6469,7 +6469,7 @@
       <c r="G292" s="56"/>
       <c r="H292" s="14"/>
     </row>
-    <row r="293" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A293" s="38"/>
       <c r="B293" s="15"/>
       <c r="C293" s="15"/>
@@ -6477,7 +6477,7 @@
       <c r="G293" s="56"/>
       <c r="H293" s="14"/>
     </row>
-    <row r="294" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A294" s="50"/>
       <c r="B294" s="15"/>
       <c r="C294" s="15"/>
@@ -6485,7 +6485,7 @@
       <c r="G294" s="56"/>
       <c r="H294" s="14"/>
     </row>
-    <row r="295" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A295" s="16"/>
       <c r="B295" s="15"/>
       <c r="C295" s="15"/>
@@ -6493,7 +6493,7 @@
       <c r="G295" s="56"/>
       <c r="H295" s="14"/>
     </row>
-    <row r="296" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A296" s="16"/>
       <c r="B296" s="15"/>
       <c r="C296" s="15"/>
@@ -6501,7 +6501,7 @@
       <c r="G296" s="56"/>
       <c r="H296" s="14"/>
     </row>
-    <row r="297" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A297" s="16"/>
       <c r="B297" s="15"/>
       <c r="C297" s="15"/>
@@ -6509,7 +6509,7 @@
       <c r="G297" s="56"/>
       <c r="H297" s="14"/>
     </row>
-    <row r="298" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A298" s="38"/>
       <c r="B298" s="15"/>
       <c r="C298" s="15"/>
@@ -6517,7 +6517,7 @@
       <c r="G298" s="56"/>
       <c r="H298" s="14"/>
     </row>
-    <row r="299" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A299" s="50"/>
       <c r="B299" s="15"/>
       <c r="C299" s="15"/>
@@ -6525,7 +6525,7 @@
       <c r="G299" s="56"/>
       <c r="H299" s="14"/>
     </row>
-    <row r="300" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A300" s="16"/>
       <c r="B300" s="15"/>
       <c r="C300" s="15"/>
@@ -6533,7 +6533,7 @@
       <c r="G300" s="56"/>
       <c r="H300" s="14"/>
     </row>
-    <row r="301" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A301" s="16"/>
       <c r="B301" s="15"/>
       <c r="C301" s="15"/>
@@ -6541,7 +6541,7 @@
       <c r="G301" s="56"/>
       <c r="H301" s="14"/>
     </row>
-    <row r="302" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A302" s="16"/>
       <c r="B302" s="15"/>
       <c r="C302" s="15"/>
@@ -6549,7 +6549,7 @@
       <c r="G302" s="56"/>
       <c r="H302" s="14"/>
     </row>
-    <row r="303" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A303" s="38"/>
       <c r="B303" s="15"/>
       <c r="C303" s="15"/>
@@ -6557,7 +6557,7 @@
       <c r="G303" s="56"/>
       <c r="H303" s="14"/>
     </row>
-    <row r="304" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A304" s="50"/>
       <c r="B304" s="15"/>
       <c r="C304" s="15"/>
@@ -6565,7 +6565,7 @@
       <c r="G304" s="56"/>
       <c r="H304" s="14"/>
     </row>
-    <row r="305" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A305" s="16"/>
       <c r="B305" s="15"/>
       <c r="C305" s="15"/>
@@ -6573,7 +6573,7 @@
       <c r="G305" s="56"/>
       <c r="H305" s="14"/>
     </row>
-    <row r="306" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A306" s="16"/>
       <c r="B306" s="15"/>
       <c r="C306" s="15"/>
@@ -6581,7 +6581,7 @@
       <c r="G306" s="56"/>
       <c r="H306" s="14"/>
     </row>
-    <row r="307" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A307" s="16"/>
       <c r="B307" s="15"/>
       <c r="C307" s="15"/>
@@ -6589,7 +6589,7 @@
       <c r="G307" s="56"/>
       <c r="H307" s="14"/>
     </row>
-    <row r="308" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A308" s="38"/>
       <c r="B308" s="15"/>
       <c r="C308" s="15"/>
@@ -6597,7 +6597,7 @@
       <c r="G308" s="56"/>
       <c r="H308" s="14"/>
     </row>
-    <row r="309" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A309" s="50"/>
       <c r="B309" s="15"/>
       <c r="C309" s="15"/>
@@ -6605,7 +6605,7 @@
       <c r="G309" s="56"/>
       <c r="H309" s="14"/>
     </row>
-    <row r="310" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A310" s="16"/>
       <c r="B310" s="15"/>
       <c r="C310" s="15"/>
@@ -6613,7 +6613,7 @@
       <c r="G310" s="56"/>
       <c r="H310" s="14"/>
     </row>
-    <row r="311" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A311" s="16"/>
       <c r="B311" s="15"/>
       <c r="C311" s="15"/>
@@ -6621,7 +6621,7 @@
       <c r="G311" s="56"/>
       <c r="H311" s="14"/>
     </row>
-    <row r="312" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A312" s="16"/>
       <c r="B312" s="15"/>
       <c r="C312" s="15"/>
@@ -6629,7 +6629,7 @@
       <c r="G312" s="56"/>
       <c r="H312" s="14"/>
     </row>
-    <row r="313" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A313" s="38"/>
       <c r="B313" s="15"/>
       <c r="C313" s="15"/>
@@ -6637,7 +6637,7 @@
       <c r="G313" s="56"/>
       <c r="H313" s="14"/>
     </row>
-    <row r="314" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A314" s="50"/>
       <c r="B314" s="15"/>
       <c r="C314" s="15"/>
@@ -6645,7 +6645,7 @@
       <c r="G314" s="56"/>
       <c r="H314" s="14"/>
     </row>
-    <row r="315" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A315" s="16"/>
       <c r="B315" s="15"/>
       <c r="C315" s="15"/>
@@ -6653,7 +6653,7 @@
       <c r="G315" s="56"/>
       <c r="H315" s="14"/>
     </row>
-    <row r="316" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A316" s="16"/>
       <c r="B316" s="15"/>
       <c r="C316" s="15"/>
@@ -6661,7 +6661,7 @@
       <c r="G316" s="56"/>
       <c r="H316" s="14"/>
     </row>
-    <row r="317" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A317" s="16"/>
       <c r="B317" s="15"/>
       <c r="C317" s="15"/>
@@ -6669,7 +6669,7 @@
       <c r="G317" s="56"/>
       <c r="H317" s="14"/>
     </row>
-    <row r="318" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A318" s="38"/>
       <c r="B318" s="15"/>
       <c r="C318" s="15"/>
@@ -6677,7 +6677,7 @@
       <c r="G318" s="56"/>
       <c r="H318" s="14"/>
     </row>
-    <row r="319" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A319" s="50"/>
       <c r="B319" s="15"/>
       <c r="C319" s="15"/>
@@ -6685,7 +6685,7 @@
       <c r="G319" s="56"/>
       <c r="H319" s="14"/>
     </row>
-    <row r="320" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A320" s="16"/>
       <c r="B320" s="15"/>
       <c r="C320" s="15"/>
@@ -6693,7 +6693,7 @@
       <c r="G320" s="56"/>
       <c r="H320" s="14"/>
     </row>
-    <row r="321" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A321" s="16"/>
       <c r="B321" s="15"/>
       <c r="C321" s="15"/>
@@ -6701,7 +6701,7 @@
       <c r="G321" s="56"/>
       <c r="H321" s="14"/>
     </row>
-    <row r="322" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A322" s="16"/>
       <c r="B322" s="15"/>
       <c r="C322" s="15"/>
@@ -6709,7 +6709,7 @@
       <c r="G322" s="56"/>
       <c r="H322" s="14"/>
     </row>
-    <row r="323" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A323" s="38"/>
       <c r="B323" s="15"/>
       <c r="C323" s="15"/>
@@ -6717,7 +6717,7 @@
       <c r="G323" s="56"/>
       <c r="H323" s="14"/>
     </row>
-    <row r="324" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A324" s="50"/>
       <c r="B324" s="15"/>
       <c r="C324" s="15"/>
@@ -6725,7 +6725,7 @@
       <c r="G324" s="56"/>
       <c r="H324" s="14"/>
     </row>
-    <row r="325" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A325" s="16"/>
       <c r="B325" s="15"/>
       <c r="C325" s="15"/>
@@ -6733,7 +6733,7 @@
       <c r="G325" s="56"/>
       <c r="H325" s="14"/>
     </row>
-    <row r="326" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A326" s="16"/>
       <c r="B326" s="15"/>
       <c r="C326" s="15"/>
@@ -6741,7 +6741,7 @@
       <c r="G326" s="56"/>
       <c r="H326" s="14"/>
     </row>
-    <row r="327" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A327" s="16"/>
       <c r="B327" s="15"/>
       <c r="C327" s="15"/>
@@ -6749,7 +6749,7 @@
       <c r="G327" s="56"/>
       <c r="H327" s="14"/>
     </row>
-    <row r="328" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A328" s="38"/>
       <c r="B328" s="15"/>
       <c r="C328" s="15"/>
@@ -6757,7 +6757,7 @@
       <c r="G328" s="56"/>
       <c r="H328" s="14"/>
     </row>
-    <row r="329" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A329" s="50"/>
       <c r="B329" s="15"/>
       <c r="C329" s="15"/>
@@ -6765,7 +6765,7 @@
       <c r="G329" s="56"/>
       <c r="H329" s="14"/>
     </row>
-    <row r="330" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A330" s="16"/>
       <c r="B330" s="15"/>
       <c r="C330" s="15"/>
@@ -6773,7 +6773,7 @@
       <c r="G330" s="56"/>
       <c r="H330" s="14"/>
     </row>
-    <row r="331" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A331" s="16"/>
       <c r="B331" s="15"/>
       <c r="C331" s="15"/>
@@ -6781,7 +6781,7 @@
       <c r="G331" s="56"/>
       <c r="H331" s="14"/>
     </row>
-    <row r="332" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A332" s="16"/>
       <c r="B332" s="15"/>
       <c r="C332" s="15"/>
@@ -6789,7 +6789,7 @@
       <c r="G332" s="56"/>
       <c r="H332" s="14"/>
     </row>
-    <row r="333" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A333" s="38"/>
       <c r="B333" s="15"/>
       <c r="C333" s="15"/>
@@ -6797,7 +6797,7 @@
       <c r="G333" s="56"/>
       <c r="H333" s="14"/>
     </row>
-    <row r="334" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A334" s="50"/>
       <c r="B334" s="15"/>
       <c r="C334" s="15"/>
@@ -6805,7 +6805,7 @@
       <c r="G334" s="56"/>
       <c r="H334" s="14"/>
     </row>
-    <row r="335" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A335" s="16"/>
       <c r="B335" s="15"/>
       <c r="C335" s="15"/>
@@ -6813,7 +6813,7 @@
       <c r="G335" s="56"/>
       <c r="H335" s="14"/>
     </row>
-    <row r="336" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A336" s="16"/>
       <c r="B336" s="15"/>
       <c r="C336" s="15"/>
@@ -6821,7 +6821,7 @@
       <c r="G336" s="56"/>
       <c r="H336" s="14"/>
     </row>
-    <row r="337" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A337" s="16"/>
       <c r="B337" s="15"/>
       <c r="C337" s="15"/>
@@ -6829,7 +6829,7 @@
       <c r="G337" s="56"/>
       <c r="H337" s="14"/>
     </row>
-    <row r="338" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A338" s="38"/>
       <c r="B338" s="15"/>
       <c r="C338" s="15"/>
@@ -6837,7 +6837,7 @@
       <c r="G338" s="56"/>
       <c r="H338" s="14"/>
     </row>
-    <row r="339" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A339" s="50"/>
       <c r="B339" s="15"/>
       <c r="C339" s="15"/>
@@ -6845,7 +6845,7 @@
       <c r="G339" s="56"/>
       <c r="H339" s="14"/>
     </row>
-    <row r="340" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A340" s="16"/>
       <c r="B340" s="15"/>
       <c r="C340" s="15"/>
@@ -6853,7 +6853,7 @@
       <c r="G340" s="56"/>
       <c r="H340" s="14"/>
     </row>
-    <row r="341" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A341" s="16"/>
       <c r="B341" s="15"/>
       <c r="C341" s="15"/>
@@ -6861,7 +6861,7 @@
       <c r="G341" s="56"/>
       <c r="H341" s="14"/>
     </row>
-    <row r="342" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A342" s="16"/>
       <c r="B342" s="15"/>
       <c r="C342" s="15"/>
@@ -6869,7 +6869,7 @@
       <c r="G342" s="56"/>
       <c r="H342" s="14"/>
     </row>
-    <row r="343" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A343" s="38"/>
       <c r="B343" s="15"/>
       <c r="C343" s="15"/>
@@ -6877,7 +6877,7 @@
       <c r="G343" s="56"/>
       <c r="H343" s="14"/>
     </row>
-    <row r="344" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A344" s="50"/>
       <c r="B344" s="15"/>
       <c r="C344" s="15"/>
@@ -6885,7 +6885,7 @@
       <c r="G344" s="56"/>
       <c r="H344" s="14"/>
     </row>
-    <row r="345" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A345" s="16"/>
       <c r="B345" s="15"/>
       <c r="C345" s="15"/>
@@ -6893,7 +6893,7 @@
       <c r="G345" s="56"/>
       <c r="H345" s="14"/>
     </row>
-    <row r="346" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A346" s="16"/>
       <c r="B346" s="15"/>
       <c r="C346" s="15"/>
@@ -6913,14 +6913,14 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6931,7 +6931,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -6942,7 +6942,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>0</v>
       </c>

--- a/data/Mina_modelo_costo_fijo_BS/elmo_data.xlsx
+++ b/data/Mina_modelo_costo_fijo_BS/elmo_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TECNO-MASTER\Desktop\Elmo_infrastructure_sizing_NP-\data\Mina_modelo_costo_fijo_BS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Agustin\Desktop\Elmo_infrastructure_NP\data\Mina_modelo_costo_fijo_BS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB3E1622-4007-402D-8548-A19348BBF505}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A87EEE48-3ED1-448E-B571-DF7493953906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Batteries" sheetId="1" r:id="rId1"/>
@@ -1297,24 +1297,24 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:AC34"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.7109375" style="32" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.28515625" style="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.7109375" style="18" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="17" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="17" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" style="17" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.42578125" style="33" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.7109375" style="17" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.6640625" style="32" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.33203125" style="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.6640625" style="18" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" style="17" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5546875" style="17" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.33203125" style="17" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" style="33" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" style="17" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15" style="17" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.7109375" style="33" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.42578125" style="33" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.6640625" style="33" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.44140625" style="33" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1365,7 +1365,7 @@
       <c r="AB1" s="36"/>
       <c r="AC1" s="36"/>
     </row>
-    <row r="2" spans="1:29" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="40" t="s">
         <v>3</v>
       </c>
@@ -1416,7 +1416,7 @@
       <c r="AB2" s="36"/>
       <c r="AC2" s="36"/>
     </row>
-    <row r="3" spans="1:29" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="41">
         <v>1</v>
       </c>
@@ -1467,7 +1467,7 @@
       <c r="AB3" s="46"/>
       <c r="AC3" s="46"/>
     </row>
-    <row r="4" spans="1:29" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="41">
         <v>2</v>
       </c>
@@ -1518,7 +1518,7 @@
       <c r="AB4" s="46"/>
       <c r="AC4" s="46"/>
     </row>
-    <row r="5" spans="1:29" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="41">
         <v>3</v>
       </c>
@@ -1569,7 +1569,7 @@
       <c r="AB5" s="46"/>
       <c r="AC5" s="46"/>
     </row>
-    <row r="6" spans="1:29" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="41">
         <v>4</v>
       </c>
@@ -1620,7 +1620,7 @@
       <c r="AB6" s="46"/>
       <c r="AC6" s="46"/>
     </row>
-    <row r="7" spans="1:29" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="41"/>
       <c r="B7" s="43"/>
       <c r="C7" s="45"/>
@@ -1635,7 +1635,7 @@
       <c r="L7" s="52"/>
       <c r="M7" s="52"/>
     </row>
-    <row r="8" spans="1:29" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="41"/>
       <c r="B8" s="43"/>
       <c r="C8" s="45"/>
@@ -1650,7 +1650,7 @@
       <c r="L8" s="52"/>
       <c r="M8" s="52"/>
     </row>
-    <row r="9" spans="1:29" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="41"/>
       <c r="B9" s="43"/>
       <c r="C9" s="45"/>
@@ -1665,7 +1665,7 @@
       <c r="L9" s="52"/>
       <c r="M9" s="52"/>
     </row>
-    <row r="10" spans="1:29" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="41"/>
       <c r="B10" s="43"/>
       <c r="C10" s="45"/>
@@ -1680,7 +1680,7 @@
       <c r="L10" s="52"/>
       <c r="M10" s="52"/>
     </row>
-    <row r="11" spans="1:29" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="41"/>
       <c r="B11" s="43"/>
       <c r="C11" s="45"/>
@@ -1695,7 +1695,7 @@
       <c r="L11" s="52"/>
       <c r="M11" s="52"/>
     </row>
-    <row r="12" spans="1:29" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:29" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="41"/>
       <c r="B12" s="43"/>
       <c r="C12" s="45"/>
@@ -1710,7 +1710,7 @@
       <c r="L12" s="52"/>
       <c r="M12" s="52"/>
     </row>
-    <row r="13" spans="1:29" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:29" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="41"/>
       <c r="B13" s="43"/>
       <c r="C13" s="45"/>
@@ -1725,7 +1725,7 @@
       <c r="L13" s="52"/>
       <c r="M13" s="52"/>
     </row>
-    <row r="14" spans="1:29" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:29" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="41"/>
       <c r="B14" s="43"/>
       <c r="C14" s="45"/>
@@ -1740,7 +1740,7 @@
       <c r="L14" s="52"/>
       <c r="M14" s="52"/>
     </row>
-    <row r="15" spans="1:29" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:29" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="41"/>
       <c r="B15" s="43"/>
       <c r="C15" s="45"/>
@@ -1755,7 +1755,7 @@
       <c r="L15" s="52"/>
       <c r="M15" s="52"/>
     </row>
-    <row r="16" spans="1:29" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:29" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="41"/>
       <c r="B16" s="43"/>
       <c r="C16" s="45"/>
@@ -1770,7 +1770,7 @@
       <c r="L16" s="52"/>
       <c r="M16" s="52"/>
     </row>
-    <row r="17" spans="1:13" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="41"/>
       <c r="B17" s="43"/>
       <c r="C17" s="45"/>
@@ -1785,7 +1785,7 @@
       <c r="L17" s="52"/>
       <c r="M17" s="52"/>
     </row>
-    <row r="18" spans="1:13" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="41"/>
       <c r="B18" s="43"/>
       <c r="C18" s="45"/>
@@ -1800,7 +1800,7 @@
       <c r="L18" s="52"/>
       <c r="M18" s="52"/>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="41"/>
       <c r="B19" s="43"/>
       <c r="C19" s="45"/>
@@ -1815,7 +1815,7 @@
       <c r="L19" s="52"/>
       <c r="M19" s="52"/>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="41"/>
       <c r="B20" s="43"/>
       <c r="C20" s="45"/>
@@ -1830,7 +1830,7 @@
       <c r="L20" s="52"/>
       <c r="M20" s="52"/>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="41"/>
       <c r="B21" s="43"/>
       <c r="C21" s="45"/>
@@ -1845,7 +1845,7 @@
       <c r="L21" s="52"/>
       <c r="M21" s="52"/>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="41"/>
       <c r="B22" s="43"/>
       <c r="C22" s="45"/>
@@ -1860,7 +1860,7 @@
       <c r="L22" s="52"/>
       <c r="M22" s="52"/>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="41"/>
       <c r="B23" s="43"/>
       <c r="C23" s="45"/>
@@ -1875,7 +1875,7 @@
       <c r="L23" s="52"/>
       <c r="M23" s="52"/>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="41"/>
       <c r="B24" s="43"/>
       <c r="C24" s="45"/>
@@ -1890,7 +1890,7 @@
       <c r="L24" s="52"/>
       <c r="M24" s="52"/>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="41"/>
       <c r="B25" s="43"/>
       <c r="C25" s="45"/>
@@ -1905,7 +1905,7 @@
       <c r="L25" s="52"/>
       <c r="M25" s="52"/>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="41"/>
       <c r="B26" s="43"/>
       <c r="C26" s="45"/>
@@ -1920,7 +1920,7 @@
       <c r="L26" s="52"/>
       <c r="M26" s="52"/>
     </row>
-    <row r="34" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H34" s="33"/>
     </row>
   </sheetData>
@@ -1935,38 +1935,38 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:AE17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" style="30" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.28515625" style="30" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.28515625" style="30" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" style="30" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.42578125" style="30" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" style="30" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" style="30" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" style="30" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5546875" style="30" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.44140625" style="30" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="7" style="30" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5703125" style="30" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" style="31" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.28515625" style="30" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5546875" style="30" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.6640625" style="31" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.33203125" style="30" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="15" style="30" customWidth="1"/>
-    <col min="16" max="16" width="17.28515625" style="30" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.5703125" style="31" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.33203125" style="30" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.5546875" style="31" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="18" style="31" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="20.7109375" style="31" bestFit="1" customWidth="1"/>
-    <col min="20" max="23" width="20.7109375" style="31" customWidth="1"/>
-    <col min="24" max="24" width="18.42578125" style="31" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="20.28515625" style="31" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15.5703125" style="31" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.28515625" style="31" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="20.6640625" style="31" bestFit="1" customWidth="1"/>
+    <col min="20" max="23" width="20.6640625" style="31" customWidth="1"/>
+    <col min="24" max="24" width="18.44140625" style="31" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="20.33203125" style="31" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15.5546875" style="31" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.33203125" style="31" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -2061,7 +2061,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="2" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="40" t="s">
         <v>3</v>
       </c>
@@ -2156,7 +2156,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="3" spans="1:31" ht="23.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" ht="23.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="41">
         <v>1</v>
       </c>
@@ -2251,7 +2251,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:31" ht="23.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" ht="23.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="41">
         <v>2</v>
       </c>
@@ -2346,7 +2346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:31" ht="23.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" ht="23.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="41">
         <v>3</v>
       </c>
@@ -2441,7 +2441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:31" ht="23.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" ht="23.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="41">
         <v>4</v>
       </c>
@@ -2537,7 +2537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" ht="23.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" ht="23.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="41"/>
       <c r="B7" s="70"/>
       <c r="C7" s="71"/>
@@ -2562,7 +2562,7 @@
       <c r="V7" s="46"/>
       <c r="W7" s="46"/>
     </row>
-    <row r="8" spans="1:31" ht="23.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" ht="23.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="41"/>
       <c r="B8" s="43"/>
       <c r="C8" s="45"/>
@@ -2587,7 +2587,7 @@
       <c r="V8" s="46"/>
       <c r="W8" s="46"/>
     </row>
-    <row r="9" spans="1:31" ht="23.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:31" ht="23.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="41"/>
       <c r="B9" s="43"/>
       <c r="C9" s="45"/>
@@ -2612,7 +2612,7 @@
       <c r="V9" s="46"/>
       <c r="W9" s="46"/>
     </row>
-    <row r="10" spans="1:31" ht="23.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:31" ht="23.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="58"/>
       <c r="B10" s="59"/>
       <c r="C10" s="60"/>
@@ -2637,7 +2637,7 @@
       <c r="V10" s="68"/>
       <c r="W10" s="68"/>
     </row>
-    <row r="11" spans="1:31" s="46" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:31" s="46" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="41"/>
       <c r="B11" s="43"/>
       <c r="C11" s="45"/>
@@ -2664,7 +2664,7 @@
       <c r="Z11" s="69"/>
       <c r="AA11" s="69"/>
     </row>
-    <row r="12" spans="1:31" s="46" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:31" s="46" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="41"/>
       <c r="B12" s="43"/>
       <c r="C12" s="45"/>
@@ -2691,7 +2691,7 @@
       <c r="Z12" s="69"/>
       <c r="AA12" s="69"/>
     </row>
-    <row r="13" spans="1:31" s="46" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:31" s="46" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="41"/>
       <c r="B13" s="43"/>
       <c r="C13" s="45"/>
@@ -2718,7 +2718,7 @@
       <c r="Z13" s="69"/>
       <c r="AA13" s="69"/>
     </row>
-    <row r="14" spans="1:31" s="46" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:31" s="46" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="41"/>
       <c r="B14" s="43"/>
       <c r="C14" s="45"/>
@@ -2745,9 +2745,9 @@
       <c r="Z14" s="69"/>
       <c r="AA14" s="69"/>
     </row>
-    <row r="15" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="17" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2757,13 +2757,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D86F6B0-26ED-4B02-B890-EDAFE42B3137}">
   <dimension ref="A1:G5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2786,7 +2786,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2809,7 +2809,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2829,10 +2829,10 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2852,10 +2852,10 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
@@ -2875,7 +2875,7 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>100</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -2886,15 +2886,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0351544-AA63-4F3E-855C-5CF465DCF681}">
   <dimension ref="A1:I3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2923,7 +2923,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2952,7 +2952,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2992,16 +2992,16 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:H346"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" style="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="13.5703125" style="18" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="29.28515625" style="17" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5703125" style="17" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" style="17" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="13.5546875" style="18" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" style="18" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="29.33203125" style="17" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5546875" style="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -3027,7 +3027,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>3</v>
       </c>
@@ -3053,7 +3053,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14">
         <v>0</v>
       </c>
@@ -3079,7 +3079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="16">
         <v>1</v>
       </c>
@@ -3105,7 +3105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="16">
         <v>2</v>
       </c>
@@ -3131,7 +3131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="16">
         <v>3</v>
       </c>
@@ -3157,7 +3157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="16">
         <v>4</v>
       </c>
@@ -3183,7 +3183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="16">
         <v>5</v>
       </c>
@@ -3209,7 +3209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="16">
         <v>6</v>
       </c>
@@ -3235,7 +3235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="16">
         <v>7</v>
       </c>
@@ -3261,7 +3261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="16">
         <v>8</v>
       </c>
@@ -3287,7 +3287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="16">
         <v>9</v>
       </c>
@@ -3313,7 +3313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="16">
         <v>10</v>
       </c>
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="16">
         <v>11</v>
       </c>
@@ -3365,7 +3365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="16">
         <v>12</v>
       </c>
@@ -3391,7 +3391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="16">
         <v>13</v>
       </c>
@@ -3417,7 +3417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="16">
         <v>14</v>
       </c>
@@ -3443,7 +3443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="16">
         <v>15</v>
       </c>
@@ -3469,7 +3469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="16">
         <v>16</v>
       </c>
@@ -3495,7 +3495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="16">
         <v>17</v>
       </c>
@@ -3521,7 +3521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="16">
         <v>18</v>
       </c>
@@ -3547,7 +3547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="16">
         <v>19</v>
       </c>
@@ -3573,7 +3573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="16">
         <v>20</v>
       </c>
@@ -3599,7 +3599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="16">
         <v>21</v>
       </c>
@@ -3625,7 +3625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="16">
         <v>22</v>
       </c>
@@ -3651,7 +3651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="16">
         <v>23</v>
       </c>
@@ -3677,7 +3677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="16">
         <v>24</v>
       </c>
@@ -3703,7 +3703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="16">
         <v>25</v>
       </c>
@@ -3729,7 +3729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="16">
         <v>26</v>
       </c>
@@ -3755,7 +3755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="16">
         <v>27</v>
       </c>
@@ -3781,7 +3781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="16">
         <v>28</v>
       </c>
@@ -3807,7 +3807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="16">
         <v>29</v>
       </c>
@@ -3833,7 +3833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="16">
         <v>30</v>
       </c>
@@ -3859,7 +3859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="16">
         <v>31</v>
       </c>
@@ -3885,7 +3885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="16">
         <v>32</v>
       </c>
@@ -3911,7 +3911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="16">
         <v>33</v>
       </c>
@@ -3937,7 +3937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="16">
         <v>34</v>
       </c>
@@ -3963,7 +3963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="16">
         <v>35</v>
       </c>
@@ -3989,7 +3989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="16">
         <v>36</v>
       </c>
@@ -4015,7 +4015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="16">
         <v>37</v>
       </c>
@@ -4041,7 +4041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="16">
         <v>38</v>
       </c>
@@ -4067,7 +4067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="16">
         <v>39</v>
       </c>
@@ -4093,7 +4093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="16"/>
       <c r="B43" s="15"/>
       <c r="C43" s="15"/>
@@ -4103,7 +4103,7 @@
       <c r="G43" s="16"/>
       <c r="H43" s="14"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="16"/>
       <c r="B44" s="15"/>
       <c r="C44" s="15"/>
@@ -4113,7 +4113,7 @@
       <c r="G44" s="16"/>
       <c r="H44" s="14"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="16"/>
       <c r="B45" s="15"/>
       <c r="C45" s="15"/>
@@ -4123,7 +4123,7 @@
       <c r="G45" s="16"/>
       <c r="H45" s="14"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="16"/>
       <c r="B46" s="15"/>
       <c r="C46" s="15"/>
@@ -4133,7 +4133,7 @@
       <c r="G46" s="16"/>
       <c r="H46" s="14"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="16"/>
       <c r="B47" s="15"/>
       <c r="C47" s="15"/>
@@ -4143,7 +4143,7 @@
       <c r="G47" s="16"/>
       <c r="H47" s="14"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="16"/>
       <c r="B48" s="15"/>
       <c r="C48" s="15"/>
@@ -4153,7 +4153,7 @@
       <c r="G48" s="16"/>
       <c r="H48" s="14"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="16"/>
       <c r="B49" s="15"/>
       <c r="C49" s="15"/>
@@ -4163,7 +4163,7 @@
       <c r="G49" s="16"/>
       <c r="H49" s="14"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="16"/>
       <c r="B50" s="15"/>
       <c r="C50" s="15"/>
@@ -4173,7 +4173,7 @@
       <c r="G50" s="16"/>
       <c r="H50" s="14"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="16"/>
       <c r="B51" s="15"/>
       <c r="C51" s="15"/>
@@ -4183,7 +4183,7 @@
       <c r="G51" s="16"/>
       <c r="H51" s="14"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="16"/>
       <c r="B52" s="15"/>
       <c r="C52" s="15"/>
@@ -4193,7 +4193,7 @@
       <c r="G52" s="16"/>
       <c r="H52" s="14"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="16"/>
       <c r="B53" s="15"/>
       <c r="C53" s="15"/>
@@ -4203,7 +4203,7 @@
       <c r="G53" s="16"/>
       <c r="H53" s="14"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="16"/>
       <c r="B54" s="15"/>
       <c r="C54" s="15"/>
@@ -4213,7 +4213,7 @@
       <c r="G54" s="16"/>
       <c r="H54" s="14"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" s="16"/>
       <c r="B55" s="15"/>
       <c r="C55" s="15"/>
@@ -4223,7 +4223,7 @@
       <c r="G55" s="16"/>
       <c r="H55" s="14"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="16"/>
       <c r="B56" s="15"/>
       <c r="C56" s="15"/>
@@ -4233,7 +4233,7 @@
       <c r="G56" s="16"/>
       <c r="H56" s="14"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="16"/>
       <c r="B57" s="15"/>
       <c r="C57" s="15"/>
@@ -4243,7 +4243,7 @@
       <c r="G57" s="16"/>
       <c r="H57" s="14"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="16"/>
       <c r="B58" s="15"/>
       <c r="C58" s="15"/>
@@ -4253,7 +4253,7 @@
       <c r="G58" s="16"/>
       <c r="H58" s="14"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="16"/>
       <c r="B59" s="15"/>
       <c r="C59" s="15"/>
@@ -4263,7 +4263,7 @@
       <c r="G59" s="16"/>
       <c r="H59" s="14"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="16"/>
       <c r="B60" s="15"/>
       <c r="C60" s="15"/>
@@ -4273,7 +4273,7 @@
       <c r="G60" s="16"/>
       <c r="H60" s="14"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="16"/>
       <c r="B61" s="15"/>
       <c r="C61" s="15"/>
@@ -4283,7 +4283,7 @@
       <c r="G61" s="16"/>
       <c r="H61" s="14"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="16"/>
       <c r="B62" s="15"/>
       <c r="C62" s="15"/>
@@ -4293,7 +4293,7 @@
       <c r="G62" s="16"/>
       <c r="H62" s="14"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="16"/>
       <c r="B63" s="15"/>
       <c r="C63" s="15"/>
@@ -4303,7 +4303,7 @@
       <c r="G63" s="16"/>
       <c r="H63" s="14"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="16"/>
       <c r="B64" s="15"/>
       <c r="C64" s="15"/>
@@ -4313,7 +4313,7 @@
       <c r="G64" s="16"/>
       <c r="H64" s="14"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="16"/>
       <c r="B65" s="15"/>
       <c r="C65" s="15"/>
@@ -4323,7 +4323,7 @@
       <c r="G65" s="16"/>
       <c r="H65" s="14"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" s="16"/>
       <c r="B66" s="15"/>
       <c r="C66" s="15"/>
@@ -4333,7 +4333,7 @@
       <c r="G66" s="16"/>
       <c r="H66" s="14"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" s="16"/>
       <c r="B67" s="15"/>
       <c r="C67" s="15"/>
@@ -4343,7 +4343,7 @@
       <c r="G67" s="16"/>
       <c r="H67" s="14"/>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" s="16"/>
       <c r="B68" s="15"/>
       <c r="C68" s="15"/>
@@ -4353,7 +4353,7 @@
       <c r="G68" s="16"/>
       <c r="H68" s="14"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" s="16"/>
       <c r="B69" s="15"/>
       <c r="C69" s="15"/>
@@ -4363,7 +4363,7 @@
       <c r="G69" s="16"/>
       <c r="H69" s="14"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="16"/>
       <c r="B70" s="15"/>
       <c r="C70" s="15"/>
@@ -4373,7 +4373,7 @@
       <c r="G70" s="16"/>
       <c r="H70" s="14"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" s="16"/>
       <c r="B71" s="15"/>
       <c r="C71" s="15"/>
@@ -4383,7 +4383,7 @@
       <c r="G71" s="16"/>
       <c r="H71" s="14"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" s="16"/>
       <c r="B72" s="15"/>
       <c r="C72" s="15"/>
@@ -4393,7 +4393,7 @@
       <c r="G72" s="16"/>
       <c r="H72" s="14"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" s="16"/>
       <c r="B73" s="15"/>
       <c r="C73" s="15"/>
@@ -4403,7 +4403,7 @@
       <c r="G73" s="16"/>
       <c r="H73" s="14"/>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" s="16"/>
       <c r="B74" s="15"/>
       <c r="C74" s="15"/>
@@ -4413,7 +4413,7 @@
       <c r="G74" s="16"/>
       <c r="H74" s="14"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" s="16"/>
       <c r="B75" s="15"/>
       <c r="C75" s="15"/>
@@ -4423,7 +4423,7 @@
       <c r="G75" s="16"/>
       <c r="H75" s="14"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" s="16"/>
       <c r="B76" s="15"/>
       <c r="C76" s="15"/>
@@ -4433,7 +4433,7 @@
       <c r="G76" s="16"/>
       <c r="H76" s="14"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" s="16"/>
       <c r="B77" s="15"/>
       <c r="C77" s="15"/>
@@ -4443,7 +4443,7 @@
       <c r="G77" s="16"/>
       <c r="H77" s="14"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" s="16"/>
       <c r="B78" s="15"/>
       <c r="C78" s="15"/>
@@ -4453,7 +4453,7 @@
       <c r="G78" s="16"/>
       <c r="H78" s="14"/>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" s="16"/>
       <c r="B79" s="15"/>
       <c r="C79" s="15"/>
@@ -4463,7 +4463,7 @@
       <c r="G79" s="16"/>
       <c r="H79" s="14"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" s="16"/>
       <c r="B80" s="15"/>
       <c r="C80" s="15"/>
@@ -4473,7 +4473,7 @@
       <c r="G80" s="16"/>
       <c r="H80" s="14"/>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="16"/>
       <c r="B81" s="15"/>
       <c r="C81" s="15"/>
@@ -4483,7 +4483,7 @@
       <c r="G81" s="16"/>
       <c r="H81" s="14"/>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="16"/>
       <c r="B82" s="15"/>
       <c r="C82" s="15"/>
@@ -4493,7 +4493,7 @@
       <c r="G82" s="16"/>
       <c r="H82" s="14"/>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="16"/>
       <c r="B83" s="15"/>
       <c r="C83" s="15"/>
@@ -4503,7 +4503,7 @@
       <c r="G83" s="16"/>
       <c r="H83" s="14"/>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="16"/>
       <c r="B84" s="15"/>
       <c r="C84" s="15"/>
@@ -4513,7 +4513,7 @@
       <c r="G84" s="16"/>
       <c r="H84" s="14"/>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" s="16"/>
       <c r="B85" s="15"/>
       <c r="C85" s="15"/>
@@ -4523,7 +4523,7 @@
       <c r="G85" s="16"/>
       <c r="H85" s="14"/>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" s="16"/>
       <c r="B86" s="15"/>
       <c r="C86" s="15"/>
@@ -4533,7 +4533,7 @@
       <c r="G86" s="16"/>
       <c r="H86" s="14"/>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" s="16"/>
       <c r="B87" s="15"/>
       <c r="C87" s="15"/>
@@ -4543,7 +4543,7 @@
       <c r="G87" s="16"/>
       <c r="H87" s="14"/>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" s="16"/>
       <c r="B88" s="15"/>
       <c r="C88" s="15"/>
@@ -4553,7 +4553,7 @@
       <c r="G88" s="16"/>
       <c r="H88" s="14"/>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" s="16"/>
       <c r="B89" s="15"/>
       <c r="C89" s="15"/>
@@ -4563,7 +4563,7 @@
       <c r="G89" s="16"/>
       <c r="H89" s="14"/>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" s="16"/>
       <c r="B90" s="15"/>
       <c r="C90" s="15"/>
@@ -4573,7 +4573,7 @@
       <c r="G90" s="16"/>
       <c r="H90" s="14"/>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" s="16"/>
       <c r="B91" s="15"/>
       <c r="C91" s="15"/>
@@ -4583,7 +4583,7 @@
       <c r="G91" s="16"/>
       <c r="H91" s="14"/>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" s="16"/>
       <c r="B92" s="15"/>
       <c r="C92" s="15"/>
@@ -4593,7 +4593,7 @@
       <c r="G92" s="16"/>
       <c r="H92" s="14"/>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" s="16"/>
       <c r="B93" s="15"/>
       <c r="C93" s="15"/>
@@ -4603,7 +4603,7 @@
       <c r="G93" s="16"/>
       <c r="H93" s="14"/>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" s="16"/>
       <c r="B94" s="15"/>
       <c r="C94" s="15"/>
@@ -4613,7 +4613,7 @@
       <c r="G94" s="16"/>
       <c r="H94" s="14"/>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" s="16"/>
       <c r="B95" s="15"/>
       <c r="C95" s="15"/>
@@ -4623,7 +4623,7 @@
       <c r="G95" s="16"/>
       <c r="H95" s="14"/>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" s="16"/>
       <c r="B96" s="15"/>
       <c r="C96" s="15"/>
@@ -4633,7 +4633,7 @@
       <c r="G96" s="16"/>
       <c r="H96" s="14"/>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" s="16"/>
       <c r="B97" s="15"/>
       <c r="C97" s="15"/>
@@ -4643,7 +4643,7 @@
       <c r="G97" s="16"/>
       <c r="H97" s="14"/>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" s="16"/>
       <c r="B98" s="15"/>
       <c r="C98" s="15"/>
@@ -4653,7 +4653,7 @@
       <c r="G98" s="16"/>
       <c r="H98" s="14"/>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" s="16"/>
       <c r="B99" s="15"/>
       <c r="C99" s="15"/>
@@ -4663,7 +4663,7 @@
       <c r="G99" s="16"/>
       <c r="H99" s="14"/>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" s="16"/>
       <c r="B100" s="15"/>
       <c r="C100" s="15"/>
@@ -4673,7 +4673,7 @@
       <c r="G100" s="16"/>
       <c r="H100" s="14"/>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" s="16"/>
       <c r="B101" s="15"/>
       <c r="C101" s="15"/>
@@ -4683,7 +4683,7 @@
       <c r="G101" s="16"/>
       <c r="H101" s="14"/>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" s="16"/>
       <c r="B102" s="15"/>
       <c r="C102" s="15"/>
@@ -4693,7 +4693,7 @@
       <c r="G102" s="16"/>
       <c r="H102" s="14"/>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" s="16"/>
       <c r="B103" s="15"/>
       <c r="C103" s="15"/>
@@ -4703,7 +4703,7 @@
       <c r="G103" s="16"/>
       <c r="H103" s="14"/>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" s="16"/>
       <c r="B104" s="15"/>
       <c r="C104" s="15"/>
@@ -4713,7 +4713,7 @@
       <c r="G104" s="16"/>
       <c r="H104" s="14"/>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" s="16"/>
       <c r="B105" s="15"/>
       <c r="C105" s="15"/>
@@ -4723,7 +4723,7 @@
       <c r="G105" s="16"/>
       <c r="H105" s="14"/>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" s="16"/>
       <c r="B106" s="15"/>
       <c r="C106" s="15"/>
@@ -4733,7 +4733,7 @@
       <c r="G106" s="16"/>
       <c r="H106" s="14"/>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" s="16"/>
       <c r="B107" s="15"/>
       <c r="C107" s="15"/>
@@ -4743,7 +4743,7 @@
       <c r="G107" s="16"/>
       <c r="H107" s="14"/>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" s="16"/>
       <c r="B108" s="15"/>
       <c r="C108" s="15"/>
@@ -4753,7 +4753,7 @@
       <c r="G108" s="16"/>
       <c r="H108" s="14"/>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" s="16"/>
       <c r="B109" s="15"/>
       <c r="C109" s="15"/>
@@ -4763,7 +4763,7 @@
       <c r="G109" s="16"/>
       <c r="H109" s="14"/>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" s="16"/>
       <c r="B110" s="15"/>
       <c r="C110" s="15"/>
@@ -4773,7 +4773,7 @@
       <c r="G110" s="16"/>
       <c r="H110" s="14"/>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" s="16"/>
       <c r="B111" s="15"/>
       <c r="C111" s="15"/>
@@ -4783,7 +4783,7 @@
       <c r="G111" s="16"/>
       <c r="H111" s="14"/>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" s="38"/>
       <c r="B112" s="15"/>
       <c r="C112" s="15"/>
@@ -4793,7 +4793,7 @@
       <c r="G112" s="16"/>
       <c r="H112" s="14"/>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" s="50"/>
       <c r="B113" s="15"/>
       <c r="C113" s="15"/>
@@ -4803,7 +4803,7 @@
       <c r="G113" s="16"/>
       <c r="H113" s="14"/>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" s="16"/>
       <c r="B114" s="15"/>
       <c r="C114" s="15"/>
@@ -4813,7 +4813,7 @@
       <c r="G114" s="56"/>
       <c r="H114" s="14"/>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" s="16"/>
       <c r="B115" s="15"/>
       <c r="C115" s="15"/>
@@ -4823,7 +4823,7 @@
       <c r="G115" s="56"/>
       <c r="H115" s="14"/>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" s="38"/>
       <c r="B116" s="15"/>
       <c r="C116" s="15"/>
@@ -4833,7 +4833,7 @@
       <c r="G116" s="56"/>
       <c r="H116" s="14"/>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" s="50"/>
       <c r="B117" s="15"/>
       <c r="C117" s="15"/>
@@ -4843,7 +4843,7 @@
       <c r="G117" s="56"/>
       <c r="H117" s="14"/>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" s="16"/>
       <c r="B118" s="15"/>
       <c r="C118" s="15"/>
@@ -4853,7 +4853,7 @@
       <c r="G118" s="56"/>
       <c r="H118" s="14"/>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" s="16"/>
       <c r="B119" s="15"/>
       <c r="C119" s="15"/>
@@ -4863,7 +4863,7 @@
       <c r="G119" s="56"/>
       <c r="H119" s="14"/>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" s="38"/>
       <c r="B120" s="15"/>
       <c r="C120" s="15"/>
@@ -4873,7 +4873,7 @@
       <c r="G120" s="56"/>
       <c r="H120" s="14"/>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" s="50"/>
       <c r="B121" s="15"/>
       <c r="C121" s="15"/>
@@ -4883,7 +4883,7 @@
       <c r="G121" s="56"/>
       <c r="H121" s="14"/>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" s="16"/>
       <c r="B122" s="15"/>
       <c r="C122" s="15"/>
@@ -4893,7 +4893,7 @@
       <c r="G122" s="56"/>
       <c r="H122" s="14"/>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" s="16"/>
       <c r="B123" s="15"/>
       <c r="C123" s="15"/>
@@ -4903,7 +4903,7 @@
       <c r="G123" s="56"/>
       <c r="H123" s="14"/>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" s="38"/>
       <c r="B124" s="15"/>
       <c r="C124" s="15"/>
@@ -4913,7 +4913,7 @@
       <c r="G124" s="56"/>
       <c r="H124" s="14"/>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" s="50"/>
       <c r="B125" s="15"/>
       <c r="C125" s="15"/>
@@ -4923,7 +4923,7 @@
       <c r="G125" s="56"/>
       <c r="H125" s="14"/>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" s="16"/>
       <c r="B126" s="15"/>
       <c r="C126" s="15"/>
@@ -4933,7 +4933,7 @@
       <c r="G126" s="56"/>
       <c r="H126" s="14"/>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127" s="16"/>
       <c r="B127" s="15"/>
       <c r="C127" s="15"/>
@@ -4943,7 +4943,7 @@
       <c r="G127" s="56"/>
       <c r="H127" s="14"/>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128" s="38"/>
       <c r="B128" s="15"/>
       <c r="C128" s="15"/>
@@ -4953,7 +4953,7 @@
       <c r="G128" s="56"/>
       <c r="H128" s="14"/>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129" s="50"/>
       <c r="B129" s="15"/>
       <c r="C129" s="15"/>
@@ -4963,7 +4963,7 @@
       <c r="G129" s="56"/>
       <c r="H129" s="14"/>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130" s="16"/>
       <c r="B130" s="15"/>
       <c r="C130" s="15"/>
@@ -4973,7 +4973,7 @@
       <c r="G130" s="56"/>
       <c r="H130" s="14"/>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A131" s="16"/>
       <c r="B131" s="15"/>
       <c r="C131" s="15"/>
@@ -4983,7 +4983,7 @@
       <c r="G131" s="56"/>
       <c r="H131" s="14"/>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132" s="38"/>
       <c r="B132" s="15"/>
       <c r="C132" s="15"/>
@@ -4993,7 +4993,7 @@
       <c r="G132" s="56"/>
       <c r="H132" s="14"/>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A133" s="50"/>
       <c r="B133" s="15"/>
       <c r="C133" s="15"/>
@@ -5003,7 +5003,7 @@
       <c r="G133" s="56"/>
       <c r="H133" s="14"/>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134" s="16"/>
       <c r="B134" s="15"/>
       <c r="C134" s="15"/>
@@ -5013,7 +5013,7 @@
       <c r="G134" s="56"/>
       <c r="H134" s="14"/>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135" s="16"/>
       <c r="B135" s="15"/>
       <c r="C135" s="15"/>
@@ -5023,7 +5023,7 @@
       <c r="G135" s="56"/>
       <c r="H135" s="14"/>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A136" s="38"/>
       <c r="B136" s="15"/>
       <c r="C136" s="15"/>
@@ -5033,7 +5033,7 @@
       <c r="G136" s="56"/>
       <c r="H136" s="14"/>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A137" s="50"/>
       <c r="B137" s="15"/>
       <c r="C137" s="15"/>
@@ -5043,7 +5043,7 @@
       <c r="G137" s="56"/>
       <c r="H137" s="14"/>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138" s="16"/>
       <c r="B138" s="15"/>
       <c r="C138" s="15"/>
@@ -5053,7 +5053,7 @@
       <c r="G138" s="56"/>
       <c r="H138" s="14"/>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A139" s="16"/>
       <c r="B139" s="15"/>
       <c r="C139" s="15"/>
@@ -5063,7 +5063,7 @@
       <c r="G139" s="56"/>
       <c r="H139" s="14"/>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140" s="38"/>
       <c r="B140" s="15"/>
       <c r="C140" s="15"/>
@@ -5073,7 +5073,7 @@
       <c r="G140" s="56"/>
       <c r="H140" s="14"/>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A141" s="50"/>
       <c r="B141" s="15"/>
       <c r="C141" s="15"/>
@@ -5083,7 +5083,7 @@
       <c r="G141" s="56"/>
       <c r="H141" s="14"/>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A142" s="16"/>
       <c r="B142" s="15"/>
       <c r="C142" s="15"/>
@@ -5093,7 +5093,7 @@
       <c r="G142" s="56"/>
       <c r="H142" s="14"/>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A143" s="16"/>
       <c r="B143" s="15"/>
       <c r="C143" s="15"/>
@@ -5103,7 +5103,7 @@
       <c r="G143" s="56"/>
       <c r="H143" s="14"/>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A144" s="38"/>
       <c r="B144" s="15"/>
       <c r="C144" s="15"/>
@@ -5113,7 +5113,7 @@
       <c r="G144" s="56"/>
       <c r="H144" s="14"/>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A145" s="50"/>
       <c r="B145" s="15"/>
       <c r="C145" s="15"/>
@@ -5123,7 +5123,7 @@
       <c r="G145" s="56"/>
       <c r="H145" s="14"/>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A146" s="16"/>
       <c r="B146" s="15"/>
       <c r="C146" s="15"/>
@@ -5133,7 +5133,7 @@
       <c r="G146" s="56"/>
       <c r="H146" s="14"/>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A147" s="16"/>
       <c r="B147" s="15"/>
       <c r="C147" s="15"/>
@@ -5143,7 +5143,7 @@
       <c r="G147" s="56"/>
       <c r="H147" s="14"/>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A148" s="38"/>
       <c r="B148" s="15"/>
       <c r="C148" s="15"/>
@@ -5153,7 +5153,7 @@
       <c r="G148" s="56"/>
       <c r="H148" s="14"/>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A149" s="50"/>
       <c r="B149" s="15"/>
       <c r="C149" s="15"/>
@@ -5163,7 +5163,7 @@
       <c r="G149" s="56"/>
       <c r="H149" s="14"/>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A150" s="16"/>
       <c r="B150" s="15"/>
       <c r="C150" s="15"/>
@@ -5173,7 +5173,7 @@
       <c r="G150" s="56"/>
       <c r="H150" s="14"/>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A151" s="16"/>
       <c r="B151" s="15"/>
       <c r="C151" s="15"/>
@@ -5183,7 +5183,7 @@
       <c r="G151" s="56"/>
       <c r="H151" s="14"/>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A152" s="38"/>
       <c r="B152" s="15"/>
       <c r="C152" s="15"/>
@@ -5193,7 +5193,7 @@
       <c r="G152" s="56"/>
       <c r="H152" s="14"/>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A153" s="50"/>
       <c r="B153" s="15"/>
       <c r="C153" s="15"/>
@@ -5203,7 +5203,7 @@
       <c r="G153" s="56"/>
       <c r="H153" s="14"/>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A154" s="16"/>
       <c r="B154" s="15"/>
       <c r="C154" s="15"/>
@@ -5213,7 +5213,7 @@
       <c r="G154" s="56"/>
       <c r="H154" s="14"/>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A155" s="16"/>
       <c r="B155" s="15"/>
       <c r="C155" s="15"/>
@@ -5223,7 +5223,7 @@
       <c r="G155" s="56"/>
       <c r="H155" s="14"/>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A156" s="38"/>
       <c r="B156" s="15"/>
       <c r="C156" s="15"/>
@@ -5233,7 +5233,7 @@
       <c r="G156" s="56"/>
       <c r="H156" s="14"/>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A157" s="50"/>
       <c r="B157" s="15"/>
       <c r="C157" s="15"/>
@@ -5243,7 +5243,7 @@
       <c r="G157" s="56"/>
       <c r="H157" s="14"/>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A158" s="16"/>
       <c r="B158" s="15"/>
       <c r="C158" s="15"/>
@@ -5253,7 +5253,7 @@
       <c r="G158" s="56"/>
       <c r="H158" s="14"/>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A159" s="16"/>
       <c r="B159" s="15"/>
       <c r="C159" s="15"/>
@@ -5263,7 +5263,7 @@
       <c r="G159" s="56"/>
       <c r="H159" s="14"/>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A160" s="38"/>
       <c r="B160" s="15"/>
       <c r="C160" s="15"/>
@@ -5273,7 +5273,7 @@
       <c r="G160" s="56"/>
       <c r="H160" s="14"/>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A161" s="50"/>
       <c r="B161" s="15"/>
       <c r="C161" s="15"/>
@@ -5283,7 +5283,7 @@
       <c r="G161" s="56"/>
       <c r="H161" s="14"/>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A162" s="16"/>
       <c r="B162" s="15"/>
       <c r="C162" s="15"/>
@@ -5293,7 +5293,7 @@
       <c r="G162" s="56"/>
       <c r="H162" s="14"/>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A163" s="16"/>
       <c r="B163" s="15"/>
       <c r="C163" s="15"/>
@@ -5303,7 +5303,7 @@
       <c r="G163" s="56"/>
       <c r="H163" s="14"/>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A164" s="38"/>
       <c r="B164" s="15"/>
       <c r="C164" s="15"/>
@@ -5313,7 +5313,7 @@
       <c r="G164" s="56"/>
       <c r="H164" s="14"/>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A165" s="50"/>
       <c r="B165" s="15"/>
       <c r="C165" s="15"/>
@@ -5323,7 +5323,7 @@
       <c r="G165" s="56"/>
       <c r="H165" s="14"/>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A166" s="16"/>
       <c r="B166" s="15"/>
       <c r="C166" s="15"/>
@@ -5333,7 +5333,7 @@
       <c r="G166" s="56"/>
       <c r="H166" s="14"/>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A167" s="16"/>
       <c r="B167" s="15"/>
       <c r="C167" s="15"/>
@@ -5343,7 +5343,7 @@
       <c r="G167" s="56"/>
       <c r="H167" s="14"/>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A168" s="38"/>
       <c r="B168" s="15"/>
       <c r="C168" s="15"/>
@@ -5353,7 +5353,7 @@
       <c r="G168" s="56"/>
       <c r="H168" s="14"/>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A169" s="50"/>
       <c r="B169" s="15"/>
       <c r="C169" s="15"/>
@@ -5363,7 +5363,7 @@
       <c r="G169" s="56"/>
       <c r="H169" s="14"/>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A170" s="16"/>
       <c r="B170" s="15"/>
       <c r="C170" s="15"/>
@@ -5373,7 +5373,7 @@
       <c r="G170" s="56"/>
       <c r="H170" s="14"/>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A171" s="16"/>
       <c r="B171" s="15"/>
       <c r="C171" s="15"/>
@@ -5383,7 +5383,7 @@
       <c r="G171" s="56"/>
       <c r="H171" s="14"/>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A172" s="38"/>
       <c r="B172" s="15"/>
       <c r="C172" s="15"/>
@@ -5393,7 +5393,7 @@
       <c r="G172" s="56"/>
       <c r="H172" s="14"/>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A173" s="50"/>
       <c r="B173" s="15"/>
       <c r="C173" s="15"/>
@@ -5403,7 +5403,7 @@
       <c r="G173" s="56"/>
       <c r="H173" s="14"/>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A174" s="16"/>
       <c r="B174" s="15"/>
       <c r="C174" s="15"/>
@@ -5413,7 +5413,7 @@
       <c r="G174" s="56"/>
       <c r="H174" s="14"/>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A175" s="16"/>
       <c r="B175" s="15"/>
       <c r="C175" s="15"/>
@@ -5423,7 +5423,7 @@
       <c r="G175" s="56"/>
       <c r="H175" s="14"/>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A176" s="38"/>
       <c r="B176" s="15"/>
       <c r="C176" s="15"/>
@@ -5433,7 +5433,7 @@
       <c r="G176" s="56"/>
       <c r="H176" s="14"/>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A177" s="50"/>
       <c r="B177" s="15"/>
       <c r="C177" s="15"/>
@@ -5443,7 +5443,7 @@
       <c r="G177" s="56"/>
       <c r="H177" s="14"/>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A178" s="16"/>
       <c r="B178" s="15"/>
       <c r="C178" s="15"/>
@@ -5453,7 +5453,7 @@
       <c r="G178" s="56"/>
       <c r="H178" s="14"/>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A179" s="16"/>
       <c r="B179" s="15"/>
       <c r="C179" s="15"/>
@@ -5463,7 +5463,7 @@
       <c r="G179" s="56"/>
       <c r="H179" s="14"/>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A180" s="38"/>
       <c r="B180" s="15"/>
       <c r="C180" s="15"/>
@@ -5473,7 +5473,7 @@
       <c r="G180" s="56"/>
       <c r="H180" s="14"/>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A181" s="50"/>
       <c r="B181" s="15"/>
       <c r="C181" s="15"/>
@@ -5483,7 +5483,7 @@
       <c r="G181" s="56"/>
       <c r="H181" s="14"/>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A182" s="16"/>
       <c r="B182" s="15"/>
       <c r="C182" s="15"/>
@@ -5493,7 +5493,7 @@
       <c r="G182" s="56"/>
       <c r="H182" s="14"/>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A183" s="16"/>
       <c r="B183" s="15"/>
       <c r="C183" s="15"/>
@@ -5503,7 +5503,7 @@
       <c r="G183" s="56"/>
       <c r="H183" s="14"/>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A184" s="38"/>
       <c r="B184" s="15"/>
       <c r="C184" s="15"/>
@@ -5513,7 +5513,7 @@
       <c r="G184" s="56"/>
       <c r="H184" s="14"/>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A185" s="50"/>
       <c r="B185" s="15"/>
       <c r="C185" s="15"/>
@@ -5523,7 +5523,7 @@
       <c r="G185" s="56"/>
       <c r="H185" s="14"/>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A186" s="16"/>
       <c r="B186" s="15"/>
       <c r="C186" s="15"/>
@@ -5533,7 +5533,7 @@
       <c r="G186" s="56"/>
       <c r="H186" s="14"/>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A187" s="16"/>
       <c r="B187" s="15"/>
       <c r="C187" s="15"/>
@@ -5543,7 +5543,7 @@
       <c r="G187" s="56"/>
       <c r="H187" s="14"/>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A188" s="38"/>
       <c r="B188" s="15"/>
       <c r="C188" s="15"/>
@@ -5553,7 +5553,7 @@
       <c r="G188" s="56"/>
       <c r="H188" s="14"/>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A189" s="50"/>
       <c r="B189" s="15"/>
       <c r="C189" s="15"/>
@@ -5563,7 +5563,7 @@
       <c r="G189" s="56"/>
       <c r="H189" s="14"/>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A190" s="16"/>
       <c r="B190" s="15"/>
       <c r="C190" s="15"/>
@@ -5573,7 +5573,7 @@
       <c r="G190" s="56"/>
       <c r="H190" s="14"/>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A191" s="16"/>
       <c r="B191" s="15"/>
       <c r="C191" s="15"/>
@@ -5583,7 +5583,7 @@
       <c r="G191" s="56"/>
       <c r="H191" s="14"/>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A192" s="38"/>
       <c r="B192" s="15"/>
       <c r="C192" s="15"/>
@@ -5593,7 +5593,7 @@
       <c r="G192" s="56"/>
       <c r="H192" s="14"/>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A193" s="50"/>
       <c r="B193" s="15"/>
       <c r="C193" s="15"/>
@@ -5603,7 +5603,7 @@
       <c r="G193" s="56"/>
       <c r="H193" s="14"/>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A194" s="16"/>
       <c r="B194" s="15"/>
       <c r="C194" s="15"/>
@@ -5613,7 +5613,7 @@
       <c r="G194" s="56"/>
       <c r="H194" s="14"/>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A195" s="16"/>
       <c r="B195" s="15"/>
       <c r="C195" s="15"/>
@@ -5623,7 +5623,7 @@
       <c r="G195" s="56"/>
       <c r="H195" s="14"/>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A196" s="38"/>
       <c r="B196" s="15"/>
       <c r="C196" s="15"/>
@@ -5633,7 +5633,7 @@
       <c r="G196" s="56"/>
       <c r="H196" s="14"/>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A197" s="50"/>
       <c r="B197" s="15"/>
       <c r="C197" s="15"/>
@@ -5643,7 +5643,7 @@
       <c r="G197" s="56"/>
       <c r="H197" s="14"/>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A198" s="16"/>
       <c r="B198" s="15"/>
       <c r="C198" s="15"/>
@@ -5653,7 +5653,7 @@
       <c r="G198" s="56"/>
       <c r="H198" s="14"/>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A199" s="16"/>
       <c r="B199" s="15"/>
       <c r="C199" s="15"/>
@@ -5663,7 +5663,7 @@
       <c r="G199" s="56"/>
       <c r="H199" s="14"/>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A200" s="38"/>
       <c r="B200" s="15"/>
       <c r="C200" s="15"/>
@@ -5673,7 +5673,7 @@
       <c r="G200" s="56"/>
       <c r="H200" s="14"/>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A201" s="50"/>
       <c r="B201" s="15"/>
       <c r="C201" s="15"/>
@@ -5683,7 +5683,7 @@
       <c r="G201" s="56"/>
       <c r="H201" s="14"/>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A202" s="16"/>
       <c r="B202" s="15"/>
       <c r="C202" s="15"/>
@@ -5693,7 +5693,7 @@
       <c r="G202" s="56"/>
       <c r="H202" s="14"/>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A203" s="16"/>
       <c r="B203" s="15"/>
       <c r="C203" s="15"/>
@@ -5703,7 +5703,7 @@
       <c r="G203" s="56"/>
       <c r="H203" s="14"/>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A204" s="38"/>
       <c r="B204" s="15"/>
       <c r="C204" s="15"/>
@@ -5713,7 +5713,7 @@
       <c r="G204" s="56"/>
       <c r="H204" s="14"/>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A205" s="50"/>
       <c r="B205" s="15"/>
       <c r="C205" s="15"/>
@@ -5723,7 +5723,7 @@
       <c r="G205" s="56"/>
       <c r="H205" s="14"/>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A206" s="16"/>
       <c r="B206" s="15"/>
       <c r="C206" s="15"/>
@@ -5733,7 +5733,7 @@
       <c r="G206" s="56"/>
       <c r="H206" s="14"/>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A207" s="16"/>
       <c r="B207" s="15"/>
       <c r="C207" s="15"/>
@@ -5743,7 +5743,7 @@
       <c r="G207" s="56"/>
       <c r="H207" s="14"/>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A208" s="38"/>
       <c r="B208" s="15"/>
       <c r="C208" s="15"/>
@@ -5753,7 +5753,7 @@
       <c r="G208" s="56"/>
       <c r="H208" s="14"/>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A209" s="50"/>
       <c r="B209" s="15"/>
       <c r="C209" s="15"/>
@@ -5763,7 +5763,7 @@
       <c r="G209" s="56"/>
       <c r="H209" s="14"/>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A210" s="16"/>
       <c r="B210" s="15"/>
       <c r="C210" s="15"/>
@@ -5773,7 +5773,7 @@
       <c r="G210" s="56"/>
       <c r="H210" s="14"/>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A211" s="16"/>
       <c r="B211" s="15"/>
       <c r="C211" s="15"/>
@@ -5783,7 +5783,7 @@
       <c r="G211" s="56"/>
       <c r="H211" s="14"/>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A212" s="38"/>
       <c r="B212" s="15"/>
       <c r="C212" s="15"/>
@@ -5793,7 +5793,7 @@
       <c r="G212" s="56"/>
       <c r="H212" s="14"/>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A213" s="50"/>
       <c r="B213" s="15"/>
       <c r="C213" s="15"/>
@@ -5803,7 +5803,7 @@
       <c r="G213" s="56"/>
       <c r="H213" s="14"/>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A214" s="16"/>
       <c r="B214" s="15"/>
       <c r="C214" s="15"/>
@@ -5813,7 +5813,7 @@
       <c r="G214" s="56"/>
       <c r="H214" s="14"/>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A215" s="16"/>
       <c r="B215" s="15"/>
       <c r="C215" s="15"/>
@@ -5823,7 +5823,7 @@
       <c r="G215" s="56"/>
       <c r="H215" s="14"/>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A216" s="38"/>
       <c r="B216" s="15"/>
       <c r="C216" s="15"/>
@@ -5833,7 +5833,7 @@
       <c r="G216" s="56"/>
       <c r="H216" s="14"/>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A217" s="50"/>
       <c r="B217" s="15"/>
       <c r="C217" s="15"/>
@@ -5843,7 +5843,7 @@
       <c r="G217" s="56"/>
       <c r="H217" s="14"/>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A218" s="16"/>
       <c r="B218" s="15"/>
       <c r="C218" s="15"/>
@@ -5853,7 +5853,7 @@
       <c r="G218" s="56"/>
       <c r="H218" s="14"/>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A219" s="16"/>
       <c r="B219" s="15"/>
       <c r="C219" s="15"/>
@@ -5863,7 +5863,7 @@
       <c r="G219" s="56"/>
       <c r="H219" s="14"/>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A220" s="38"/>
       <c r="B220" s="15"/>
       <c r="C220" s="15"/>
@@ -5873,7 +5873,7 @@
       <c r="G220" s="56"/>
       <c r="H220" s="14"/>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A221" s="50"/>
       <c r="B221" s="15"/>
       <c r="C221" s="15"/>
@@ -5883,7 +5883,7 @@
       <c r="G221" s="56"/>
       <c r="H221" s="14"/>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A222" s="16"/>
       <c r="B222" s="15"/>
       <c r="C222" s="15"/>
@@ -5893,7 +5893,7 @@
       <c r="G222" s="56"/>
       <c r="H222" s="14"/>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A223" s="16"/>
       <c r="B223" s="15"/>
       <c r="C223" s="15"/>
@@ -5903,7 +5903,7 @@
       <c r="G223" s="56"/>
       <c r="H223" s="14"/>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A224" s="38"/>
       <c r="B224" s="15"/>
       <c r="C224" s="15"/>
@@ -5913,7 +5913,7 @@
       <c r="G224" s="56"/>
       <c r="H224" s="14"/>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A225" s="50"/>
       <c r="B225" s="15"/>
       <c r="C225" s="15"/>
@@ -5923,7 +5923,7 @@
       <c r="G225" s="56"/>
       <c r="H225" s="14"/>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A226" s="16"/>
       <c r="B226" s="15"/>
       <c r="C226" s="15"/>
@@ -5933,7 +5933,7 @@
       <c r="G226" s="56"/>
       <c r="H226" s="14"/>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A227" s="16"/>
       <c r="B227" s="15"/>
       <c r="C227" s="15"/>
@@ -5943,7 +5943,7 @@
       <c r="G227" s="56"/>
       <c r="H227" s="14"/>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A228" s="38"/>
       <c r="B228" s="15"/>
       <c r="C228" s="15"/>
@@ -5953,7 +5953,7 @@
       <c r="G228" s="56"/>
       <c r="H228" s="14"/>
     </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A229" s="50"/>
       <c r="B229" s="15"/>
       <c r="C229" s="15"/>
@@ -5963,7 +5963,7 @@
       <c r="G229" s="56"/>
       <c r="H229" s="14"/>
     </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A230" s="16"/>
       <c r="B230" s="15"/>
       <c r="C230" s="15"/>
@@ -5973,7 +5973,7 @@
       <c r="G230" s="56"/>
       <c r="H230" s="14"/>
     </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A231" s="16"/>
       <c r="B231" s="15"/>
       <c r="C231" s="15"/>
@@ -5981,7 +5981,7 @@
       <c r="G231" s="56"/>
       <c r="H231" s="14"/>
     </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A232" s="16"/>
       <c r="B232" s="15"/>
       <c r="C232" s="15"/>
@@ -5989,7 +5989,7 @@
       <c r="G232" s="56"/>
       <c r="H232" s="14"/>
     </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A233" s="38"/>
       <c r="B233" s="15"/>
       <c r="C233" s="15"/>
@@ -5997,7 +5997,7 @@
       <c r="G233" s="56"/>
       <c r="H233" s="14"/>
     </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A234" s="50"/>
       <c r="B234" s="15"/>
       <c r="C234" s="15"/>
@@ -6005,7 +6005,7 @@
       <c r="G234" s="56"/>
       <c r="H234" s="14"/>
     </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A235" s="16"/>
       <c r="B235" s="15"/>
       <c r="C235" s="15"/>
@@ -6013,7 +6013,7 @@
       <c r="G235" s="56"/>
       <c r="H235" s="14"/>
     </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A236" s="16"/>
       <c r="B236" s="15"/>
       <c r="C236" s="15"/>
@@ -6021,7 +6021,7 @@
       <c r="G236" s="56"/>
       <c r="H236" s="14"/>
     </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A237" s="16"/>
       <c r="B237" s="15"/>
       <c r="C237" s="15"/>
@@ -6029,7 +6029,7 @@
       <c r="G237" s="56"/>
       <c r="H237" s="14"/>
     </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A238" s="38"/>
       <c r="B238" s="15"/>
       <c r="C238" s="15"/>
@@ -6037,7 +6037,7 @@
       <c r="G238" s="56"/>
       <c r="H238" s="14"/>
     </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A239" s="50"/>
       <c r="B239" s="15"/>
       <c r="C239" s="15"/>
@@ -6045,7 +6045,7 @@
       <c r="G239" s="56"/>
       <c r="H239" s="14"/>
     </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A240" s="16"/>
       <c r="B240" s="15"/>
       <c r="C240" s="15"/>
@@ -6053,7 +6053,7 @@
       <c r="G240" s="56"/>
       <c r="H240" s="14"/>
     </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A241" s="16"/>
       <c r="B241" s="15"/>
       <c r="C241" s="15"/>
@@ -6061,7 +6061,7 @@
       <c r="G241" s="56"/>
       <c r="H241" s="14"/>
     </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A242" s="16"/>
       <c r="B242" s="15"/>
       <c r="C242" s="15"/>
@@ -6069,7 +6069,7 @@
       <c r="G242" s="56"/>
       <c r="H242" s="14"/>
     </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A243" s="38"/>
       <c r="B243" s="15"/>
       <c r="C243" s="15"/>
@@ -6077,7 +6077,7 @@
       <c r="G243" s="56"/>
       <c r="H243" s="14"/>
     </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A244" s="50"/>
       <c r="B244" s="15"/>
       <c r="C244" s="15"/>
@@ -6085,7 +6085,7 @@
       <c r="G244" s="56"/>
       <c r="H244" s="14"/>
     </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A245" s="16"/>
       <c r="B245" s="15"/>
       <c r="C245" s="15"/>
@@ -6093,7 +6093,7 @@
       <c r="G245" s="56"/>
       <c r="H245" s="14"/>
     </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A246" s="16"/>
       <c r="B246" s="15"/>
       <c r="C246" s="15"/>
@@ -6101,7 +6101,7 @@
       <c r="G246" s="56"/>
       <c r="H246" s="14"/>
     </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A247" s="16"/>
       <c r="B247" s="15"/>
       <c r="C247" s="15"/>
@@ -6109,7 +6109,7 @@
       <c r="G247" s="56"/>
       <c r="H247" s="14"/>
     </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A248" s="38"/>
       <c r="B248" s="15"/>
       <c r="C248" s="15"/>
@@ -6117,7 +6117,7 @@
       <c r="G248" s="56"/>
       <c r="H248" s="14"/>
     </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A249" s="50"/>
       <c r="B249" s="15"/>
       <c r="C249" s="15"/>
@@ -6125,7 +6125,7 @@
       <c r="G249" s="56"/>
       <c r="H249" s="14"/>
     </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A250" s="16"/>
       <c r="B250" s="15"/>
       <c r="C250" s="15"/>
@@ -6133,7 +6133,7 @@
       <c r="G250" s="56"/>
       <c r="H250" s="14"/>
     </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A251" s="16"/>
       <c r="B251" s="15"/>
       <c r="C251" s="15"/>
@@ -6141,7 +6141,7 @@
       <c r="G251" s="56"/>
       <c r="H251" s="14"/>
     </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A252" s="16"/>
       <c r="B252" s="15"/>
       <c r="C252" s="15"/>
@@ -6149,7 +6149,7 @@
       <c r="G252" s="56"/>
       <c r="H252" s="14"/>
     </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A253" s="38"/>
       <c r="B253" s="15"/>
       <c r="C253" s="15"/>
@@ -6157,7 +6157,7 @@
       <c r="G253" s="56"/>
       <c r="H253" s="14"/>
     </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A254" s="50"/>
       <c r="B254" s="15"/>
       <c r="C254" s="15"/>
@@ -6165,7 +6165,7 @@
       <c r="G254" s="56"/>
       <c r="H254" s="14"/>
     </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A255" s="16"/>
       <c r="B255" s="15"/>
       <c r="C255" s="15"/>
@@ -6173,7 +6173,7 @@
       <c r="G255" s="56"/>
       <c r="H255" s="14"/>
     </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A256" s="16"/>
       <c r="B256" s="15"/>
       <c r="C256" s="15"/>
@@ -6181,7 +6181,7 @@
       <c r="G256" s="56"/>
       <c r="H256" s="14"/>
     </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A257" s="16"/>
       <c r="B257" s="15"/>
       <c r="C257" s="15"/>
@@ -6189,7 +6189,7 @@
       <c r="G257" s="56"/>
       <c r="H257" s="14"/>
     </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A258" s="38"/>
       <c r="B258" s="15"/>
       <c r="C258" s="15"/>
@@ -6197,7 +6197,7 @@
       <c r="G258" s="56"/>
       <c r="H258" s="14"/>
     </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A259" s="50"/>
       <c r="B259" s="15"/>
       <c r="C259" s="15"/>
@@ -6205,7 +6205,7 @@
       <c r="G259" s="56"/>
       <c r="H259" s="14"/>
     </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A260" s="16"/>
       <c r="B260" s="15"/>
       <c r="C260" s="15"/>
@@ -6213,7 +6213,7 @@
       <c r="G260" s="56"/>
       <c r="H260" s="14"/>
     </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A261" s="16"/>
       <c r="B261" s="15"/>
       <c r="C261" s="15"/>
@@ -6221,7 +6221,7 @@
       <c r="G261" s="56"/>
       <c r="H261" s="14"/>
     </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A262" s="16"/>
       <c r="B262" s="15"/>
       <c r="C262" s="15"/>
@@ -6229,7 +6229,7 @@
       <c r="G262" s="56"/>
       <c r="H262" s="14"/>
     </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A263" s="38"/>
       <c r="B263" s="15"/>
       <c r="C263" s="15"/>
@@ -6237,7 +6237,7 @@
       <c r="G263" s="56"/>
       <c r="H263" s="14"/>
     </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A264" s="50"/>
       <c r="B264" s="15"/>
       <c r="C264" s="15"/>
@@ -6245,7 +6245,7 @@
       <c r="G264" s="56"/>
       <c r="H264" s="14"/>
     </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A265" s="16"/>
       <c r="B265" s="15"/>
       <c r="C265" s="15"/>
@@ -6253,7 +6253,7 @@
       <c r="G265" s="56"/>
       <c r="H265" s="14"/>
     </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A266" s="16"/>
       <c r="B266" s="15"/>
       <c r="C266" s="15"/>
@@ -6261,7 +6261,7 @@
       <c r="G266" s="56"/>
       <c r="H266" s="14"/>
     </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A267" s="16"/>
       <c r="B267" s="15"/>
       <c r="C267" s="15"/>
@@ -6269,7 +6269,7 @@
       <c r="G267" s="56"/>
       <c r="H267" s="14"/>
     </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A268" s="38"/>
       <c r="B268" s="15"/>
       <c r="C268" s="15"/>
@@ -6277,7 +6277,7 @@
       <c r="G268" s="56"/>
       <c r="H268" s="14"/>
     </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A269" s="50"/>
       <c r="B269" s="15"/>
       <c r="C269" s="15"/>
@@ -6285,7 +6285,7 @@
       <c r="G269" s="56"/>
       <c r="H269" s="14"/>
     </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A270" s="16"/>
       <c r="B270" s="15"/>
       <c r="C270" s="15"/>
@@ -6293,7 +6293,7 @@
       <c r="G270" s="56"/>
       <c r="H270" s="14"/>
     </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A271" s="16"/>
       <c r="B271" s="15"/>
       <c r="C271" s="15"/>
@@ -6301,7 +6301,7 @@
       <c r="G271" s="56"/>
       <c r="H271" s="14"/>
     </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A272" s="16"/>
       <c r="B272" s="15"/>
       <c r="C272" s="15"/>
@@ -6309,7 +6309,7 @@
       <c r="G272" s="56"/>
       <c r="H272" s="14"/>
     </row>
-    <row r="273" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A273" s="38"/>
       <c r="B273" s="15"/>
       <c r="C273" s="15"/>
@@ -6317,7 +6317,7 @@
       <c r="G273" s="56"/>
       <c r="H273" s="14"/>
     </row>
-    <row r="274" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A274" s="50"/>
       <c r="B274" s="15"/>
       <c r="C274" s="15"/>
@@ -6325,7 +6325,7 @@
       <c r="G274" s="56"/>
       <c r="H274" s="14"/>
     </row>
-    <row r="275" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A275" s="16"/>
       <c r="B275" s="15"/>
       <c r="C275" s="15"/>
@@ -6333,7 +6333,7 @@
       <c r="G275" s="56"/>
       <c r="H275" s="14"/>
     </row>
-    <row r="276" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A276" s="16"/>
       <c r="B276" s="15"/>
       <c r="C276" s="15"/>
@@ -6341,7 +6341,7 @@
       <c r="G276" s="56"/>
       <c r="H276" s="14"/>
     </row>
-    <row r="277" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A277" s="16"/>
       <c r="B277" s="15"/>
       <c r="C277" s="15"/>
@@ -6349,7 +6349,7 @@
       <c r="G277" s="56"/>
       <c r="H277" s="14"/>
     </row>
-    <row r="278" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A278" s="38"/>
       <c r="B278" s="15"/>
       <c r="C278" s="15"/>
@@ -6357,7 +6357,7 @@
       <c r="G278" s="56"/>
       <c r="H278" s="14"/>
     </row>
-    <row r="279" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A279" s="50"/>
       <c r="B279" s="15"/>
       <c r="C279" s="15"/>
@@ -6365,7 +6365,7 @@
       <c r="G279" s="56"/>
       <c r="H279" s="14"/>
     </row>
-    <row r="280" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A280" s="16"/>
       <c r="B280" s="15"/>
       <c r="C280" s="15"/>
@@ -6373,7 +6373,7 @@
       <c r="G280" s="56"/>
       <c r="H280" s="14"/>
     </row>
-    <row r="281" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A281" s="16"/>
       <c r="B281" s="15"/>
       <c r="C281" s="15"/>
@@ -6381,7 +6381,7 @@
       <c r="G281" s="56"/>
       <c r="H281" s="14"/>
     </row>
-    <row r="282" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A282" s="16"/>
       <c r="B282" s="15"/>
       <c r="C282" s="15"/>
@@ -6389,7 +6389,7 @@
       <c r="G282" s="56"/>
       <c r="H282" s="14"/>
     </row>
-    <row r="283" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A283" s="38"/>
       <c r="B283" s="15"/>
       <c r="C283" s="15"/>
@@ -6397,7 +6397,7 @@
       <c r="G283" s="56"/>
       <c r="H283" s="14"/>
     </row>
-    <row r="284" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A284" s="50"/>
       <c r="B284" s="15"/>
       <c r="C284" s="15"/>
@@ -6405,7 +6405,7 @@
       <c r="G284" s="56"/>
       <c r="H284" s="14"/>
     </row>
-    <row r="285" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A285" s="16"/>
       <c r="B285" s="15"/>
       <c r="C285" s="15"/>
@@ -6413,7 +6413,7 @@
       <c r="G285" s="56"/>
       <c r="H285" s="14"/>
     </row>
-    <row r="286" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A286" s="16"/>
       <c r="B286" s="15"/>
       <c r="C286" s="15"/>
@@ -6421,7 +6421,7 @@
       <c r="G286" s="56"/>
       <c r="H286" s="14"/>
     </row>
-    <row r="287" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A287" s="16"/>
       <c r="B287" s="15"/>
       <c r="C287" s="15"/>
@@ -6429,7 +6429,7 @@
       <c r="G287" s="56"/>
       <c r="H287" s="14"/>
     </row>
-    <row r="288" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A288" s="38"/>
       <c r="B288" s="15"/>
       <c r="C288" s="15"/>
@@ -6437,7 +6437,7 @@
       <c r="G288" s="56"/>
       <c r="H288" s="14"/>
     </row>
-    <row r="289" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A289" s="50"/>
       <c r="B289" s="15"/>
       <c r="C289" s="15"/>
@@ -6445,7 +6445,7 @@
       <c r="G289" s="56"/>
       <c r="H289" s="14"/>
     </row>
-    <row r="290" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A290" s="16"/>
       <c r="B290" s="15"/>
       <c r="C290" s="15"/>
@@ -6453,7 +6453,7 @@
       <c r="G290" s="56"/>
       <c r="H290" s="14"/>
     </row>
-    <row r="291" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A291" s="16"/>
       <c r="B291" s="15"/>
       <c r="C291" s="15"/>
@@ -6461,7 +6461,7 @@
       <c r="G291" s="56"/>
       <c r="H291" s="14"/>
     </row>
-    <row r="292" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A292" s="16"/>
       <c r="B292" s="15"/>
       <c r="C292" s="15"/>
@@ -6469,7 +6469,7 @@
       <c r="G292" s="56"/>
       <c r="H292" s="14"/>
     </row>
-    <row r="293" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A293" s="38"/>
       <c r="B293" s="15"/>
       <c r="C293" s="15"/>
@@ -6477,7 +6477,7 @@
       <c r="G293" s="56"/>
       <c r="H293" s="14"/>
     </row>
-    <row r="294" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A294" s="50"/>
       <c r="B294" s="15"/>
       <c r="C294" s="15"/>
@@ -6485,7 +6485,7 @@
       <c r="G294" s="56"/>
       <c r="H294" s="14"/>
     </row>
-    <row r="295" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A295" s="16"/>
       <c r="B295" s="15"/>
       <c r="C295" s="15"/>
@@ -6493,7 +6493,7 @@
       <c r="G295" s="56"/>
       <c r="H295" s="14"/>
     </row>
-    <row r="296" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A296" s="16"/>
       <c r="B296" s="15"/>
       <c r="C296" s="15"/>
@@ -6501,7 +6501,7 @@
       <c r="G296" s="56"/>
       <c r="H296" s="14"/>
     </row>
-    <row r="297" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A297" s="16"/>
       <c r="B297" s="15"/>
       <c r="C297" s="15"/>
@@ -6509,7 +6509,7 @@
       <c r="G297" s="56"/>
       <c r="H297" s="14"/>
     </row>
-    <row r="298" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A298" s="38"/>
       <c r="B298" s="15"/>
       <c r="C298" s="15"/>
@@ -6517,7 +6517,7 @@
       <c r="G298" s="56"/>
       <c r="H298" s="14"/>
     </row>
-    <row r="299" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A299" s="50"/>
       <c r="B299" s="15"/>
       <c r="C299" s="15"/>
@@ -6525,7 +6525,7 @@
       <c r="G299" s="56"/>
       <c r="H299" s="14"/>
     </row>
-    <row r="300" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A300" s="16"/>
       <c r="B300" s="15"/>
       <c r="C300" s="15"/>
@@ -6533,7 +6533,7 @@
       <c r="G300" s="56"/>
       <c r="H300" s="14"/>
     </row>
-    <row r="301" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A301" s="16"/>
       <c r="B301" s="15"/>
       <c r="C301" s="15"/>
@@ -6541,7 +6541,7 @@
       <c r="G301" s="56"/>
       <c r="H301" s="14"/>
     </row>
-    <row r="302" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A302" s="16"/>
       <c r="B302" s="15"/>
       <c r="C302" s="15"/>
@@ -6549,7 +6549,7 @@
       <c r="G302" s="56"/>
       <c r="H302" s="14"/>
     </row>
-    <row r="303" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A303" s="38"/>
       <c r="B303" s="15"/>
       <c r="C303" s="15"/>
@@ -6557,7 +6557,7 @@
       <c r="G303" s="56"/>
       <c r="H303" s="14"/>
     </row>
-    <row r="304" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A304" s="50"/>
       <c r="B304" s="15"/>
       <c r="C304" s="15"/>
@@ -6565,7 +6565,7 @@
       <c r="G304" s="56"/>
       <c r="H304" s="14"/>
     </row>
-    <row r="305" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A305" s="16"/>
       <c r="B305" s="15"/>
       <c r="C305" s="15"/>
@@ -6573,7 +6573,7 @@
       <c r="G305" s="56"/>
       <c r="H305" s="14"/>
     </row>
-    <row r="306" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A306" s="16"/>
       <c r="B306" s="15"/>
       <c r="C306" s="15"/>
@@ -6581,7 +6581,7 @@
       <c r="G306" s="56"/>
       <c r="H306" s="14"/>
     </row>
-    <row r="307" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A307" s="16"/>
       <c r="B307" s="15"/>
       <c r="C307" s="15"/>
@@ -6589,7 +6589,7 @@
       <c r="G307" s="56"/>
       <c r="H307" s="14"/>
     </row>
-    <row r="308" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A308" s="38"/>
       <c r="B308" s="15"/>
       <c r="C308" s="15"/>
@@ -6597,7 +6597,7 @@
       <c r="G308" s="56"/>
       <c r="H308" s="14"/>
     </row>
-    <row r="309" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A309" s="50"/>
       <c r="B309" s="15"/>
       <c r="C309" s="15"/>
@@ -6605,7 +6605,7 @@
       <c r="G309" s="56"/>
       <c r="H309" s="14"/>
     </row>
-    <row r="310" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A310" s="16"/>
       <c r="B310" s="15"/>
       <c r="C310" s="15"/>
@@ -6613,7 +6613,7 @@
       <c r="G310" s="56"/>
       <c r="H310" s="14"/>
     </row>
-    <row r="311" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A311" s="16"/>
       <c r="B311" s="15"/>
       <c r="C311" s="15"/>
@@ -6621,7 +6621,7 @@
       <c r="G311" s="56"/>
       <c r="H311" s="14"/>
     </row>
-    <row r="312" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A312" s="16"/>
       <c r="B312" s="15"/>
       <c r="C312" s="15"/>
@@ -6629,7 +6629,7 @@
       <c r="G312" s="56"/>
       <c r="H312" s="14"/>
     </row>
-    <row r="313" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A313" s="38"/>
       <c r="B313" s="15"/>
       <c r="C313" s="15"/>
@@ -6637,7 +6637,7 @@
       <c r="G313" s="56"/>
       <c r="H313" s="14"/>
     </row>
-    <row r="314" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A314" s="50"/>
       <c r="B314" s="15"/>
       <c r="C314" s="15"/>
@@ -6645,7 +6645,7 @@
       <c r="G314" s="56"/>
       <c r="H314" s="14"/>
     </row>
-    <row r="315" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A315" s="16"/>
       <c r="B315" s="15"/>
       <c r="C315" s="15"/>
@@ -6653,7 +6653,7 @@
       <c r="G315" s="56"/>
       <c r="H315" s="14"/>
     </row>
-    <row r="316" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A316" s="16"/>
       <c r="B316" s="15"/>
       <c r="C316" s="15"/>
@@ -6661,7 +6661,7 @@
       <c r="G316" s="56"/>
       <c r="H316" s="14"/>
     </row>
-    <row r="317" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A317" s="16"/>
       <c r="B317" s="15"/>
       <c r="C317" s="15"/>
@@ -6669,7 +6669,7 @@
       <c r="G317" s="56"/>
       <c r="H317" s="14"/>
     </row>
-    <row r="318" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A318" s="38"/>
       <c r="B318" s="15"/>
       <c r="C318" s="15"/>
@@ -6677,7 +6677,7 @@
       <c r="G318" s="56"/>
       <c r="H318" s="14"/>
     </row>
-    <row r="319" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A319" s="50"/>
       <c r="B319" s="15"/>
       <c r="C319" s="15"/>
@@ -6685,7 +6685,7 @@
       <c r="G319" s="56"/>
       <c r="H319" s="14"/>
     </row>
-    <row r="320" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A320" s="16"/>
       <c r="B320" s="15"/>
       <c r="C320" s="15"/>
@@ -6693,7 +6693,7 @@
       <c r="G320" s="56"/>
       <c r="H320" s="14"/>
     </row>
-    <row r="321" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A321" s="16"/>
       <c r="B321" s="15"/>
       <c r="C321" s="15"/>
@@ -6701,7 +6701,7 @@
       <c r="G321" s="56"/>
       <c r="H321" s="14"/>
     </row>
-    <row r="322" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A322" s="16"/>
       <c r="B322" s="15"/>
       <c r="C322" s="15"/>
@@ -6709,7 +6709,7 @@
       <c r="G322" s="56"/>
       <c r="H322" s="14"/>
     </row>
-    <row r="323" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A323" s="38"/>
       <c r="B323" s="15"/>
       <c r="C323" s="15"/>
@@ -6717,7 +6717,7 @@
       <c r="G323" s="56"/>
       <c r="H323" s="14"/>
     </row>
-    <row r="324" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A324" s="50"/>
       <c r="B324" s="15"/>
       <c r="C324" s="15"/>
@@ -6725,7 +6725,7 @@
       <c r="G324" s="56"/>
       <c r="H324" s="14"/>
     </row>
-    <row r="325" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A325" s="16"/>
       <c r="B325" s="15"/>
       <c r="C325" s="15"/>
@@ -6733,7 +6733,7 @@
       <c r="G325" s="56"/>
       <c r="H325" s="14"/>
     </row>
-    <row r="326" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A326" s="16"/>
       <c r="B326" s="15"/>
       <c r="C326" s="15"/>
@@ -6741,7 +6741,7 @@
       <c r="G326" s="56"/>
       <c r="H326" s="14"/>
     </row>
-    <row r="327" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A327" s="16"/>
       <c r="B327" s="15"/>
       <c r="C327" s="15"/>
@@ -6749,7 +6749,7 @@
       <c r="G327" s="56"/>
       <c r="H327" s="14"/>
     </row>
-    <row r="328" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A328" s="38"/>
       <c r="B328" s="15"/>
       <c r="C328" s="15"/>
@@ -6757,7 +6757,7 @@
       <c r="G328" s="56"/>
       <c r="H328" s="14"/>
     </row>
-    <row r="329" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A329" s="50"/>
       <c r="B329" s="15"/>
       <c r="C329" s="15"/>
@@ -6765,7 +6765,7 @@
       <c r="G329" s="56"/>
       <c r="H329" s="14"/>
     </row>
-    <row r="330" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A330" s="16"/>
       <c r="B330" s="15"/>
       <c r="C330" s="15"/>
@@ -6773,7 +6773,7 @@
       <c r="G330" s="56"/>
       <c r="H330" s="14"/>
     </row>
-    <row r="331" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A331" s="16"/>
       <c r="B331" s="15"/>
       <c r="C331" s="15"/>
@@ -6781,7 +6781,7 @@
       <c r="G331" s="56"/>
       <c r="H331" s="14"/>
     </row>
-    <row r="332" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A332" s="16"/>
       <c r="B332" s="15"/>
       <c r="C332" s="15"/>
@@ -6789,7 +6789,7 @@
       <c r="G332" s="56"/>
       <c r="H332" s="14"/>
     </row>
-    <row r="333" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A333" s="38"/>
       <c r="B333" s="15"/>
       <c r="C333" s="15"/>
@@ -6797,7 +6797,7 @@
       <c r="G333" s="56"/>
       <c r="H333" s="14"/>
     </row>
-    <row r="334" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A334" s="50"/>
       <c r="B334" s="15"/>
       <c r="C334" s="15"/>
@@ -6805,7 +6805,7 @@
       <c r="G334" s="56"/>
       <c r="H334" s="14"/>
     </row>
-    <row r="335" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A335" s="16"/>
       <c r="B335" s="15"/>
       <c r="C335" s="15"/>
@@ -6813,7 +6813,7 @@
       <c r="G335" s="56"/>
       <c r="H335" s="14"/>
     </row>
-    <row r="336" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A336" s="16"/>
       <c r="B336" s="15"/>
       <c r="C336" s="15"/>
@@ -6821,7 +6821,7 @@
       <c r="G336" s="56"/>
       <c r="H336" s="14"/>
     </row>
-    <row r="337" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A337" s="16"/>
       <c r="B337" s="15"/>
       <c r="C337" s="15"/>
@@ -6829,7 +6829,7 @@
       <c r="G337" s="56"/>
       <c r="H337" s="14"/>
     </row>
-    <row r="338" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A338" s="38"/>
       <c r="B338" s="15"/>
       <c r="C338" s="15"/>
@@ -6837,7 +6837,7 @@
       <c r="G338" s="56"/>
       <c r="H338" s="14"/>
     </row>
-    <row r="339" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A339" s="50"/>
       <c r="B339" s="15"/>
       <c r="C339" s="15"/>
@@ -6845,7 +6845,7 @@
       <c r="G339" s="56"/>
       <c r="H339" s="14"/>
     </row>
-    <row r="340" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A340" s="16"/>
       <c r="B340" s="15"/>
       <c r="C340" s="15"/>
@@ -6853,7 +6853,7 @@
       <c r="G340" s="56"/>
       <c r="H340" s="14"/>
     </row>
-    <row r="341" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A341" s="16"/>
       <c r="B341" s="15"/>
       <c r="C341" s="15"/>
@@ -6861,7 +6861,7 @@
       <c r="G341" s="56"/>
       <c r="H341" s="14"/>
     </row>
-    <row r="342" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A342" s="16"/>
       <c r="B342" s="15"/>
       <c r="C342" s="15"/>
@@ -6869,7 +6869,7 @@
       <c r="G342" s="56"/>
       <c r="H342" s="14"/>
     </row>
-    <row r="343" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A343" s="38"/>
       <c r="B343" s="15"/>
       <c r="C343" s="15"/>
@@ -6877,7 +6877,7 @@
       <c r="G343" s="56"/>
       <c r="H343" s="14"/>
     </row>
-    <row r="344" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A344" s="50"/>
       <c r="B344" s="15"/>
       <c r="C344" s="15"/>
@@ -6885,7 +6885,7 @@
       <c r="G344" s="56"/>
       <c r="H344" s="14"/>
     </row>
-    <row r="345" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A345" s="16"/>
       <c r="B345" s="15"/>
       <c r="C345" s="15"/>
@@ -6893,7 +6893,7 @@
       <c r="G345" s="56"/>
       <c r="H345" s="14"/>
     </row>
-    <row r="346" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A346" s="16"/>
       <c r="B346" s="15"/>
       <c r="C346" s="15"/>
@@ -6913,14 +6913,14 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6931,7 +6931,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -6942,7 +6942,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>0</v>
       </c>

--- a/data/Mina_modelo_costo_fijo_BS/elmo_data.xlsx
+++ b/data/Mina_modelo_costo_fijo_BS/elmo_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Agustin\Desktop\Elmo_infrastructure_NP\data\Mina_modelo_costo_fijo_BS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TECNO-MASTER\Desktop\Elmo_infrastructure_sizing_NP-\data\Mina_modelo_costo_fijo_BS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A87EEE48-3ED1-448E-B571-DF7493953906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A48833B-C1F7-47B2-9D37-1A155AB6B738}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Batteries" sheetId="1" r:id="rId1"/>
@@ -1297,24 +1297,24 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:AC34"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.6640625" style="32" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.33203125" style="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.6640625" style="18" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" style="17" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5546875" style="17" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.33203125" style="17" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" style="33" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.6640625" style="17" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.7109375" style="32" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" style="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.7109375" style="18" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" style="17" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="17" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="17" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" style="33" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" style="17" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15" style="17" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.6640625" style="33" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.44140625" style="33" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.7109375" style="33" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.42578125" style="33" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:29" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1365,7 +1365,7 @@
       <c r="AB1" s="36"/>
       <c r="AC1" s="36"/>
     </row>
-    <row r="2" spans="1:29" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:29" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="40" t="s">
         <v>3</v>
       </c>
@@ -1416,7 +1416,7 @@
       <c r="AB2" s="36"/>
       <c r="AC2" s="36"/>
     </row>
-    <row r="3" spans="1:29" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:29" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="41">
         <v>1</v>
       </c>
@@ -1467,7 +1467,7 @@
       <c r="AB3" s="46"/>
       <c r="AC3" s="46"/>
     </row>
-    <row r="4" spans="1:29" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:29" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="41">
         <v>2</v>
       </c>
@@ -1518,7 +1518,7 @@
       <c r="AB4" s="46"/>
       <c r="AC4" s="46"/>
     </row>
-    <row r="5" spans="1:29" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:29" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="41">
         <v>3</v>
       </c>
@@ -1569,7 +1569,7 @@
       <c r="AB5" s="46"/>
       <c r="AC5" s="46"/>
     </row>
-    <row r="6" spans="1:29" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:29" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="41">
         <v>4</v>
       </c>
@@ -1620,7 +1620,7 @@
       <c r="AB6" s="46"/>
       <c r="AC6" s="46"/>
     </row>
-    <row r="7" spans="1:29" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:29" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="41"/>
       <c r="B7" s="43"/>
       <c r="C7" s="45"/>
@@ -1635,7 +1635,7 @@
       <c r="L7" s="52"/>
       <c r="M7" s="52"/>
     </row>
-    <row r="8" spans="1:29" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:29" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="41"/>
       <c r="B8" s="43"/>
       <c r="C8" s="45"/>
@@ -1650,7 +1650,7 @@
       <c r="L8" s="52"/>
       <c r="M8" s="52"/>
     </row>
-    <row r="9" spans="1:29" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:29" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="41"/>
       <c r="B9" s="43"/>
       <c r="C9" s="45"/>
@@ -1665,7 +1665,7 @@
       <c r="L9" s="52"/>
       <c r="M9" s="52"/>
     </row>
-    <row r="10" spans="1:29" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:29" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="41"/>
       <c r="B10" s="43"/>
       <c r="C10" s="45"/>
@@ -1680,7 +1680,7 @@
       <c r="L10" s="52"/>
       <c r="M10" s="52"/>
     </row>
-    <row r="11" spans="1:29" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:29" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="41"/>
       <c r="B11" s="43"/>
       <c r="C11" s="45"/>
@@ -1695,7 +1695,7 @@
       <c r="L11" s="52"/>
       <c r="M11" s="52"/>
     </row>
-    <row r="12" spans="1:29" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:29" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="41"/>
       <c r="B12" s="43"/>
       <c r="C12" s="45"/>
@@ -1710,7 +1710,7 @@
       <c r="L12" s="52"/>
       <c r="M12" s="52"/>
     </row>
-    <row r="13" spans="1:29" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:29" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="41"/>
       <c r="B13" s="43"/>
       <c r="C13" s="45"/>
@@ -1725,7 +1725,7 @@
       <c r="L13" s="52"/>
       <c r="M13" s="52"/>
     </row>
-    <row r="14" spans="1:29" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:29" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="41"/>
       <c r="B14" s="43"/>
       <c r="C14" s="45"/>
@@ -1740,7 +1740,7 @@
       <c r="L14" s="52"/>
       <c r="M14" s="52"/>
     </row>
-    <row r="15" spans="1:29" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:29" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="41"/>
       <c r="B15" s="43"/>
       <c r="C15" s="45"/>
@@ -1755,7 +1755,7 @@
       <c r="L15" s="52"/>
       <c r="M15" s="52"/>
     </row>
-    <row r="16" spans="1:29" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:29" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="41"/>
       <c r="B16" s="43"/>
       <c r="C16" s="45"/>
@@ -1770,7 +1770,7 @@
       <c r="L16" s="52"/>
       <c r="M16" s="52"/>
     </row>
-    <row r="17" spans="1:13" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="41"/>
       <c r="B17" s="43"/>
       <c r="C17" s="45"/>
@@ -1785,7 +1785,7 @@
       <c r="L17" s="52"/>
       <c r="M17" s="52"/>
     </row>
-    <row r="18" spans="1:13" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="41"/>
       <c r="B18" s="43"/>
       <c r="C18" s="45"/>
@@ -1800,7 +1800,7 @@
       <c r="L18" s="52"/>
       <c r="M18" s="52"/>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="41"/>
       <c r="B19" s="43"/>
       <c r="C19" s="45"/>
@@ -1815,7 +1815,7 @@
       <c r="L19" s="52"/>
       <c r="M19" s="52"/>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="41"/>
       <c r="B20" s="43"/>
       <c r="C20" s="45"/>
@@ -1830,7 +1830,7 @@
       <c r="L20" s="52"/>
       <c r="M20" s="52"/>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="41"/>
       <c r="B21" s="43"/>
       <c r="C21" s="45"/>
@@ -1845,7 +1845,7 @@
       <c r="L21" s="52"/>
       <c r="M21" s="52"/>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="41"/>
       <c r="B22" s="43"/>
       <c r="C22" s="45"/>
@@ -1860,7 +1860,7 @@
       <c r="L22" s="52"/>
       <c r="M22" s="52"/>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="41"/>
       <c r="B23" s="43"/>
       <c r="C23" s="45"/>
@@ -1875,7 +1875,7 @@
       <c r="L23" s="52"/>
       <c r="M23" s="52"/>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="41"/>
       <c r="B24" s="43"/>
       <c r="C24" s="45"/>
@@ -1890,7 +1890,7 @@
       <c r="L24" s="52"/>
       <c r="M24" s="52"/>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="41"/>
       <c r="B25" s="43"/>
       <c r="C25" s="45"/>
@@ -1905,7 +1905,7 @@
       <c r="L25" s="52"/>
       <c r="M25" s="52"/>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="41"/>
       <c r="B26" s="43"/>
       <c r="C26" s="45"/>
@@ -1920,7 +1920,7 @@
       <c r="L26" s="52"/>
       <c r="M26" s="52"/>
     </row>
-    <row r="34" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H34" s="33"/>
     </row>
   </sheetData>
@@ -1935,38 +1935,38 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:AE17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" style="30" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" style="30" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.33203125" style="30" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5546875" style="30" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.44140625" style="30" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" style="30" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" style="30" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" style="30" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" style="30" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.42578125" style="30" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="7" style="30" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5546875" style="30" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.6640625" style="31" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.33203125" style="30" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5703125" style="30" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" style="31" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.28515625" style="30" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="15" style="30" customWidth="1"/>
-    <col min="16" max="16" width="17.33203125" style="30" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.5546875" style="31" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.28515625" style="30" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.5703125" style="31" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="18" style="31" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="20.6640625" style="31" bestFit="1" customWidth="1"/>
-    <col min="20" max="23" width="20.6640625" style="31" customWidth="1"/>
-    <col min="24" max="24" width="18.44140625" style="31" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="20.33203125" style="31" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15.5546875" style="31" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.33203125" style="31" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="20.7109375" style="31" bestFit="1" customWidth="1"/>
+    <col min="20" max="23" width="20.7109375" style="31" customWidth="1"/>
+    <col min="24" max="24" width="18.42578125" style="31" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="20.28515625" style="31" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15.5703125" style="31" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.28515625" style="31" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -2061,7 +2061,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="2" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="40" t="s">
         <v>3</v>
       </c>
@@ -2156,7 +2156,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="3" spans="1:31" ht="23.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:31" ht="23.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="41">
         <v>1</v>
       </c>
@@ -2251,7 +2251,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:31" ht="23.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:31" ht="23.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="41">
         <v>2</v>
       </c>
@@ -2346,7 +2346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:31" ht="23.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:31" ht="23.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="41">
         <v>3</v>
       </c>
@@ -2441,7 +2441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:31" ht="23.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:31" ht="23.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="41">
         <v>4</v>
       </c>
@@ -2537,7 +2537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" ht="23.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:31" ht="23.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="41"/>
       <c r="B7" s="70"/>
       <c r="C7" s="71"/>
@@ -2562,7 +2562,7 @@
       <c r="V7" s="46"/>
       <c r="W7" s="46"/>
     </row>
-    <row r="8" spans="1:31" ht="23.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:31" ht="23.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="41"/>
       <c r="B8" s="43"/>
       <c r="C8" s="45"/>
@@ -2587,7 +2587,7 @@
       <c r="V8" s="46"/>
       <c r="W8" s="46"/>
     </row>
-    <row r="9" spans="1:31" ht="23.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:31" ht="23.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="41"/>
       <c r="B9" s="43"/>
       <c r="C9" s="45"/>
@@ -2612,7 +2612,7 @@
       <c r="V9" s="46"/>
       <c r="W9" s="46"/>
     </row>
-    <row r="10" spans="1:31" ht="23.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:31" ht="23.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="58"/>
       <c r="B10" s="59"/>
       <c r="C10" s="60"/>
@@ -2637,7 +2637,7 @@
       <c r="V10" s="68"/>
       <c r="W10" s="68"/>
     </row>
-    <row r="11" spans="1:31" s="46" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:31" s="46" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="41"/>
       <c r="B11" s="43"/>
       <c r="C11" s="45"/>
@@ -2664,7 +2664,7 @@
       <c r="Z11" s="69"/>
       <c r="AA11" s="69"/>
     </row>
-    <row r="12" spans="1:31" s="46" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:31" s="46" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="41"/>
       <c r="B12" s="43"/>
       <c r="C12" s="45"/>
@@ -2691,7 +2691,7 @@
       <c r="Z12" s="69"/>
       <c r="AA12" s="69"/>
     </row>
-    <row r="13" spans="1:31" s="46" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:31" s="46" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="41"/>
       <c r="B13" s="43"/>
       <c r="C13" s="45"/>
@@ -2718,7 +2718,7 @@
       <c r="Z13" s="69"/>
       <c r="AA13" s="69"/>
     </row>
-    <row r="14" spans="1:31" s="46" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:31" s="46" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="41"/>
       <c r="B14" s="43"/>
       <c r="C14" s="45"/>
@@ -2745,9 +2745,9 @@
       <c r="Z14" s="69"/>
       <c r="AA14" s="69"/>
     </row>
-    <row r="15" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="17" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2757,13 +2757,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D86F6B0-26ED-4B02-B890-EDAFE42B3137}">
   <dimension ref="A1:G5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2786,7 +2786,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2809,7 +2809,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2832,7 +2832,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2855,7 +2855,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>3</v>
       </c>
@@ -2875,7 +2875,7 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -2886,15 +2886,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0351544-AA63-4F3E-855C-5CF465DCF681}">
   <dimension ref="A1:I3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2923,7 +2923,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2952,7 +2952,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2992,16 +2992,16 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:H346"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="13.5546875" style="18" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.44140625" style="18" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="29.33203125" style="17" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5546875" style="17" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" style="17" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="13.5703125" style="18" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="29.28515625" style="17" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" style="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -3027,7 +3027,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>3</v>
       </c>
@@ -3053,7 +3053,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14">
         <v>0</v>
       </c>
@@ -3079,7 +3079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="16">
         <v>1</v>
       </c>
@@ -3105,7 +3105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="16">
         <v>2</v>
       </c>
@@ -3131,7 +3131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="16">
         <v>3</v>
       </c>
@@ -3157,7 +3157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="16">
         <v>4</v>
       </c>
@@ -3183,7 +3183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16">
         <v>5</v>
       </c>
@@ -3209,7 +3209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16">
         <v>6</v>
       </c>
@@ -3235,7 +3235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16">
         <v>7</v>
       </c>
@@ -3261,7 +3261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="16">
         <v>8</v>
       </c>
@@ -3287,7 +3287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16">
         <v>9</v>
       </c>
@@ -3313,7 +3313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="16">
         <v>10</v>
       </c>
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="16">
         <v>11</v>
       </c>
@@ -3365,7 +3365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="16">
         <v>12</v>
       </c>
@@ -3391,7 +3391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="16">
         <v>13</v>
       </c>
@@ -3417,7 +3417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="16">
         <v>14</v>
       </c>
@@ -3443,7 +3443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="16">
         <v>15</v>
       </c>
@@ -3469,7 +3469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="16">
         <v>16</v>
       </c>
@@ -3495,7 +3495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16">
         <v>17</v>
       </c>
@@ -3521,7 +3521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="16">
         <v>18</v>
       </c>
@@ -3547,7 +3547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="16">
         <v>19</v>
       </c>
@@ -3573,7 +3573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="16">
         <v>20</v>
       </c>
@@ -3599,7 +3599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16">
         <v>21</v>
       </c>
@@ -3625,7 +3625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="16">
         <v>22</v>
       </c>
@@ -3651,7 +3651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="16">
         <v>23</v>
       </c>
@@ -3677,7 +3677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="16">
         <v>24</v>
       </c>
@@ -3703,7 +3703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="16">
         <v>25</v>
       </c>
@@ -3729,7 +3729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="16">
         <v>26</v>
       </c>
@@ -3755,7 +3755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="16">
         <v>27</v>
       </c>
@@ -3781,7 +3781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="16">
         <v>28</v>
       </c>
@@ -3807,7 +3807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="16">
         <v>29</v>
       </c>
@@ -3833,7 +3833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="16">
         <v>30</v>
       </c>
@@ -3859,7 +3859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="16">
         <v>31</v>
       </c>
@@ -3885,7 +3885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="16">
         <v>32</v>
       </c>
@@ -3911,7 +3911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="16">
         <v>33</v>
       </c>
@@ -3937,7 +3937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="16">
         <v>34</v>
       </c>
@@ -3963,7 +3963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="16">
         <v>35</v>
       </c>
@@ -3989,7 +3989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="16">
         <v>36</v>
       </c>
@@ -4015,7 +4015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="16">
         <v>37</v>
       </c>
@@ -4041,7 +4041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="16">
         <v>38</v>
       </c>
@@ -4067,7 +4067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="16">
         <v>39</v>
       </c>
@@ -4093,7 +4093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="16"/>
       <c r="B43" s="15"/>
       <c r="C43" s="15"/>
@@ -4103,7 +4103,7 @@
       <c r="G43" s="16"/>
       <c r="H43" s="14"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="16"/>
       <c r="B44" s="15"/>
       <c r="C44" s="15"/>
@@ -4113,7 +4113,7 @@
       <c r="G44" s="16"/>
       <c r="H44" s="14"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="16"/>
       <c r="B45" s="15"/>
       <c r="C45" s="15"/>
@@ -4123,7 +4123,7 @@
       <c r="G45" s="16"/>
       <c r="H45" s="14"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="16"/>
       <c r="B46" s="15"/>
       <c r="C46" s="15"/>
@@ -4133,7 +4133,7 @@
       <c r="G46" s="16"/>
       <c r="H46" s="14"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="16"/>
       <c r="B47" s="15"/>
       <c r="C47" s="15"/>
@@ -4143,7 +4143,7 @@
       <c r="G47" s="16"/>
       <c r="H47" s="14"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="16"/>
       <c r="B48" s="15"/>
       <c r="C48" s="15"/>
@@ -4153,7 +4153,7 @@
       <c r="G48" s="16"/>
       <c r="H48" s="14"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="16"/>
       <c r="B49" s="15"/>
       <c r="C49" s="15"/>
@@ -4163,7 +4163,7 @@
       <c r="G49" s="16"/>
       <c r="H49" s="14"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="16"/>
       <c r="B50" s="15"/>
       <c r="C50" s="15"/>
@@ -4173,7 +4173,7 @@
       <c r="G50" s="16"/>
       <c r="H50" s="14"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="16"/>
       <c r="B51" s="15"/>
       <c r="C51" s="15"/>
@@ -4183,7 +4183,7 @@
       <c r="G51" s="16"/>
       <c r="H51" s="14"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="16"/>
       <c r="B52" s="15"/>
       <c r="C52" s="15"/>
@@ -4193,7 +4193,7 @@
       <c r="G52" s="16"/>
       <c r="H52" s="14"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="16"/>
       <c r="B53" s="15"/>
       <c r="C53" s="15"/>
@@ -4203,7 +4203,7 @@
       <c r="G53" s="16"/>
       <c r="H53" s="14"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="16"/>
       <c r="B54" s="15"/>
       <c r="C54" s="15"/>
@@ -4213,7 +4213,7 @@
       <c r="G54" s="16"/>
       <c r="H54" s="14"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="16"/>
       <c r="B55" s="15"/>
       <c r="C55" s="15"/>
@@ -4223,7 +4223,7 @@
       <c r="G55" s="16"/>
       <c r="H55" s="14"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="16"/>
       <c r="B56" s="15"/>
       <c r="C56" s="15"/>
@@ -4233,7 +4233,7 @@
       <c r="G56" s="16"/>
       <c r="H56" s="14"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="16"/>
       <c r="B57" s="15"/>
       <c r="C57" s="15"/>
@@ -4243,7 +4243,7 @@
       <c r="G57" s="16"/>
       <c r="H57" s="14"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="16"/>
       <c r="B58" s="15"/>
       <c r="C58" s="15"/>
@@ -4253,7 +4253,7 @@
       <c r="G58" s="16"/>
       <c r="H58" s="14"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="16"/>
       <c r="B59" s="15"/>
       <c r="C59" s="15"/>
@@ -4263,7 +4263,7 @@
       <c r="G59" s="16"/>
       <c r="H59" s="14"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="16"/>
       <c r="B60" s="15"/>
       <c r="C60" s="15"/>
@@ -4273,7 +4273,7 @@
       <c r="G60" s="16"/>
       <c r="H60" s="14"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="16"/>
       <c r="B61" s="15"/>
       <c r="C61" s="15"/>
@@ -4283,7 +4283,7 @@
       <c r="G61" s="16"/>
       <c r="H61" s="14"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="16"/>
       <c r="B62" s="15"/>
       <c r="C62" s="15"/>
@@ -4293,7 +4293,7 @@
       <c r="G62" s="16"/>
       <c r="H62" s="14"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="16"/>
       <c r="B63" s="15"/>
       <c r="C63" s="15"/>
@@ -4303,7 +4303,7 @@
       <c r="G63" s="16"/>
       <c r="H63" s="14"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="16"/>
       <c r="B64" s="15"/>
       <c r="C64" s="15"/>
@@ -4313,7 +4313,7 @@
       <c r="G64" s="16"/>
       <c r="H64" s="14"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="16"/>
       <c r="B65" s="15"/>
       <c r="C65" s="15"/>
@@ -4323,7 +4323,7 @@
       <c r="G65" s="16"/>
       <c r="H65" s="14"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="16"/>
       <c r="B66" s="15"/>
       <c r="C66" s="15"/>
@@ -4333,7 +4333,7 @@
       <c r="G66" s="16"/>
       <c r="H66" s="14"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="16"/>
       <c r="B67" s="15"/>
       <c r="C67" s="15"/>
@@ -4343,7 +4343,7 @@
       <c r="G67" s="16"/>
       <c r="H67" s="14"/>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="16"/>
       <c r="B68" s="15"/>
       <c r="C68" s="15"/>
@@ -4353,7 +4353,7 @@
       <c r="G68" s="16"/>
       <c r="H68" s="14"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="16"/>
       <c r="B69" s="15"/>
       <c r="C69" s="15"/>
@@ -4363,7 +4363,7 @@
       <c r="G69" s="16"/>
       <c r="H69" s="14"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="16"/>
       <c r="B70" s="15"/>
       <c r="C70" s="15"/>
@@ -4373,7 +4373,7 @@
       <c r="G70" s="16"/>
       <c r="H70" s="14"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="16"/>
       <c r="B71" s="15"/>
       <c r="C71" s="15"/>
@@ -4383,7 +4383,7 @@
       <c r="G71" s="16"/>
       <c r="H71" s="14"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="16"/>
       <c r="B72" s="15"/>
       <c r="C72" s="15"/>
@@ -4393,7 +4393,7 @@
       <c r="G72" s="16"/>
       <c r="H72" s="14"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="16"/>
       <c r="B73" s="15"/>
       <c r="C73" s="15"/>
@@ -4403,7 +4403,7 @@
       <c r="G73" s="16"/>
       <c r="H73" s="14"/>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="16"/>
       <c r="B74" s="15"/>
       <c r="C74" s="15"/>
@@ -4413,7 +4413,7 @@
       <c r="G74" s="16"/>
       <c r="H74" s="14"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="16"/>
       <c r="B75" s="15"/>
       <c r="C75" s="15"/>
@@ -4423,7 +4423,7 @@
       <c r="G75" s="16"/>
       <c r="H75" s="14"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="16"/>
       <c r="B76" s="15"/>
       <c r="C76" s="15"/>
@@ -4433,7 +4433,7 @@
       <c r="G76" s="16"/>
       <c r="H76" s="14"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="16"/>
       <c r="B77" s="15"/>
       <c r="C77" s="15"/>
@@ -4443,7 +4443,7 @@
       <c r="G77" s="16"/>
       <c r="H77" s="14"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="16"/>
       <c r="B78" s="15"/>
       <c r="C78" s="15"/>
@@ -4453,7 +4453,7 @@
       <c r="G78" s="16"/>
       <c r="H78" s="14"/>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="16"/>
       <c r="B79" s="15"/>
       <c r="C79" s="15"/>
@@ -4463,7 +4463,7 @@
       <c r="G79" s="16"/>
       <c r="H79" s="14"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="16"/>
       <c r="B80" s="15"/>
       <c r="C80" s="15"/>
@@ -4473,7 +4473,7 @@
       <c r="G80" s="16"/>
       <c r="H80" s="14"/>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="16"/>
       <c r="B81" s="15"/>
       <c r="C81" s="15"/>
@@ -4483,7 +4483,7 @@
       <c r="G81" s="16"/>
       <c r="H81" s="14"/>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="16"/>
       <c r="B82" s="15"/>
       <c r="C82" s="15"/>
@@ -4493,7 +4493,7 @@
       <c r="G82" s="16"/>
       <c r="H82" s="14"/>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="16"/>
       <c r="B83" s="15"/>
       <c r="C83" s="15"/>
@@ -4503,7 +4503,7 @@
       <c r="G83" s="16"/>
       <c r="H83" s="14"/>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="16"/>
       <c r="B84" s="15"/>
       <c r="C84" s="15"/>
@@ -4513,7 +4513,7 @@
       <c r="G84" s="16"/>
       <c r="H84" s="14"/>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="16"/>
       <c r="B85" s="15"/>
       <c r="C85" s="15"/>
@@ -4523,7 +4523,7 @@
       <c r="G85" s="16"/>
       <c r="H85" s="14"/>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="16"/>
       <c r="B86" s="15"/>
       <c r="C86" s="15"/>
@@ -4533,7 +4533,7 @@
       <c r="G86" s="16"/>
       <c r="H86" s="14"/>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="16"/>
       <c r="B87" s="15"/>
       <c r="C87" s="15"/>
@@ -4543,7 +4543,7 @@
       <c r="G87" s="16"/>
       <c r="H87" s="14"/>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="16"/>
       <c r="B88" s="15"/>
       <c r="C88" s="15"/>
@@ -4553,7 +4553,7 @@
       <c r="G88" s="16"/>
       <c r="H88" s="14"/>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="16"/>
       <c r="B89" s="15"/>
       <c r="C89" s="15"/>
@@ -4563,7 +4563,7 @@
       <c r="G89" s="16"/>
       <c r="H89" s="14"/>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="16"/>
       <c r="B90" s="15"/>
       <c r="C90" s="15"/>
@@ -4573,7 +4573,7 @@
       <c r="G90" s="16"/>
       <c r="H90" s="14"/>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="16"/>
       <c r="B91" s="15"/>
       <c r="C91" s="15"/>
@@ -4583,7 +4583,7 @@
       <c r="G91" s="16"/>
       <c r="H91" s="14"/>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="16"/>
       <c r="B92" s="15"/>
       <c r="C92" s="15"/>
@@ -4593,7 +4593,7 @@
       <c r="G92" s="16"/>
       <c r="H92" s="14"/>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="16"/>
       <c r="B93" s="15"/>
       <c r="C93" s="15"/>
@@ -4603,7 +4603,7 @@
       <c r="G93" s="16"/>
       <c r="H93" s="14"/>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="16"/>
       <c r="B94" s="15"/>
       <c r="C94" s="15"/>
@@ -4613,7 +4613,7 @@
       <c r="G94" s="16"/>
       <c r="H94" s="14"/>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="16"/>
       <c r="B95" s="15"/>
       <c r="C95" s="15"/>
@@ -4623,7 +4623,7 @@
       <c r="G95" s="16"/>
       <c r="H95" s="14"/>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="16"/>
       <c r="B96" s="15"/>
       <c r="C96" s="15"/>
@@ -4633,7 +4633,7 @@
       <c r="G96" s="16"/>
       <c r="H96" s="14"/>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="16"/>
       <c r="B97" s="15"/>
       <c r="C97" s="15"/>
@@ -4643,7 +4643,7 @@
       <c r="G97" s="16"/>
       <c r="H97" s="14"/>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="16"/>
       <c r="B98" s="15"/>
       <c r="C98" s="15"/>
@@ -4653,7 +4653,7 @@
       <c r="G98" s="16"/>
       <c r="H98" s="14"/>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" s="16"/>
       <c r="B99" s="15"/>
       <c r="C99" s="15"/>
@@ -4663,7 +4663,7 @@
       <c r="G99" s="16"/>
       <c r="H99" s="14"/>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="16"/>
       <c r="B100" s="15"/>
       <c r="C100" s="15"/>
@@ -4673,7 +4673,7 @@
       <c r="G100" s="16"/>
       <c r="H100" s="14"/>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="16"/>
       <c r="B101" s="15"/>
       <c r="C101" s="15"/>
@@ -4683,7 +4683,7 @@
       <c r="G101" s="16"/>
       <c r="H101" s="14"/>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" s="16"/>
       <c r="B102" s="15"/>
       <c r="C102" s="15"/>
@@ -4693,7 +4693,7 @@
       <c r="G102" s="16"/>
       <c r="H102" s="14"/>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" s="16"/>
       <c r="B103" s="15"/>
       <c r="C103" s="15"/>
@@ -4703,7 +4703,7 @@
       <c r="G103" s="16"/>
       <c r="H103" s="14"/>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" s="16"/>
       <c r="B104" s="15"/>
       <c r="C104" s="15"/>
@@ -4713,7 +4713,7 @@
       <c r="G104" s="16"/>
       <c r="H104" s="14"/>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" s="16"/>
       <c r="B105" s="15"/>
       <c r="C105" s="15"/>
@@ -4723,7 +4723,7 @@
       <c r="G105" s="16"/>
       <c r="H105" s="14"/>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" s="16"/>
       <c r="B106" s="15"/>
       <c r="C106" s="15"/>
@@ -4733,7 +4733,7 @@
       <c r="G106" s="16"/>
       <c r="H106" s="14"/>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" s="16"/>
       <c r="B107" s="15"/>
       <c r="C107" s="15"/>
@@ -4743,7 +4743,7 @@
       <c r="G107" s="16"/>
       <c r="H107" s="14"/>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" s="16"/>
       <c r="B108" s="15"/>
       <c r="C108" s="15"/>
@@ -4753,7 +4753,7 @@
       <c r="G108" s="16"/>
       <c r="H108" s="14"/>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" s="16"/>
       <c r="B109" s="15"/>
       <c r="C109" s="15"/>
@@ -4763,7 +4763,7 @@
       <c r="G109" s="16"/>
       <c r="H109" s="14"/>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" s="16"/>
       <c r="B110" s="15"/>
       <c r="C110" s="15"/>
@@ -4773,7 +4773,7 @@
       <c r="G110" s="16"/>
       <c r="H110" s="14"/>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" s="16"/>
       <c r="B111" s="15"/>
       <c r="C111" s="15"/>
@@ -4783,7 +4783,7 @@
       <c r="G111" s="16"/>
       <c r="H111" s="14"/>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" s="38"/>
       <c r="B112" s="15"/>
       <c r="C112" s="15"/>
@@ -4793,7 +4793,7 @@
       <c r="G112" s="16"/>
       <c r="H112" s="14"/>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" s="50"/>
       <c r="B113" s="15"/>
       <c r="C113" s="15"/>
@@ -4803,7 +4803,7 @@
       <c r="G113" s="16"/>
       <c r="H113" s="14"/>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" s="16"/>
       <c r="B114" s="15"/>
       <c r="C114" s="15"/>
@@ -4813,7 +4813,7 @@
       <c r="G114" s="56"/>
       <c r="H114" s="14"/>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" s="16"/>
       <c r="B115" s="15"/>
       <c r="C115" s="15"/>
@@ -4823,7 +4823,7 @@
       <c r="G115" s="56"/>
       <c r="H115" s="14"/>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" s="38"/>
       <c r="B116" s="15"/>
       <c r="C116" s="15"/>
@@ -4833,7 +4833,7 @@
       <c r="G116" s="56"/>
       <c r="H116" s="14"/>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" s="50"/>
       <c r="B117" s="15"/>
       <c r="C117" s="15"/>
@@ -4843,7 +4843,7 @@
       <c r="G117" s="56"/>
       <c r="H117" s="14"/>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" s="16"/>
       <c r="B118" s="15"/>
       <c r="C118" s="15"/>
@@ -4853,7 +4853,7 @@
       <c r="G118" s="56"/>
       <c r="H118" s="14"/>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" s="16"/>
       <c r="B119" s="15"/>
       <c r="C119" s="15"/>
@@ -4863,7 +4863,7 @@
       <c r="G119" s="56"/>
       <c r="H119" s="14"/>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" s="38"/>
       <c r="B120" s="15"/>
       <c r="C120" s="15"/>
@@ -4873,7 +4873,7 @@
       <c r="G120" s="56"/>
       <c r="H120" s="14"/>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" s="50"/>
       <c r="B121" s="15"/>
       <c r="C121" s="15"/>
@@ -4883,7 +4883,7 @@
       <c r="G121" s="56"/>
       <c r="H121" s="14"/>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" s="16"/>
       <c r="B122" s="15"/>
       <c r="C122" s="15"/>
@@ -4893,7 +4893,7 @@
       <c r="G122" s="56"/>
       <c r="H122" s="14"/>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" s="16"/>
       <c r="B123" s="15"/>
       <c r="C123" s="15"/>
@@ -4903,7 +4903,7 @@
       <c r="G123" s="56"/>
       <c r="H123" s="14"/>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" s="38"/>
       <c r="B124" s="15"/>
       <c r="C124" s="15"/>
@@ -4913,7 +4913,7 @@
       <c r="G124" s="56"/>
       <c r="H124" s="14"/>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" s="50"/>
       <c r="B125" s="15"/>
       <c r="C125" s="15"/>
@@ -4923,7 +4923,7 @@
       <c r="G125" s="56"/>
       <c r="H125" s="14"/>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" s="16"/>
       <c r="B126" s="15"/>
       <c r="C126" s="15"/>
@@ -4933,7 +4933,7 @@
       <c r="G126" s="56"/>
       <c r="H126" s="14"/>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" s="16"/>
       <c r="B127" s="15"/>
       <c r="C127" s="15"/>
@@ -4943,7 +4943,7 @@
       <c r="G127" s="56"/>
       <c r="H127" s="14"/>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" s="38"/>
       <c r="B128" s="15"/>
       <c r="C128" s="15"/>
@@ -4953,7 +4953,7 @@
       <c r="G128" s="56"/>
       <c r="H128" s="14"/>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" s="50"/>
       <c r="B129" s="15"/>
       <c r="C129" s="15"/>
@@ -4963,7 +4963,7 @@
       <c r="G129" s="56"/>
       <c r="H129" s="14"/>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" s="16"/>
       <c r="B130" s="15"/>
       <c r="C130" s="15"/>
@@ -4973,7 +4973,7 @@
       <c r="G130" s="56"/>
       <c r="H130" s="14"/>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" s="16"/>
       <c r="B131" s="15"/>
       <c r="C131" s="15"/>
@@ -4983,7 +4983,7 @@
       <c r="G131" s="56"/>
       <c r="H131" s="14"/>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" s="38"/>
       <c r="B132" s="15"/>
       <c r="C132" s="15"/>
@@ -4993,7 +4993,7 @@
       <c r="G132" s="56"/>
       <c r="H132" s="14"/>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" s="50"/>
       <c r="B133" s="15"/>
       <c r="C133" s="15"/>
@@ -5003,7 +5003,7 @@
       <c r="G133" s="56"/>
       <c r="H133" s="14"/>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" s="16"/>
       <c r="B134" s="15"/>
       <c r="C134" s="15"/>
@@ -5013,7 +5013,7 @@
       <c r="G134" s="56"/>
       <c r="H134" s="14"/>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" s="16"/>
       <c r="B135" s="15"/>
       <c r="C135" s="15"/>
@@ -5023,7 +5023,7 @@
       <c r="G135" s="56"/>
       <c r="H135" s="14"/>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" s="38"/>
       <c r="B136" s="15"/>
       <c r="C136" s="15"/>
@@ -5033,7 +5033,7 @@
       <c r="G136" s="56"/>
       <c r="H136" s="14"/>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" s="50"/>
       <c r="B137" s="15"/>
       <c r="C137" s="15"/>
@@ -5043,7 +5043,7 @@
       <c r="G137" s="56"/>
       <c r="H137" s="14"/>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" s="16"/>
       <c r="B138" s="15"/>
       <c r="C138" s="15"/>
@@ -5053,7 +5053,7 @@
       <c r="G138" s="56"/>
       <c r="H138" s="14"/>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" s="16"/>
       <c r="B139" s="15"/>
       <c r="C139" s="15"/>
@@ -5063,7 +5063,7 @@
       <c r="G139" s="56"/>
       <c r="H139" s="14"/>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" s="38"/>
       <c r="B140" s="15"/>
       <c r="C140" s="15"/>
@@ -5073,7 +5073,7 @@
       <c r="G140" s="56"/>
       <c r="H140" s="14"/>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" s="50"/>
       <c r="B141" s="15"/>
       <c r="C141" s="15"/>
@@ -5083,7 +5083,7 @@
       <c r="G141" s="56"/>
       <c r="H141" s="14"/>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" s="16"/>
       <c r="B142" s="15"/>
       <c r="C142" s="15"/>
@@ -5093,7 +5093,7 @@
       <c r="G142" s="56"/>
       <c r="H142" s="14"/>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" s="16"/>
       <c r="B143" s="15"/>
       <c r="C143" s="15"/>
@@ -5103,7 +5103,7 @@
       <c r="G143" s="56"/>
       <c r="H143" s="14"/>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" s="38"/>
       <c r="B144" s="15"/>
       <c r="C144" s="15"/>
@@ -5113,7 +5113,7 @@
       <c r="G144" s="56"/>
       <c r="H144" s="14"/>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" s="50"/>
       <c r="B145" s="15"/>
       <c r="C145" s="15"/>
@@ -5123,7 +5123,7 @@
       <c r="G145" s="56"/>
       <c r="H145" s="14"/>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" s="16"/>
       <c r="B146" s="15"/>
       <c r="C146" s="15"/>
@@ -5133,7 +5133,7 @@
       <c r="G146" s="56"/>
       <c r="H146" s="14"/>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" s="16"/>
       <c r="B147" s="15"/>
       <c r="C147" s="15"/>
@@ -5143,7 +5143,7 @@
       <c r="G147" s="56"/>
       <c r="H147" s="14"/>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" s="38"/>
       <c r="B148" s="15"/>
       <c r="C148" s="15"/>
@@ -5153,7 +5153,7 @@
       <c r="G148" s="56"/>
       <c r="H148" s="14"/>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" s="50"/>
       <c r="B149" s="15"/>
       <c r="C149" s="15"/>
@@ -5163,7 +5163,7 @@
       <c r="G149" s="56"/>
       <c r="H149" s="14"/>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" s="16"/>
       <c r="B150" s="15"/>
       <c r="C150" s="15"/>
@@ -5173,7 +5173,7 @@
       <c r="G150" s="56"/>
       <c r="H150" s="14"/>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" s="16"/>
       <c r="B151" s="15"/>
       <c r="C151" s="15"/>
@@ -5183,7 +5183,7 @@
       <c r="G151" s="56"/>
       <c r="H151" s="14"/>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" s="38"/>
       <c r="B152" s="15"/>
       <c r="C152" s="15"/>
@@ -5193,7 +5193,7 @@
       <c r="G152" s="56"/>
       <c r="H152" s="14"/>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" s="50"/>
       <c r="B153" s="15"/>
       <c r="C153" s="15"/>
@@ -5203,7 +5203,7 @@
       <c r="G153" s="56"/>
       <c r="H153" s="14"/>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" s="16"/>
       <c r="B154" s="15"/>
       <c r="C154" s="15"/>
@@ -5213,7 +5213,7 @@
       <c r="G154" s="56"/>
       <c r="H154" s="14"/>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155" s="16"/>
       <c r="B155" s="15"/>
       <c r="C155" s="15"/>
@@ -5223,7 +5223,7 @@
       <c r="G155" s="56"/>
       <c r="H155" s="14"/>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" s="38"/>
       <c r="B156" s="15"/>
       <c r="C156" s="15"/>
@@ -5233,7 +5233,7 @@
       <c r="G156" s="56"/>
       <c r="H156" s="14"/>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" s="50"/>
       <c r="B157" s="15"/>
       <c r="C157" s="15"/>
@@ -5243,7 +5243,7 @@
       <c r="G157" s="56"/>
       <c r="H157" s="14"/>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" s="16"/>
       <c r="B158" s="15"/>
       <c r="C158" s="15"/>
@@ -5253,7 +5253,7 @@
       <c r="G158" s="56"/>
       <c r="H158" s="14"/>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" s="16"/>
       <c r="B159" s="15"/>
       <c r="C159" s="15"/>
@@ -5263,7 +5263,7 @@
       <c r="G159" s="56"/>
       <c r="H159" s="14"/>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160" s="38"/>
       <c r="B160" s="15"/>
       <c r="C160" s="15"/>
@@ -5273,7 +5273,7 @@
       <c r="G160" s="56"/>
       <c r="H160" s="14"/>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" s="50"/>
       <c r="B161" s="15"/>
       <c r="C161" s="15"/>
@@ -5283,7 +5283,7 @@
       <c r="G161" s="56"/>
       <c r="H161" s="14"/>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" s="16"/>
       <c r="B162" s="15"/>
       <c r="C162" s="15"/>
@@ -5293,7 +5293,7 @@
       <c r="G162" s="56"/>
       <c r="H162" s="14"/>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" s="16"/>
       <c r="B163" s="15"/>
       <c r="C163" s="15"/>
@@ -5303,7 +5303,7 @@
       <c r="G163" s="56"/>
       <c r="H163" s="14"/>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" s="38"/>
       <c r="B164" s="15"/>
       <c r="C164" s="15"/>
@@ -5313,7 +5313,7 @@
       <c r="G164" s="56"/>
       <c r="H164" s="14"/>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165" s="50"/>
       <c r="B165" s="15"/>
       <c r="C165" s="15"/>
@@ -5323,7 +5323,7 @@
       <c r="G165" s="56"/>
       <c r="H165" s="14"/>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166" s="16"/>
       <c r="B166" s="15"/>
       <c r="C166" s="15"/>
@@ -5333,7 +5333,7 @@
       <c r="G166" s="56"/>
       <c r="H166" s="14"/>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167" s="16"/>
       <c r="B167" s="15"/>
       <c r="C167" s="15"/>
@@ -5343,7 +5343,7 @@
       <c r="G167" s="56"/>
       <c r="H167" s="14"/>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168" s="38"/>
       <c r="B168" s="15"/>
       <c r="C168" s="15"/>
@@ -5353,7 +5353,7 @@
       <c r="G168" s="56"/>
       <c r="H168" s="14"/>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169" s="50"/>
       <c r="B169" s="15"/>
       <c r="C169" s="15"/>
@@ -5363,7 +5363,7 @@
       <c r="G169" s="56"/>
       <c r="H169" s="14"/>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170" s="16"/>
       <c r="B170" s="15"/>
       <c r="C170" s="15"/>
@@ -5373,7 +5373,7 @@
       <c r="G170" s="56"/>
       <c r="H170" s="14"/>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171" s="16"/>
       <c r="B171" s="15"/>
       <c r="C171" s="15"/>
@@ -5383,7 +5383,7 @@
       <c r="G171" s="56"/>
       <c r="H171" s="14"/>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172" s="38"/>
       <c r="B172" s="15"/>
       <c r="C172" s="15"/>
@@ -5393,7 +5393,7 @@
       <c r="G172" s="56"/>
       <c r="H172" s="14"/>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" s="50"/>
       <c r="B173" s="15"/>
       <c r="C173" s="15"/>
@@ -5403,7 +5403,7 @@
       <c r="G173" s="56"/>
       <c r="H173" s="14"/>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174" s="16"/>
       <c r="B174" s="15"/>
       <c r="C174" s="15"/>
@@ -5413,7 +5413,7 @@
       <c r="G174" s="56"/>
       <c r="H174" s="14"/>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175" s="16"/>
       <c r="B175" s="15"/>
       <c r="C175" s="15"/>
@@ -5423,7 +5423,7 @@
       <c r="G175" s="56"/>
       <c r="H175" s="14"/>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176" s="38"/>
       <c r="B176" s="15"/>
       <c r="C176" s="15"/>
@@ -5433,7 +5433,7 @@
       <c r="G176" s="56"/>
       <c r="H176" s="14"/>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177" s="50"/>
       <c r="B177" s="15"/>
       <c r="C177" s="15"/>
@@ -5443,7 +5443,7 @@
       <c r="G177" s="56"/>
       <c r="H177" s="14"/>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178" s="16"/>
       <c r="B178" s="15"/>
       <c r="C178" s="15"/>
@@ -5453,7 +5453,7 @@
       <c r="G178" s="56"/>
       <c r="H178" s="14"/>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179" s="16"/>
       <c r="B179" s="15"/>
       <c r="C179" s="15"/>
@@ -5463,7 +5463,7 @@
       <c r="G179" s="56"/>
       <c r="H179" s="14"/>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180" s="38"/>
       <c r="B180" s="15"/>
       <c r="C180" s="15"/>
@@ -5473,7 +5473,7 @@
       <c r="G180" s="56"/>
       <c r="H180" s="14"/>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181" s="50"/>
       <c r="B181" s="15"/>
       <c r="C181" s="15"/>
@@ -5483,7 +5483,7 @@
       <c r="G181" s="56"/>
       <c r="H181" s="14"/>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182" s="16"/>
       <c r="B182" s="15"/>
       <c r="C182" s="15"/>
@@ -5493,7 +5493,7 @@
       <c r="G182" s="56"/>
       <c r="H182" s="14"/>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183" s="16"/>
       <c r="B183" s="15"/>
       <c r="C183" s="15"/>
@@ -5503,7 +5503,7 @@
       <c r="G183" s="56"/>
       <c r="H183" s="14"/>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184" s="38"/>
       <c r="B184" s="15"/>
       <c r="C184" s="15"/>
@@ -5513,7 +5513,7 @@
       <c r="G184" s="56"/>
       <c r="H184" s="14"/>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185" s="50"/>
       <c r="B185" s="15"/>
       <c r="C185" s="15"/>
@@ -5523,7 +5523,7 @@
       <c r="G185" s="56"/>
       <c r="H185" s="14"/>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186" s="16"/>
       <c r="B186" s="15"/>
       <c r="C186" s="15"/>
@@ -5533,7 +5533,7 @@
       <c r="G186" s="56"/>
       <c r="H186" s="14"/>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A187" s="16"/>
       <c r="B187" s="15"/>
       <c r="C187" s="15"/>
@@ -5543,7 +5543,7 @@
       <c r="G187" s="56"/>
       <c r="H187" s="14"/>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188" s="38"/>
       <c r="B188" s="15"/>
       <c r="C188" s="15"/>
@@ -5553,7 +5553,7 @@
       <c r="G188" s="56"/>
       <c r="H188" s="14"/>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189" s="50"/>
       <c r="B189" s="15"/>
       <c r="C189" s="15"/>
@@ -5563,7 +5563,7 @@
       <c r="G189" s="56"/>
       <c r="H189" s="14"/>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A190" s="16"/>
       <c r="B190" s="15"/>
       <c r="C190" s="15"/>
@@ -5573,7 +5573,7 @@
       <c r="G190" s="56"/>
       <c r="H190" s="14"/>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191" s="16"/>
       <c r="B191" s="15"/>
       <c r="C191" s="15"/>
@@ -5583,7 +5583,7 @@
       <c r="G191" s="56"/>
       <c r="H191" s="14"/>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A192" s="38"/>
       <c r="B192" s="15"/>
       <c r="C192" s="15"/>
@@ -5593,7 +5593,7 @@
       <c r="G192" s="56"/>
       <c r="H192" s="14"/>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193" s="50"/>
       <c r="B193" s="15"/>
       <c r="C193" s="15"/>
@@ -5603,7 +5603,7 @@
       <c r="G193" s="56"/>
       <c r="H193" s="14"/>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194" s="16"/>
       <c r="B194" s="15"/>
       <c r="C194" s="15"/>
@@ -5613,7 +5613,7 @@
       <c r="G194" s="56"/>
       <c r="H194" s="14"/>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195" s="16"/>
       <c r="B195" s="15"/>
       <c r="C195" s="15"/>
@@ -5623,7 +5623,7 @@
       <c r="G195" s="56"/>
       <c r="H195" s="14"/>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196" s="38"/>
       <c r="B196" s="15"/>
       <c r="C196" s="15"/>
@@ -5633,7 +5633,7 @@
       <c r="G196" s="56"/>
       <c r="H196" s="14"/>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197" s="50"/>
       <c r="B197" s="15"/>
       <c r="C197" s="15"/>
@@ -5643,7 +5643,7 @@
       <c r="G197" s="56"/>
       <c r="H197" s="14"/>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198" s="16"/>
       <c r="B198" s="15"/>
       <c r="C198" s="15"/>
@@ -5653,7 +5653,7 @@
       <c r="G198" s="56"/>
       <c r="H198" s="14"/>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A199" s="16"/>
       <c r="B199" s="15"/>
       <c r="C199" s="15"/>
@@ -5663,7 +5663,7 @@
       <c r="G199" s="56"/>
       <c r="H199" s="14"/>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200" s="38"/>
       <c r="B200" s="15"/>
       <c r="C200" s="15"/>
@@ -5673,7 +5673,7 @@
       <c r="G200" s="56"/>
       <c r="H200" s="14"/>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201" s="50"/>
       <c r="B201" s="15"/>
       <c r="C201" s="15"/>
@@ -5683,7 +5683,7 @@
       <c r="G201" s="56"/>
       <c r="H201" s="14"/>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A202" s="16"/>
       <c r="B202" s="15"/>
       <c r="C202" s="15"/>
@@ -5693,7 +5693,7 @@
       <c r="G202" s="56"/>
       <c r="H202" s="14"/>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A203" s="16"/>
       <c r="B203" s="15"/>
       <c r="C203" s="15"/>
@@ -5703,7 +5703,7 @@
       <c r="G203" s="56"/>
       <c r="H203" s="14"/>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A204" s="38"/>
       <c r="B204" s="15"/>
       <c r="C204" s="15"/>
@@ -5713,7 +5713,7 @@
       <c r="G204" s="56"/>
       <c r="H204" s="14"/>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A205" s="50"/>
       <c r="B205" s="15"/>
       <c r="C205" s="15"/>
@@ -5723,7 +5723,7 @@
       <c r="G205" s="56"/>
       <c r="H205" s="14"/>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A206" s="16"/>
       <c r="B206" s="15"/>
       <c r="C206" s="15"/>
@@ -5733,7 +5733,7 @@
       <c r="G206" s="56"/>
       <c r="H206" s="14"/>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A207" s="16"/>
       <c r="B207" s="15"/>
       <c r="C207" s="15"/>
@@ -5743,7 +5743,7 @@
       <c r="G207" s="56"/>
       <c r="H207" s="14"/>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A208" s="38"/>
       <c r="B208" s="15"/>
       <c r="C208" s="15"/>
@@ -5753,7 +5753,7 @@
       <c r="G208" s="56"/>
       <c r="H208" s="14"/>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A209" s="50"/>
       <c r="B209" s="15"/>
       <c r="C209" s="15"/>
@@ -5763,7 +5763,7 @@
       <c r="G209" s="56"/>
       <c r="H209" s="14"/>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A210" s="16"/>
       <c r="B210" s="15"/>
       <c r="C210" s="15"/>
@@ -5773,7 +5773,7 @@
       <c r="G210" s="56"/>
       <c r="H210" s="14"/>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A211" s="16"/>
       <c r="B211" s="15"/>
       <c r="C211" s="15"/>
@@ -5783,7 +5783,7 @@
       <c r="G211" s="56"/>
       <c r="H211" s="14"/>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A212" s="38"/>
       <c r="B212" s="15"/>
       <c r="C212" s="15"/>
@@ -5793,7 +5793,7 @@
       <c r="G212" s="56"/>
       <c r="H212" s="14"/>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A213" s="50"/>
       <c r="B213" s="15"/>
       <c r="C213" s="15"/>
@@ -5803,7 +5803,7 @@
       <c r="G213" s="56"/>
       <c r="H213" s="14"/>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A214" s="16"/>
       <c r="B214" s="15"/>
       <c r="C214" s="15"/>
@@ -5813,7 +5813,7 @@
       <c r="G214" s="56"/>
       <c r="H214" s="14"/>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A215" s="16"/>
       <c r="B215" s="15"/>
       <c r="C215" s="15"/>
@@ -5823,7 +5823,7 @@
       <c r="G215" s="56"/>
       <c r="H215" s="14"/>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A216" s="38"/>
       <c r="B216" s="15"/>
       <c r="C216" s="15"/>
@@ -5833,7 +5833,7 @@
       <c r="G216" s="56"/>
       <c r="H216" s="14"/>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A217" s="50"/>
       <c r="B217" s="15"/>
       <c r="C217" s="15"/>
@@ -5843,7 +5843,7 @@
       <c r="G217" s="56"/>
       <c r="H217" s="14"/>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A218" s="16"/>
       <c r="B218" s="15"/>
       <c r="C218" s="15"/>
@@ -5853,7 +5853,7 @@
       <c r="G218" s="56"/>
       <c r="H218" s="14"/>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A219" s="16"/>
       <c r="B219" s="15"/>
       <c r="C219" s="15"/>
@@ -5863,7 +5863,7 @@
       <c r="G219" s="56"/>
       <c r="H219" s="14"/>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A220" s="38"/>
       <c r="B220" s="15"/>
       <c r="C220" s="15"/>
@@ -5873,7 +5873,7 @@
       <c r="G220" s="56"/>
       <c r="H220" s="14"/>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A221" s="50"/>
       <c r="B221" s="15"/>
       <c r="C221" s="15"/>
@@ -5883,7 +5883,7 @@
       <c r="G221" s="56"/>
       <c r="H221" s="14"/>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A222" s="16"/>
       <c r="B222" s="15"/>
       <c r="C222" s="15"/>
@@ -5893,7 +5893,7 @@
       <c r="G222" s="56"/>
       <c r="H222" s="14"/>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A223" s="16"/>
       <c r="B223" s="15"/>
       <c r="C223" s="15"/>
@@ -5903,7 +5903,7 @@
       <c r="G223" s="56"/>
       <c r="H223" s="14"/>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A224" s="38"/>
       <c r="B224" s="15"/>
       <c r="C224" s="15"/>
@@ -5913,7 +5913,7 @@
       <c r="G224" s="56"/>
       <c r="H224" s="14"/>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A225" s="50"/>
       <c r="B225" s="15"/>
       <c r="C225" s="15"/>
@@ -5923,7 +5923,7 @@
       <c r="G225" s="56"/>
       <c r="H225" s="14"/>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A226" s="16"/>
       <c r="B226" s="15"/>
       <c r="C226" s="15"/>
@@ -5933,7 +5933,7 @@
       <c r="G226" s="56"/>
       <c r="H226" s="14"/>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A227" s="16"/>
       <c r="B227" s="15"/>
       <c r="C227" s="15"/>
@@ -5943,7 +5943,7 @@
       <c r="G227" s="56"/>
       <c r="H227" s="14"/>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A228" s="38"/>
       <c r="B228" s="15"/>
       <c r="C228" s="15"/>
@@ -5953,7 +5953,7 @@
       <c r="G228" s="56"/>
       <c r="H228" s="14"/>
     </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A229" s="50"/>
       <c r="B229" s="15"/>
       <c r="C229" s="15"/>
@@ -5963,7 +5963,7 @@
       <c r="G229" s="56"/>
       <c r="H229" s="14"/>
     </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A230" s="16"/>
       <c r="B230" s="15"/>
       <c r="C230" s="15"/>
@@ -5973,7 +5973,7 @@
       <c r="G230" s="56"/>
       <c r="H230" s="14"/>
     </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A231" s="16"/>
       <c r="B231" s="15"/>
       <c r="C231" s="15"/>
@@ -5981,7 +5981,7 @@
       <c r="G231" s="56"/>
       <c r="H231" s="14"/>
     </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A232" s="16"/>
       <c r="B232" s="15"/>
       <c r="C232" s="15"/>
@@ -5989,7 +5989,7 @@
       <c r="G232" s="56"/>
       <c r="H232" s="14"/>
     </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A233" s="38"/>
       <c r="B233" s="15"/>
       <c r="C233" s="15"/>
@@ -5997,7 +5997,7 @@
       <c r="G233" s="56"/>
       <c r="H233" s="14"/>
     </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A234" s="50"/>
       <c r="B234" s="15"/>
       <c r="C234" s="15"/>
@@ -6005,7 +6005,7 @@
       <c r="G234" s="56"/>
       <c r="H234" s="14"/>
     </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A235" s="16"/>
       <c r="B235" s="15"/>
       <c r="C235" s="15"/>
@@ -6013,7 +6013,7 @@
       <c r="G235" s="56"/>
       <c r="H235" s="14"/>
     </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A236" s="16"/>
       <c r="B236" s="15"/>
       <c r="C236" s="15"/>
@@ -6021,7 +6021,7 @@
       <c r="G236" s="56"/>
       <c r="H236" s="14"/>
     </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A237" s="16"/>
       <c r="B237" s="15"/>
       <c r="C237" s="15"/>
@@ -6029,7 +6029,7 @@
       <c r="G237" s="56"/>
       <c r="H237" s="14"/>
     </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A238" s="38"/>
       <c r="B238" s="15"/>
       <c r="C238" s="15"/>
@@ -6037,7 +6037,7 @@
       <c r="G238" s="56"/>
       <c r="H238" s="14"/>
     </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A239" s="50"/>
       <c r="B239" s="15"/>
       <c r="C239" s="15"/>
@@ -6045,7 +6045,7 @@
       <c r="G239" s="56"/>
       <c r="H239" s="14"/>
     </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A240" s="16"/>
       <c r="B240" s="15"/>
       <c r="C240" s="15"/>
@@ -6053,7 +6053,7 @@
       <c r="G240" s="56"/>
       <c r="H240" s="14"/>
     </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A241" s="16"/>
       <c r="B241" s="15"/>
       <c r="C241" s="15"/>
@@ -6061,7 +6061,7 @@
       <c r="G241" s="56"/>
       <c r="H241" s="14"/>
     </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A242" s="16"/>
       <c r="B242" s="15"/>
       <c r="C242" s="15"/>
@@ -6069,7 +6069,7 @@
       <c r="G242" s="56"/>
       <c r="H242" s="14"/>
     </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A243" s="38"/>
       <c r="B243" s="15"/>
       <c r="C243" s="15"/>
@@ -6077,7 +6077,7 @@
       <c r="G243" s="56"/>
       <c r="H243" s="14"/>
     </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A244" s="50"/>
       <c r="B244" s="15"/>
       <c r="C244" s="15"/>
@@ -6085,7 +6085,7 @@
       <c r="G244" s="56"/>
       <c r="H244" s="14"/>
     </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A245" s="16"/>
       <c r="B245" s="15"/>
       <c r="C245" s="15"/>
@@ -6093,7 +6093,7 @@
       <c r="G245" s="56"/>
       <c r="H245" s="14"/>
     </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A246" s="16"/>
       <c r="B246" s="15"/>
       <c r="C246" s="15"/>
@@ -6101,7 +6101,7 @@
       <c r="G246" s="56"/>
       <c r="H246" s="14"/>
     </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A247" s="16"/>
       <c r="B247" s="15"/>
       <c r="C247" s="15"/>
@@ -6109,7 +6109,7 @@
       <c r="G247" s="56"/>
       <c r="H247" s="14"/>
     </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A248" s="38"/>
       <c r="B248" s="15"/>
       <c r="C248" s="15"/>
@@ -6117,7 +6117,7 @@
       <c r="G248" s="56"/>
       <c r="H248" s="14"/>
     </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A249" s="50"/>
       <c r="B249" s="15"/>
       <c r="C249" s="15"/>
@@ -6125,7 +6125,7 @@
       <c r="G249" s="56"/>
       <c r="H249" s="14"/>
     </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A250" s="16"/>
       <c r="B250" s="15"/>
       <c r="C250" s="15"/>
@@ -6133,7 +6133,7 @@
       <c r="G250" s="56"/>
       <c r="H250" s="14"/>
     </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A251" s="16"/>
       <c r="B251" s="15"/>
       <c r="C251" s="15"/>
@@ -6141,7 +6141,7 @@
       <c r="G251" s="56"/>
       <c r="H251" s="14"/>
     </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A252" s="16"/>
       <c r="B252" s="15"/>
       <c r="C252" s="15"/>
@@ -6149,7 +6149,7 @@
       <c r="G252" s="56"/>
       <c r="H252" s="14"/>
     </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A253" s="38"/>
       <c r="B253" s="15"/>
       <c r="C253" s="15"/>
@@ -6157,7 +6157,7 @@
       <c r="G253" s="56"/>
       <c r="H253" s="14"/>
     </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A254" s="50"/>
       <c r="B254" s="15"/>
       <c r="C254" s="15"/>
@@ -6165,7 +6165,7 @@
       <c r="G254" s="56"/>
       <c r="H254" s="14"/>
     </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A255" s="16"/>
       <c r="B255" s="15"/>
       <c r="C255" s="15"/>
@@ -6173,7 +6173,7 @@
       <c r="G255" s="56"/>
       <c r="H255" s="14"/>
     </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A256" s="16"/>
       <c r="B256" s="15"/>
       <c r="C256" s="15"/>
@@ -6181,7 +6181,7 @@
       <c r="G256" s="56"/>
       <c r="H256" s="14"/>
     </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A257" s="16"/>
       <c r="B257" s="15"/>
       <c r="C257" s="15"/>
@@ -6189,7 +6189,7 @@
       <c r="G257" s="56"/>
       <c r="H257" s="14"/>
     </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A258" s="38"/>
       <c r="B258" s="15"/>
       <c r="C258" s="15"/>
@@ -6197,7 +6197,7 @@
       <c r="G258" s="56"/>
       <c r="H258" s="14"/>
     </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A259" s="50"/>
       <c r="B259" s="15"/>
       <c r="C259" s="15"/>
@@ -6205,7 +6205,7 @@
       <c r="G259" s="56"/>
       <c r="H259" s="14"/>
     </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A260" s="16"/>
       <c r="B260" s="15"/>
       <c r="C260" s="15"/>
@@ -6213,7 +6213,7 @@
       <c r="G260" s="56"/>
       <c r="H260" s="14"/>
     </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A261" s="16"/>
       <c r="B261" s="15"/>
       <c r="C261" s="15"/>
@@ -6221,7 +6221,7 @@
       <c r="G261" s="56"/>
       <c r="H261" s="14"/>
     </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A262" s="16"/>
       <c r="B262" s="15"/>
       <c r="C262" s="15"/>
@@ -6229,7 +6229,7 @@
       <c r="G262" s="56"/>
       <c r="H262" s="14"/>
     </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A263" s="38"/>
       <c r="B263" s="15"/>
       <c r="C263" s="15"/>
@@ -6237,7 +6237,7 @@
       <c r="G263" s="56"/>
       <c r="H263" s="14"/>
     </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A264" s="50"/>
       <c r="B264" s="15"/>
       <c r="C264" s="15"/>
@@ -6245,7 +6245,7 @@
       <c r="G264" s="56"/>
       <c r="H264" s="14"/>
     </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A265" s="16"/>
       <c r="B265" s="15"/>
       <c r="C265" s="15"/>
@@ -6253,7 +6253,7 @@
       <c r="G265" s="56"/>
       <c r="H265" s="14"/>
     </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A266" s="16"/>
       <c r="B266" s="15"/>
       <c r="C266" s="15"/>
@@ -6261,7 +6261,7 @@
       <c r="G266" s="56"/>
       <c r="H266" s="14"/>
     </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A267" s="16"/>
       <c r="B267" s="15"/>
       <c r="C267" s="15"/>
@@ -6269,7 +6269,7 @@
       <c r="G267" s="56"/>
       <c r="H267" s="14"/>
     </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A268" s="38"/>
       <c r="B268" s="15"/>
       <c r="C268" s="15"/>
@@ -6277,7 +6277,7 @@
       <c r="G268" s="56"/>
       <c r="H268" s="14"/>
     </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A269" s="50"/>
       <c r="B269" s="15"/>
       <c r="C269" s="15"/>
@@ -6285,7 +6285,7 @@
       <c r="G269" s="56"/>
       <c r="H269" s="14"/>
     </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A270" s="16"/>
       <c r="B270" s="15"/>
       <c r="C270" s="15"/>
@@ -6293,7 +6293,7 @@
       <c r="G270" s="56"/>
       <c r="H270" s="14"/>
     </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A271" s="16"/>
       <c r="B271" s="15"/>
       <c r="C271" s="15"/>
@@ -6301,7 +6301,7 @@
       <c r="G271" s="56"/>
       <c r="H271" s="14"/>
     </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A272" s="16"/>
       <c r="B272" s="15"/>
       <c r="C272" s="15"/>
@@ -6309,7 +6309,7 @@
       <c r="G272" s="56"/>
       <c r="H272" s="14"/>
     </row>
-    <row r="273" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A273" s="38"/>
       <c r="B273" s="15"/>
       <c r="C273" s="15"/>
@@ -6317,7 +6317,7 @@
       <c r="G273" s="56"/>
       <c r="H273" s="14"/>
     </row>
-    <row r="274" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A274" s="50"/>
       <c r="B274" s="15"/>
       <c r="C274" s="15"/>
@@ -6325,7 +6325,7 @@
       <c r="G274" s="56"/>
       <c r="H274" s="14"/>
     </row>
-    <row r="275" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A275" s="16"/>
       <c r="B275" s="15"/>
       <c r="C275" s="15"/>
@@ -6333,7 +6333,7 @@
       <c r="G275" s="56"/>
       <c r="H275" s="14"/>
     </row>
-    <row r="276" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A276" s="16"/>
       <c r="B276" s="15"/>
       <c r="C276" s="15"/>
@@ -6341,7 +6341,7 @@
       <c r="G276" s="56"/>
       <c r="H276" s="14"/>
     </row>
-    <row r="277" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A277" s="16"/>
       <c r="B277" s="15"/>
       <c r="C277" s="15"/>
@@ -6349,7 +6349,7 @@
       <c r="G277" s="56"/>
       <c r="H277" s="14"/>
     </row>
-    <row r="278" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A278" s="38"/>
       <c r="B278" s="15"/>
       <c r="C278" s="15"/>
@@ -6357,7 +6357,7 @@
       <c r="G278" s="56"/>
       <c r="H278" s="14"/>
     </row>
-    <row r="279" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A279" s="50"/>
       <c r="B279" s="15"/>
       <c r="C279" s="15"/>
@@ -6365,7 +6365,7 @@
       <c r="G279" s="56"/>
       <c r="H279" s="14"/>
     </row>
-    <row r="280" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A280" s="16"/>
       <c r="B280" s="15"/>
       <c r="C280" s="15"/>
@@ -6373,7 +6373,7 @@
       <c r="G280" s="56"/>
       <c r="H280" s="14"/>
     </row>
-    <row r="281" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A281" s="16"/>
       <c r="B281" s="15"/>
       <c r="C281" s="15"/>
@@ -6381,7 +6381,7 @@
       <c r="G281" s="56"/>
       <c r="H281" s="14"/>
     </row>
-    <row r="282" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A282" s="16"/>
       <c r="B282" s="15"/>
       <c r="C282" s="15"/>
@@ -6389,7 +6389,7 @@
       <c r="G282" s="56"/>
       <c r="H282" s="14"/>
     </row>
-    <row r="283" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A283" s="38"/>
       <c r="B283" s="15"/>
       <c r="C283" s="15"/>
@@ -6397,7 +6397,7 @@
       <c r="G283" s="56"/>
       <c r="H283" s="14"/>
     </row>
-    <row r="284" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A284" s="50"/>
       <c r="B284" s="15"/>
       <c r="C284" s="15"/>
@@ -6405,7 +6405,7 @@
       <c r="G284" s="56"/>
       <c r="H284" s="14"/>
     </row>
-    <row r="285" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A285" s="16"/>
       <c r="B285" s="15"/>
       <c r="C285" s="15"/>
@@ -6413,7 +6413,7 @@
       <c r="G285" s="56"/>
       <c r="H285" s="14"/>
     </row>
-    <row r="286" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A286" s="16"/>
       <c r="B286" s="15"/>
       <c r="C286" s="15"/>
@@ -6421,7 +6421,7 @@
       <c r="G286" s="56"/>
       <c r="H286" s="14"/>
     </row>
-    <row r="287" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A287" s="16"/>
       <c r="B287" s="15"/>
       <c r="C287" s="15"/>
@@ -6429,7 +6429,7 @@
       <c r="G287" s="56"/>
       <c r="H287" s="14"/>
     </row>
-    <row r="288" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A288" s="38"/>
       <c r="B288" s="15"/>
       <c r="C288" s="15"/>
@@ -6437,7 +6437,7 @@
       <c r="G288" s="56"/>
       <c r="H288" s="14"/>
     </row>
-    <row r="289" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A289" s="50"/>
       <c r="B289" s="15"/>
       <c r="C289" s="15"/>
@@ -6445,7 +6445,7 @@
       <c r="G289" s="56"/>
       <c r="H289" s="14"/>
     </row>
-    <row r="290" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A290" s="16"/>
       <c r="B290" s="15"/>
       <c r="C290" s="15"/>
@@ -6453,7 +6453,7 @@
       <c r="G290" s="56"/>
       <c r="H290" s="14"/>
     </row>
-    <row r="291" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A291" s="16"/>
       <c r="B291" s="15"/>
       <c r="C291" s="15"/>
@@ -6461,7 +6461,7 @@
       <c r="G291" s="56"/>
       <c r="H291" s="14"/>
     </row>
-    <row r="292" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A292" s="16"/>
       <c r="B292" s="15"/>
       <c r="C292" s="15"/>
@@ -6469,7 +6469,7 @@
       <c r="G292" s="56"/>
       <c r="H292" s="14"/>
     </row>
-    <row r="293" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A293" s="38"/>
       <c r="B293" s="15"/>
       <c r="C293" s="15"/>
@@ -6477,7 +6477,7 @@
       <c r="G293" s="56"/>
       <c r="H293" s="14"/>
     </row>
-    <row r="294" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A294" s="50"/>
       <c r="B294" s="15"/>
       <c r="C294" s="15"/>
@@ -6485,7 +6485,7 @@
       <c r="G294" s="56"/>
       <c r="H294" s="14"/>
     </row>
-    <row r="295" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A295" s="16"/>
       <c r="B295" s="15"/>
       <c r="C295" s="15"/>
@@ -6493,7 +6493,7 @@
       <c r="G295" s="56"/>
       <c r="H295" s="14"/>
     </row>
-    <row r="296" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A296" s="16"/>
       <c r="B296" s="15"/>
       <c r="C296" s="15"/>
@@ -6501,7 +6501,7 @@
       <c r="G296" s="56"/>
       <c r="H296" s="14"/>
     </row>
-    <row r="297" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A297" s="16"/>
       <c r="B297" s="15"/>
       <c r="C297" s="15"/>
@@ -6509,7 +6509,7 @@
       <c r="G297" s="56"/>
       <c r="H297" s="14"/>
     </row>
-    <row r="298" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A298" s="38"/>
       <c r="B298" s="15"/>
       <c r="C298" s="15"/>
@@ -6517,7 +6517,7 @@
       <c r="G298" s="56"/>
       <c r="H298" s="14"/>
     </row>
-    <row r="299" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A299" s="50"/>
       <c r="B299" s="15"/>
       <c r="C299" s="15"/>
@@ -6525,7 +6525,7 @@
       <c r="G299" s="56"/>
       <c r="H299" s="14"/>
     </row>
-    <row r="300" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A300" s="16"/>
       <c r="B300" s="15"/>
       <c r="C300" s="15"/>
@@ -6533,7 +6533,7 @@
       <c r="G300" s="56"/>
       <c r="H300" s="14"/>
     </row>
-    <row r="301" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A301" s="16"/>
       <c r="B301" s="15"/>
       <c r="C301" s="15"/>
@@ -6541,7 +6541,7 @@
       <c r="G301" s="56"/>
       <c r="H301" s="14"/>
     </row>
-    <row r="302" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A302" s="16"/>
       <c r="B302" s="15"/>
       <c r="C302" s="15"/>
@@ -6549,7 +6549,7 @@
       <c r="G302" s="56"/>
       <c r="H302" s="14"/>
     </row>
-    <row r="303" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A303" s="38"/>
       <c r="B303" s="15"/>
       <c r="C303" s="15"/>
@@ -6557,7 +6557,7 @@
       <c r="G303" s="56"/>
       <c r="H303" s="14"/>
     </row>
-    <row r="304" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A304" s="50"/>
       <c r="B304" s="15"/>
       <c r="C304" s="15"/>
@@ -6565,7 +6565,7 @@
       <c r="G304" s="56"/>
       <c r="H304" s="14"/>
     </row>
-    <row r="305" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A305" s="16"/>
       <c r="B305" s="15"/>
       <c r="C305" s="15"/>
@@ -6573,7 +6573,7 @@
       <c r="G305" s="56"/>
       <c r="H305" s="14"/>
     </row>
-    <row r="306" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A306" s="16"/>
       <c r="B306" s="15"/>
       <c r="C306" s="15"/>
@@ -6581,7 +6581,7 @@
       <c r="G306" s="56"/>
       <c r="H306" s="14"/>
     </row>
-    <row r="307" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A307" s="16"/>
       <c r="B307" s="15"/>
       <c r="C307" s="15"/>
@@ -6589,7 +6589,7 @@
       <c r="G307" s="56"/>
       <c r="H307" s="14"/>
     </row>
-    <row r="308" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A308" s="38"/>
       <c r="B308" s="15"/>
       <c r="C308" s="15"/>
@@ -6597,7 +6597,7 @@
       <c r="G308" s="56"/>
       <c r="H308" s="14"/>
     </row>
-    <row r="309" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A309" s="50"/>
       <c r="B309" s="15"/>
       <c r="C309" s="15"/>
@@ -6605,7 +6605,7 @@
       <c r="G309" s="56"/>
       <c r="H309" s="14"/>
     </row>
-    <row r="310" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A310" s="16"/>
       <c r="B310" s="15"/>
       <c r="C310" s="15"/>
@@ -6613,7 +6613,7 @@
       <c r="G310" s="56"/>
       <c r="H310" s="14"/>
     </row>
-    <row r="311" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A311" s="16"/>
       <c r="B311" s="15"/>
       <c r="C311" s="15"/>
@@ -6621,7 +6621,7 @@
       <c r="G311" s="56"/>
       <c r="H311" s="14"/>
     </row>
-    <row r="312" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A312" s="16"/>
       <c r="B312" s="15"/>
       <c r="C312" s="15"/>
@@ -6629,7 +6629,7 @@
       <c r="G312" s="56"/>
       <c r="H312" s="14"/>
     </row>
-    <row r="313" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A313" s="38"/>
       <c r="B313" s="15"/>
       <c r="C313" s="15"/>
@@ -6637,7 +6637,7 @@
       <c r="G313" s="56"/>
       <c r="H313" s="14"/>
     </row>
-    <row r="314" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A314" s="50"/>
       <c r="B314" s="15"/>
       <c r="C314" s="15"/>
@@ -6645,7 +6645,7 @@
       <c r="G314" s="56"/>
       <c r="H314" s="14"/>
     </row>
-    <row r="315" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A315" s="16"/>
       <c r="B315" s="15"/>
       <c r="C315" s="15"/>
@@ -6653,7 +6653,7 @@
       <c r="G315" s="56"/>
       <c r="H315" s="14"/>
     </row>
-    <row r="316" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A316" s="16"/>
       <c r="B316" s="15"/>
       <c r="C316" s="15"/>
@@ -6661,7 +6661,7 @@
       <c r="G316" s="56"/>
       <c r="H316" s="14"/>
     </row>
-    <row r="317" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A317" s="16"/>
       <c r="B317" s="15"/>
       <c r="C317" s="15"/>
@@ -6669,7 +6669,7 @@
       <c r="G317" s="56"/>
       <c r="H317" s="14"/>
     </row>
-    <row r="318" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A318" s="38"/>
       <c r="B318" s="15"/>
       <c r="C318" s="15"/>
@@ -6677,7 +6677,7 @@
       <c r="G318" s="56"/>
       <c r="H318" s="14"/>
     </row>
-    <row r="319" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A319" s="50"/>
       <c r="B319" s="15"/>
       <c r="C319" s="15"/>
@@ -6685,7 +6685,7 @@
       <c r="G319" s="56"/>
       <c r="H319" s="14"/>
     </row>
-    <row r="320" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A320" s="16"/>
       <c r="B320" s="15"/>
       <c r="C320" s="15"/>
@@ -6693,7 +6693,7 @@
       <c r="G320" s="56"/>
       <c r="H320" s="14"/>
     </row>
-    <row r="321" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A321" s="16"/>
       <c r="B321" s="15"/>
       <c r="C321" s="15"/>
@@ -6701,7 +6701,7 @@
       <c r="G321" s="56"/>
       <c r="H321" s="14"/>
     </row>
-    <row r="322" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A322" s="16"/>
       <c r="B322" s="15"/>
       <c r="C322" s="15"/>
@@ -6709,7 +6709,7 @@
       <c r="G322" s="56"/>
       <c r="H322" s="14"/>
     </row>
-    <row r="323" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A323" s="38"/>
       <c r="B323" s="15"/>
       <c r="C323" s="15"/>
@@ -6717,7 +6717,7 @@
       <c r="G323" s="56"/>
       <c r="H323" s="14"/>
     </row>
-    <row r="324" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A324" s="50"/>
       <c r="B324" s="15"/>
       <c r="C324" s="15"/>
@@ -6725,7 +6725,7 @@
       <c r="G324" s="56"/>
       <c r="H324" s="14"/>
     </row>
-    <row r="325" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A325" s="16"/>
       <c r="B325" s="15"/>
       <c r="C325" s="15"/>
@@ -6733,7 +6733,7 @@
       <c r="G325" s="56"/>
       <c r="H325" s="14"/>
     </row>
-    <row r="326" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A326" s="16"/>
       <c r="B326" s="15"/>
       <c r="C326" s="15"/>
@@ -6741,7 +6741,7 @@
       <c r="G326" s="56"/>
       <c r="H326" s="14"/>
     </row>
-    <row r="327" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A327" s="16"/>
       <c r="B327" s="15"/>
       <c r="C327" s="15"/>
@@ -6749,7 +6749,7 @@
       <c r="G327" s="56"/>
       <c r="H327" s="14"/>
     </row>
-    <row r="328" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A328" s="38"/>
       <c r="B328" s="15"/>
       <c r="C328" s="15"/>
@@ -6757,7 +6757,7 @@
       <c r="G328" s="56"/>
       <c r="H328" s="14"/>
     </row>
-    <row r="329" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A329" s="50"/>
       <c r="B329" s="15"/>
       <c r="C329" s="15"/>
@@ -6765,7 +6765,7 @@
       <c r="G329" s="56"/>
       <c r="H329" s="14"/>
     </row>
-    <row r="330" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A330" s="16"/>
       <c r="B330" s="15"/>
       <c r="C330" s="15"/>
@@ -6773,7 +6773,7 @@
       <c r="G330" s="56"/>
       <c r="H330" s="14"/>
     </row>
-    <row r="331" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A331" s="16"/>
       <c r="B331" s="15"/>
       <c r="C331" s="15"/>
@@ -6781,7 +6781,7 @@
       <c r="G331" s="56"/>
       <c r="H331" s="14"/>
     </row>
-    <row r="332" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A332" s="16"/>
       <c r="B332" s="15"/>
       <c r="C332" s="15"/>
@@ -6789,7 +6789,7 @@
       <c r="G332" s="56"/>
       <c r="H332" s="14"/>
     </row>
-    <row r="333" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A333" s="38"/>
       <c r="B333" s="15"/>
       <c r="C333" s="15"/>
@@ -6797,7 +6797,7 @@
       <c r="G333" s="56"/>
       <c r="H333" s="14"/>
     </row>
-    <row r="334" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A334" s="50"/>
       <c r="B334" s="15"/>
       <c r="C334" s="15"/>
@@ -6805,7 +6805,7 @@
       <c r="G334" s="56"/>
       <c r="H334" s="14"/>
     </row>
-    <row r="335" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A335" s="16"/>
       <c r="B335" s="15"/>
       <c r="C335" s="15"/>
@@ -6813,7 +6813,7 @@
       <c r="G335" s="56"/>
       <c r="H335" s="14"/>
     </row>
-    <row r="336" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A336" s="16"/>
       <c r="B336" s="15"/>
       <c r="C336" s="15"/>
@@ -6821,7 +6821,7 @@
       <c r="G336" s="56"/>
       <c r="H336" s="14"/>
     </row>
-    <row r="337" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A337" s="16"/>
       <c r="B337" s="15"/>
       <c r="C337" s="15"/>
@@ -6829,7 +6829,7 @@
       <c r="G337" s="56"/>
       <c r="H337" s="14"/>
     </row>
-    <row r="338" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A338" s="38"/>
       <c r="B338" s="15"/>
       <c r="C338" s="15"/>
@@ -6837,7 +6837,7 @@
       <c r="G338" s="56"/>
       <c r="H338" s="14"/>
     </row>
-    <row r="339" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A339" s="50"/>
       <c r="B339" s="15"/>
       <c r="C339" s="15"/>
@@ -6845,7 +6845,7 @@
       <c r="G339" s="56"/>
       <c r="H339" s="14"/>
     </row>
-    <row r="340" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A340" s="16"/>
       <c r="B340" s="15"/>
       <c r="C340" s="15"/>
@@ -6853,7 +6853,7 @@
       <c r="G340" s="56"/>
       <c r="H340" s="14"/>
     </row>
-    <row r="341" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A341" s="16"/>
       <c r="B341" s="15"/>
       <c r="C341" s="15"/>
@@ -6861,7 +6861,7 @@
       <c r="G341" s="56"/>
       <c r="H341" s="14"/>
     </row>
-    <row r="342" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A342" s="16"/>
       <c r="B342" s="15"/>
       <c r="C342" s="15"/>
@@ -6869,7 +6869,7 @@
       <c r="G342" s="56"/>
       <c r="H342" s="14"/>
     </row>
-    <row r="343" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A343" s="38"/>
       <c r="B343" s="15"/>
       <c r="C343" s="15"/>
@@ -6877,7 +6877,7 @@
       <c r="G343" s="56"/>
       <c r="H343" s="14"/>
     </row>
-    <row r="344" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A344" s="50"/>
       <c r="B344" s="15"/>
       <c r="C344" s="15"/>
@@ -6885,7 +6885,7 @@
       <c r="G344" s="56"/>
       <c r="H344" s="14"/>
     </row>
-    <row r="345" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A345" s="16"/>
       <c r="B345" s="15"/>
       <c r="C345" s="15"/>
@@ -6893,7 +6893,7 @@
       <c r="G345" s="56"/>
       <c r="H345" s="14"/>
     </row>
-    <row r="346" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A346" s="16"/>
       <c r="B346" s="15"/>
       <c r="C346" s="15"/>
@@ -6913,14 +6913,14 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6931,7 +6931,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -6942,7 +6942,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>0</v>
       </c>
